--- a/outputs/Склад против Кореи.xlsx
+++ b/outputs/Склад против Кореи.xlsx
@@ -774,47 +774,47 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="n">
+      <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>CELIMAX</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>CELIMAX PORE+DARK SPOT BRIGHTENING SERUM_30ml [30ml]/Сыворотка для выравнивания тона и рельефа кожи лица</t>
         </is>
       </c>
-      <c r="D8" s="5" t="n">
+      <c r="D8" s="7" t="n">
         <v>70</v>
       </c>
-      <c r="E8" s="5" t="n">
+      <c r="E8" s="7" t="n">
         <v>688</v>
       </c>
-      <c r="F8" s="5" t="n">
-        <v>4400</v>
-      </c>
-      <c r="G8" s="5" t="n">
-        <v>273</v>
-      </c>
-      <c r="H8" s="5" t="n">
-        <v>314</v>
-      </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>Аннеси</t>
-        </is>
-      </c>
-      <c r="J8" s="5" t="n">
-        <v>-374</v>
-      </c>
-      <c r="K8" s="4" t="n">
-        <v>-54.4</v>
-      </c>
-      <c r="L8" s="5" t="n">
-        <v>-26170</v>
+      <c r="F8" s="7" t="n">
+        <v>9900</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>614</v>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>706</v>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>G&amp;E Global</t>
+        </is>
+      </c>
+      <c r="J8" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="K8" s="6" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L8" s="7" t="n">
+        <v>1280</v>
       </c>
     </row>
     <row r="9">
@@ -1014,27 +1014,27 @@
         <v>664</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>3265</v>
+        <v>9000</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>202</v>
+        <v>558</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>233</v>
+        <v>642</v>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>G&amp;E Global</t>
+          <t>Papa Cosmetic</t>
         </is>
       </c>
       <c r="J13" s="5" t="n">
-        <v>-431</v>
+        <v>-22</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-64.90000000000001</v>
+        <v>-3.3</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>-1948416</v>
+        <v>-100163</v>
       </c>
     </row>
     <row r="14">
@@ -5232,7 +5232,7 @@
       <c r="J121" s="10" t="inlineStr"/>
       <c r="K121" s="9" t="inlineStr"/>
       <c r="L121" s="10" t="n">
-        <v>-2809014</v>
+        <v>-933311</v>
       </c>
     </row>
   </sheetData>
@@ -5246,7 +5246,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L103"/>
+  <dimension ref="A1:L102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5329,7 +5329,7 @@
       <c r="A2" s="2" t="n"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>CELIMAX</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C2" s="2" t="n"/>
@@ -5349,42 +5349,42 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>CELIMAX</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Celimax Dual Barrier Creamy Toner, тонер 150 мл</t>
+          <t>JIGOTT - Hyaluronic Acid Real Ampoule Mask [27ml] / Ампульная маска с гиалуроновой кислотой</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
-        <v>4520</v>
+        <v>1190</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>664</v>
+        <v>23</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>3265</v>
+        <v>159</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>202</v>
+        <v>10</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>233</v>
+        <v>11</v>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>G&amp;E Global</t>
+          <t>FINESKIN (ответ)</t>
         </is>
       </c>
       <c r="J3" s="5" t="n">
-        <v>-431</v>
+        <v>-11</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>-64.90000000000001</v>
+        <v>-50.1</v>
       </c>
       <c r="L3" s="5" t="n">
-        <v>-1948416</v>
+        <v>-13555</v>
       </c>
     </row>
     <row r="4">
@@ -5393,65 +5393,91 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>CELIMAX</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>CELIMAX PORE+DARK SPOT BRIGHTENING SERUM_30ml [30ml]/Сыворотка для выравнивания тона и рельефа кожи лица</t>
+          <t>JIGOTT - Camellia Real Ampoule Mask [27ml] / Ампульная маска с экстрактом камелии</t>
         </is>
       </c>
       <c r="D4" s="5" t="n">
-        <v>70</v>
+        <v>1190</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>688</v>
+        <v>23</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>4400</v>
+        <v>159</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>273</v>
+        <v>10</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>314</v>
+        <v>11</v>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>Аннеси</t>
+          <t>FINESKIN (ответ)</t>
         </is>
       </c>
       <c r="J4" s="5" t="n">
-        <v>-374</v>
+        <v>-11</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>-54.4</v>
+        <v>-50.1</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>-26170</v>
+        <v>-13555</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n"/>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="A5" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>JIGOTT</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="n"/>
-      <c r="G5" s="3" t="n"/>
-      <c r="H5" s="3" t="n"/>
-      <c r="I5" s="2" t="n"/>
-      <c r="J5" s="3" t="n"/>
-      <c r="K5" s="2" t="n"/>
-      <c r="L5" s="3" t="n"/>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>JIGOTT - Caviar Real Ampoule Mask [27ml] / Ампульная маска с экстрактом икры</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>1190</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>159</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>FINESKIN (ответ)</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>-11</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>-50.1</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>-13555</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
@@ -5460,7 +5486,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT - Hyaluronic Acid Real Ampoule Mask [27ml] / Ампульная маска с гиалуроновой кислотой</t>
+          <t>JIGOTT - Collagen Real Ampoule Mask [27ml] / Ампульная маска с коллагеном</t>
         </is>
       </c>
       <c r="D6" s="5" t="n">
@@ -5495,7 +5521,7 @@
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
@@ -5504,7 +5530,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT - Camellia Real Ampoule Mask [27ml] / Ампульная маска с экстрактом камелии</t>
+          <t>JIGOTT - Cucumber Real Ampoule Mask [27ml] / Тканевая маска с экстрактом огурца</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
@@ -5539,7 +5565,7 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
@@ -5548,7 +5574,7 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT - Caviar Real Ampoule Mask [27ml] / Ампульная маска с экстрактом икры</t>
+          <t>JIGOTT - Green Tea Real Ampoule Mask [27ml] / Ампульная маска с экстрактом зеленого чая</t>
         </is>
       </c>
       <c r="D8" s="5" t="n">
@@ -5583,7 +5609,7 @@
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
@@ -5592,7 +5618,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT - Collagen Real Ampoule Mask [27ml] / Ампульная маска с коллагеном</t>
+          <t>JIGOTT - Honey Real Ampoule Mask [27ml] / Ампульная маска с экстрактом меда</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -5627,7 +5653,7 @@
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
@@ -5636,7 +5662,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT - Cucumber Real Ampoule Mask [27ml] / Тканевая маска с экстрактом огурца</t>
+          <t>JIGOTT - Black Snail Real Ampoule Mask [27ml] / Ампульная маска с экстрактом слизи черной улитки</t>
         </is>
       </c>
       <c r="D10" s="5" t="n">
@@ -5671,7 +5697,7 @@
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
@@ -5680,7 +5706,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT - Green Tea Real Ampoule Mask [27ml] / Ампульная маска с экстрактом зеленого чая</t>
+          <t>JIGOTT - Lotus Real Ampoule Mask [27ml] / Ампульная маска с экстрактом лотоса</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -5715,7 +5741,7 @@
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
@@ -5724,7 +5750,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT - Honey Real Ampoule Mask [27ml] / Ампульная маска с экстрактом меда</t>
+          <t>JIGOTT - Placenta Real Ampoule Mask [27ml] / Ампульная маска с плацентой</t>
         </is>
       </c>
       <c r="D12" s="5" t="n">
@@ -5759,7 +5785,7 @@
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
@@ -5768,7 +5794,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT - Lotus Real Ampoule Mask [27ml] / Ампульная маска с экстрактом лотоса</t>
+          <t>JIGOTT - Pomegranate Real Ampoule Mask [27ml] / Ампульная маска с экстрактом граната</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
@@ -5803,7 +5829,7 @@
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
@@ -5812,7 +5838,7 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT - Pearl Real Ampoule Mask [27ml] / ампульная маска для лица с жемчугом</t>
+          <t>JIGOTT - Potato Real Ampoule Mask [27ml] / Ампульная маска с экстрактом картофеля</t>
         </is>
       </c>
       <c r="D14" s="5" t="n">
@@ -5847,7 +5873,7 @@
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
@@ -5856,7 +5882,7 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT - Placenta Real Ampoule Mask [27ml] / Ампульная маска с плацентой</t>
+          <t>JIGOTT - Red Ginseng Real Ampoule Mask [27ml] / Ампульная маска с красным женьшенем</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
@@ -5891,7 +5917,7 @@
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
@@ -5900,7 +5926,7 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT - Pomegranate Real Ampoule Mask [27ml] / Ампульная маска с экстрактом граната</t>
+          <t>JIGOTT - Vitamin Real Ampoule Mask [27ml] / Ампульная маска с витаминами</t>
         </is>
       </c>
       <c r="D16" s="5" t="n">
@@ -5935,7 +5961,7 @@
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
@@ -5944,7 +5970,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT - Potato Real Ampoule Mask [27ml] / Ампульная маска с экстрактом картофеля</t>
+          <t>JIGOTT - Pearl Real Ampoule Mask [27ml] / ампульная маска для лица с жемчугом</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
@@ -5979,7 +6005,7 @@
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
@@ -5988,7 +6014,7 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT - Red Ginseng Real Ampoule Mask [27ml] / Ампульная маска с красным женьшенем</t>
+          <t>JIGOTT - Aloe Real Ampoule Mask [27ml] / Ампульная маска с экстрактом алое</t>
         </is>
       </c>
       <c r="D18" s="5" t="n">
@@ -6023,7 +6049,7 @@
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
@@ -6032,23 +6058,23 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT - Vitamin Real Ampoule Mask [27ml] / Ампульная маска с витаминами</t>
+          <t>JIGOTT - Daily Real Cica Toner [300ml] / Тонер для лица с центеллой азиатской</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1190</v>
+        <v>800</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>23</v>
+        <v>265</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>159</v>
+        <v>2120</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>10</v>
+        <v>131</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>11</v>
+        <v>151</v>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
@@ -6056,18 +6082,18 @@
         </is>
       </c>
       <c r="J19" s="5" t="n">
-        <v>-11</v>
+        <v>-114</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-50.1</v>
+        <v>-43</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>-13555</v>
+        <v>-91363</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
@@ -6076,23 +6102,23 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT - Black Snail Real Ampoule Mask [27ml] / Ампульная маска с экстрактом слизи черной улитки</t>
+          <t>JIGOTT - Ultimate Real Collagen Toner [300ml] / тонер с коллагеном антивозрастной</t>
         </is>
       </c>
       <c r="D20" s="5" t="n">
-        <v>1190</v>
+        <v>800</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>23</v>
+        <v>265</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>159</v>
+        <v>2120</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>10</v>
+        <v>131</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>11</v>
+        <v>151</v>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
@@ -6100,18 +6126,18 @@
         </is>
       </c>
       <c r="J20" s="5" t="n">
-        <v>-11</v>
+        <v>-114</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-50.1</v>
+        <v>-43</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>-13555</v>
+        <v>-91363</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
@@ -6120,23 +6146,23 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT - Aloe Real Ampoule Mask [27ml] / Ампульная маска с экстрактом алое</t>
+          <t>JIGOTT - Moisture Real Aloe Vera Toner [300ml] / Тонер для лица увлажняющий с экстрактом алоэ</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1190</v>
+        <v>100</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>23</v>
+        <v>265</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>159</v>
+        <v>2120</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>10</v>
+        <v>131</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>11</v>
+        <v>151</v>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
@@ -6144,58 +6170,32 @@
         </is>
       </c>
       <c r="J21" s="5" t="n">
-        <v>-11</v>
+        <v>-114</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-50.1</v>
+        <v>-43</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>-13555</v>
+        <v>-11420</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>JIGOTT</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>JIGOTT - Daily Real Cica Toner [300ml] / Тонер для лица с центеллой азиатской</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="n">
-        <v>800</v>
-      </c>
-      <c r="E22" s="5" t="n">
-        <v>265</v>
-      </c>
-      <c r="F22" s="5" t="n">
-        <v>2120</v>
-      </c>
-      <c r="G22" s="5" t="n">
-        <v>131</v>
-      </c>
-      <c r="H22" s="5" t="n">
-        <v>151</v>
-      </c>
-      <c r="I22" s="4" t="inlineStr">
-        <is>
-          <t>FINESKIN (ответ)</t>
-        </is>
-      </c>
-      <c r="J22" s="5" t="n">
-        <v>-114</v>
-      </c>
-      <c r="K22" s="4" t="n">
-        <v>-43</v>
-      </c>
-      <c r="L22" s="5" t="n">
-        <v>-91363</v>
-      </c>
+      <c r="A22" s="2" t="n"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>FARMSTAY</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="n"/>
+      <c r="D22" s="3" t="n"/>
+      <c r="E22" s="3" t="n"/>
+      <c r="F22" s="3" t="n"/>
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
+      <c r="I22" s="2" t="n"/>
+      <c r="J22" s="3" t="n"/>
+      <c r="K22" s="2" t="n"/>
+      <c r="L22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -6203,42 +6203,42 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>FARMSTAY</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT - Ultimate Real Collagen Toner [300ml] / тонер с коллагеном антивозрастной</t>
+          <t>FARMSTAY - Collagen Water Full Moist Cream [100g] / Увлажняющий крем с коллагеном</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>265</v>
+        <v>484</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>2120</v>
+        <v>4390</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>131</v>
+        <v>272</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>151</v>
+        <v>313</v>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>FINESKIN (ответ)</t>
+          <t>Классик</t>
         </is>
       </c>
       <c r="J23" s="5" t="n">
-        <v>-114</v>
+        <v>-171</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-43</v>
+        <v>-35.4</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>-91363</v>
+        <v>-34283</v>
       </c>
     </row>
     <row r="24">
@@ -6247,65 +6247,91 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>FARMSTAY</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT - Moisture Real Aloe Vera Toner [300ml] / Тонер для лица увлажняющий с экстрактом алоэ</t>
+          <t>FARMSTAY - Collagen Water Full Shampoo &amp; Conditioner [530ml] / Шампунь-кондиционер 2в1 с коллагеном</t>
         </is>
       </c>
       <c r="D24" s="5" t="n">
-        <v>100</v>
+        <v>3493</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>265</v>
+        <v>397</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>2120</v>
+        <v>3660</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>131</v>
+        <v>227</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>151</v>
+        <v>261</v>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>FINESKIN (ответ)</t>
+          <t>Классик</t>
         </is>
       </c>
       <c r="J24" s="5" t="n">
-        <v>-114</v>
+        <v>-136</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-43</v>
+        <v>-34.2</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>-11420</v>
+        <v>-474217</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n"/>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="A25" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>FARMSTAY</t>
         </is>
       </c>
-      <c r="C25" s="2" t="n"/>
-      <c r="D25" s="3" t="n"/>
-      <c r="E25" s="3" t="n"/>
-      <c r="F25" s="3" t="n"/>
-      <c r="G25" s="3" t="n"/>
-      <c r="H25" s="3" t="n"/>
-      <c r="I25" s="2" t="n"/>
-      <c r="J25" s="3" t="n"/>
-      <c r="K25" s="2" t="n"/>
-      <c r="L25" s="3" t="n"/>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>FARMSTAY - Black Garlic Nourishing Shampoo [530ml] / Шампунь-кондиционер 2в1 с экстрактом черного чеснока</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>3239</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>397</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>3660</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>227</v>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>261</v>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>Классик</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="n">
+        <v>-136</v>
+      </c>
+      <c r="K25" s="4" t="n">
+        <v>-34.2</v>
+      </c>
+      <c r="L25" s="5" t="n">
+        <v>-439733</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
@@ -6314,23 +6340,23 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>FARMSTAY - Collagen Water Full Moist Cream [100g] / Увлажняющий крем с коллагеном</t>
+          <t>FARMSTAY - Argan Oil Complete Volume Up Shampoo &amp; Conditioner [530ml] / Шампунь-кондиционер с аргановым маслом</t>
         </is>
       </c>
       <c r="D26" s="5" t="n">
-        <v>200</v>
+        <v>2435</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>484</v>
+        <v>401</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>4390</v>
+        <v>3730</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>272</v>
+        <v>231</v>
       </c>
       <c r="H26" s="5" t="n">
-        <v>313</v>
+        <v>266</v>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
@@ -6338,58 +6364,32 @@
         </is>
       </c>
       <c r="J26" s="5" t="n">
-        <v>-171</v>
+        <v>-135</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-35.4</v>
+        <v>-33.6</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>-34283</v>
+        <v>-328265</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>FARMSTAY</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>FARMSTAY - Collagen Water Full Shampoo &amp; Conditioner [530ml] / Шампунь-кондиционер 2в1 с коллагеном</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="n">
-        <v>3493</v>
-      </c>
-      <c r="E27" s="5" t="n">
-        <v>397</v>
-      </c>
-      <c r="F27" s="5" t="n">
-        <v>3660</v>
-      </c>
-      <c r="G27" s="5" t="n">
-        <v>227</v>
-      </c>
-      <c r="H27" s="5" t="n">
-        <v>261</v>
-      </c>
-      <c r="I27" s="4" t="inlineStr">
-        <is>
-          <t>Классик</t>
-        </is>
-      </c>
-      <c r="J27" s="5" t="n">
-        <v>-136</v>
-      </c>
-      <c r="K27" s="4" t="n">
-        <v>-34.2</v>
-      </c>
-      <c r="L27" s="5" t="n">
-        <v>-474217</v>
-      </c>
+      <c r="A27" s="2" t="n"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>SOME BY MI</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n"/>
+      <c r="D27" s="3" t="n"/>
+      <c r="E27" s="3" t="n"/>
+      <c r="F27" s="3" t="n"/>
+      <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
+      <c r="I27" s="2" t="n"/>
+      <c r="J27" s="3" t="n"/>
+      <c r="K27" s="2" t="n"/>
+      <c r="L27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
@@ -6397,291 +6397,291 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>FARMSTAY</t>
+          <t>SOME BY MI</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>FARMSTAY - Black Garlic Nourishing Shampoo [530ml] / Шампунь-кондиционер 2в1 с экстрактом черного чеснока</t>
+          <t>SOME BY MI - AHA-BHA-PHA 30 Days Miracle Cream [60g] / Крем для лица</t>
         </is>
       </c>
       <c r="D28" s="5" t="n">
-        <v>3239</v>
+        <v>55</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>397</v>
+        <v>1057</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>3660</v>
+        <v>10685</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>227</v>
+        <v>662</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>261</v>
+        <v>762</v>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>Классик</t>
+          <t>FINESKIN (ответ)</t>
         </is>
       </c>
       <c r="J28" s="5" t="n">
-        <v>-136</v>
+        <v>-295</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-34.2</v>
+        <v>-27.9</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>-439733</v>
+        <v>-16245</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="n">
+      <c r="A29" s="2" t="n"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>ROUND LAB</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n"/>
+      <c r="D29" s="3" t="n"/>
+      <c r="E29" s="3" t="n"/>
+      <c r="F29" s="3" t="n"/>
+      <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
+      <c r="I29" s="2" t="n"/>
+      <c r="J29" s="3" t="n"/>
+      <c r="K29" s="2" t="n"/>
+      <c r="L29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>FARMSTAY</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>FARMSTAY - Argan Oil Complete Volume Up Shampoo &amp; Conditioner [530ml] / Шампунь-кондиционер с аргановым маслом</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="n">
-        <v>2435</v>
-      </c>
-      <c r="E29" s="5" t="n">
-        <v>401</v>
-      </c>
-      <c r="F29" s="5" t="n">
-        <v>3730</v>
-      </c>
-      <c r="G29" s="5" t="n">
-        <v>231</v>
-      </c>
-      <c r="H29" s="5" t="n">
-        <v>266</v>
-      </c>
-      <c r="I29" s="4" t="inlineStr">
-        <is>
-          <t>Классик</t>
-        </is>
-      </c>
-      <c r="J29" s="5" t="n">
-        <v>-135</v>
-      </c>
-      <c r="K29" s="4" t="n">
-        <v>-33.6</v>
-      </c>
-      <c r="L29" s="5" t="n">
-        <v>-328265</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="n"/>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>ROUND LAB</t>
         </is>
       </c>
-      <c r="C30" s="2" t="n"/>
-      <c r="D30" s="3" t="n"/>
-      <c r="E30" s="3" t="n"/>
-      <c r="F30" s="3" t="n"/>
-      <c r="G30" s="3" t="n"/>
-      <c r="H30" s="3" t="n"/>
-      <c r="I30" s="2" t="n"/>
-      <c r="J30" s="3" t="n"/>
-      <c r="K30" s="2" t="n"/>
-      <c r="L30" s="3" t="n"/>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>ROUND LAB PINE CALMING CICA AMPOULE_30ml - Сыворотка для жирной кожи лица увлажняющая с центеллой</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>820</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>8293</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>514</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>591</v>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>G&amp;E Global</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="n">
+        <v>-228</v>
+      </c>
+      <c r="K30" s="4" t="n">
+        <v>-27.9</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>-7310</v>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="n">
+      <c r="A31" s="2" t="n"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="n"/>
+      <c r="D31" s="3" t="n"/>
+      <c r="E31" s="3" t="n"/>
+      <c r="F31" s="3" t="n"/>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
+      <c r="I31" s="2" t="n"/>
+      <c r="J31" s="3" t="n"/>
+      <c r="K31" s="2" t="n"/>
+      <c r="L31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>ROUND LAB</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>ROUND LAB PINE CALMING CICA AMPOULE_30ml - Сыворотка для жирной кожи лица увлажняющая с центеллой</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="n">
-        <v>32</v>
-      </c>
-      <c r="E31" s="5" t="n">
-        <v>820</v>
-      </c>
-      <c r="F31" s="5" t="n">
-        <v>8293</v>
-      </c>
-      <c r="G31" s="5" t="n">
-        <v>514</v>
-      </c>
-      <c r="H31" s="5" t="n">
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>PETITFEE - Aura Quartz Hydrogel Eye Patch [60ea]</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>89</v>
+      </c>
+      <c r="E32" s="5" t="n">
         <v>591</v>
       </c>
-      <c r="I31" s="4" t="inlineStr">
-        <is>
-          <t>G&amp;E Global</t>
-        </is>
-      </c>
-      <c r="J31" s="5" t="n">
-        <v>-228</v>
-      </c>
-      <c r="K31" s="4" t="n">
-        <v>-27.9</v>
-      </c>
-      <c r="L31" s="5" t="n">
-        <v>-7310</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="n"/>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>SOME BY MI</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="n"/>
-      <c r="D32" s="3" t="n"/>
-      <c r="E32" s="3" t="n"/>
-      <c r="F32" s="3" t="n"/>
-      <c r="G32" s="3" t="n"/>
-      <c r="H32" s="3" t="n"/>
-      <c r="I32" s="2" t="n"/>
-      <c r="J32" s="3" t="n"/>
-      <c r="K32" s="2" t="n"/>
-      <c r="L32" s="3" t="n"/>
+      <c r="F32" s="5" t="n">
+        <v>6190</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>384</v>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>441</v>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>J2K (ответ)</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="n">
+        <v>-150</v>
+      </c>
+      <c r="K32" s="4" t="n">
+        <v>-25.4</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>-13345</v>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="n">
+      <c r="A33" s="2" t="n"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>JIGOTT</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="n"/>
+      <c r="D33" s="3" t="n"/>
+      <c r="E33" s="3" t="n"/>
+      <c r="F33" s="3" t="n"/>
+      <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
+      <c r="I33" s="2" t="n"/>
+      <c r="J33" s="3" t="n"/>
+      <c r="K33" s="2" t="n"/>
+      <c r="L33" s="3" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>SOME BY MI</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>SOME BY MI - AHA-BHA-PHA 30 Days Miracle Cream [60g] / Крем для лица</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="n">
-        <v>55</v>
-      </c>
-      <c r="E33" s="5" t="n">
-        <v>1057</v>
-      </c>
-      <c r="F33" s="5" t="n">
-        <v>10685</v>
-      </c>
-      <c r="G33" s="5" t="n">
-        <v>662</v>
-      </c>
-      <c r="H33" s="5" t="n">
-        <v>762</v>
-      </c>
-      <c r="I33" s="4" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>JIGOTT</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>JIGOTT - Snail Lifting Cream [70ml] / Крем для лица увлажняющий антивозрастной</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>7463</v>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>202</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>2120</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>131</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>151</v>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
         <is>
           <t>FINESKIN (ответ)</t>
         </is>
       </c>
-      <c r="J33" s="5" t="n">
-        <v>-295</v>
-      </c>
-      <c r="K33" s="4" t="n">
-        <v>-27.9</v>
-      </c>
-      <c r="L33" s="5" t="n">
-        <v>-16245</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="n"/>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>PETITFEE</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="n"/>
-      <c r="D34" s="3" t="n"/>
-      <c r="E34" s="3" t="n"/>
-      <c r="F34" s="3" t="n"/>
-      <c r="G34" s="3" t="n"/>
-      <c r="H34" s="3" t="n"/>
-      <c r="I34" s="2" t="n"/>
-      <c r="J34" s="3" t="n"/>
-      <c r="K34" s="2" t="n"/>
-      <c r="L34" s="3" t="n"/>
+      <c r="J34" s="5" t="n">
+        <v>-51</v>
+      </c>
+      <c r="K34" s="4" t="n">
+        <v>-25.3</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>-381464</v>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="n">
+      <c r="A35" s="2" t="n"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>JMSOLUTION</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="n"/>
+      <c r="D35" s="3" t="n"/>
+      <c r="E35" s="3" t="n"/>
+      <c r="F35" s="3" t="n"/>
+      <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
+      <c r="I35" s="2" t="n"/>
+      <c r="J35" s="3" t="n"/>
+      <c r="K35" s="2" t="n"/>
+      <c r="L35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>PETITFEE</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>PETITFEE - Aura Quartz Hydrogel Eye Patch [60ea]</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="n">
-        <v>89</v>
-      </c>
-      <c r="E35" s="5" t="n">
-        <v>591</v>
-      </c>
-      <c r="F35" s="5" t="n">
-        <v>6190</v>
-      </c>
-      <c r="G35" s="5" t="n">
-        <v>384</v>
-      </c>
-      <c r="H35" s="5" t="n">
-        <v>441</v>
-      </c>
-      <c r="I35" s="4" t="inlineStr">
-        <is>
-          <t>J2K (ответ)</t>
-        </is>
-      </c>
-      <c r="J35" s="5" t="n">
-        <v>-150</v>
-      </c>
-      <c r="K35" s="4" t="n">
-        <v>-25.4</v>
-      </c>
-      <c r="L35" s="5" t="n">
-        <v>-13345</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="n"/>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>JIGOTT</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="n"/>
-      <c r="D36" s="3" t="n"/>
-      <c r="E36" s="3" t="n"/>
-      <c r="F36" s="3" t="n"/>
-      <c r="G36" s="3" t="n"/>
-      <c r="H36" s="3" t="n"/>
-      <c r="I36" s="2" t="n"/>
-      <c r="J36" s="3" t="n"/>
-      <c r="K36" s="2" t="n"/>
-      <c r="L36" s="3" t="n"/>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>JMSOLUTION</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>JMSOLUTION - Active Birds Nest Moisture Mask [30ml*10ea] / Ультратонкая тканевая маска с ласточкиным гнездом</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>110</v>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>342</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>3604</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>223</v>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>257</v>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>FINESKIN (ответ)</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="n">
+        <v>-85</v>
+      </c>
+      <c r="K36" s="4" t="n">
+        <v>-24.9</v>
+      </c>
+      <c r="L36" s="5" t="n">
+        <v>-9384</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
@@ -6689,28 +6689,28 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>JMSOLUTION</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT - Snail Lifting Cream [70ml] / Крем для лица увлажняющий антивозрастной</t>
+          <t>JMSOLUTION - Active Jellyfish Vital Mask [30ml*10ea] / Ультратонкая тканевая маска с экстрактом медузы</t>
         </is>
       </c>
       <c r="D37" s="5" t="n">
-        <v>7463</v>
+        <v>110</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>202</v>
+        <v>342</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>2120</v>
+        <v>3604</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>131</v>
+        <v>223</v>
       </c>
       <c r="H37" s="5" t="n">
-        <v>151</v>
+        <v>257</v>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
@@ -6718,36 +6718,62 @@
         </is>
       </c>
       <c r="J37" s="5" t="n">
-        <v>-51</v>
+        <v>-85</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>-25.3</v>
+        <v>-24.9</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>-381464</v>
+        <v>-9384</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n"/>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="A38" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>JMSOLUTION</t>
         </is>
       </c>
-      <c r="C38" s="2" t="n"/>
-      <c r="D38" s="3" t="n"/>
-      <c r="E38" s="3" t="n"/>
-      <c r="F38" s="3" t="n"/>
-      <c r="G38" s="3" t="n"/>
-      <c r="H38" s="3" t="n"/>
-      <c r="I38" s="2" t="n"/>
-      <c r="J38" s="3" t="n"/>
-      <c r="K38" s="2" t="n"/>
-      <c r="L38" s="3" t="n"/>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>JMSOLUTION ACTIVE BLACK CAVIAR MASK [30ml*10ea] / Ультратонкая тканевая маска с черной икрой</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>110</v>
+      </c>
+      <c r="E38" s="5" t="n">
+        <v>342</v>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>3604</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>223</v>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>257</v>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>FINESKIN (ответ)</t>
+        </is>
+      </c>
+      <c r="J38" s="5" t="n">
+        <v>-85</v>
+      </c>
+      <c r="K38" s="4" t="n">
+        <v>-24.9</v>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>-9384</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
@@ -6791,7 +6817,7 @@
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
@@ -6834,48 +6860,22 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>JMSOLUTION</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>JMSOLUTION - Active Birds Nest Moisture Mask [30ml*10ea] / Ультратонкая тканевая маска с ласточкиным гнездом</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="n">
-        <v>110</v>
-      </c>
-      <c r="E41" s="5" t="n">
-        <v>342</v>
-      </c>
-      <c r="F41" s="5" t="n">
-        <v>3604</v>
-      </c>
-      <c r="G41" s="5" t="n">
-        <v>223</v>
-      </c>
-      <c r="H41" s="5" t="n">
-        <v>257</v>
-      </c>
-      <c r="I41" s="4" t="inlineStr">
-        <is>
-          <t>FINESKIN (ответ)</t>
-        </is>
-      </c>
-      <c r="J41" s="5" t="n">
-        <v>-85</v>
-      </c>
-      <c r="K41" s="4" t="n">
-        <v>-24.9</v>
-      </c>
-      <c r="L41" s="5" t="n">
-        <v>-9384</v>
-      </c>
+      <c r="A41" s="2" t="n"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>ROUND LAB</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="n"/>
+      <c r="D41" s="3" t="n"/>
+      <c r="E41" s="3" t="n"/>
+      <c r="F41" s="3" t="n"/>
+      <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
+      <c r="I41" s="2" t="n"/>
+      <c r="J41" s="3" t="n"/>
+      <c r="K41" s="2" t="n"/>
+      <c r="L41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
@@ -6883,291 +6883,291 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>JMSOLUTION</t>
+          <t>ROUND LAB</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>JMSOLUTION - Active Jellyfish Vital Mask [30ml*10ea] / Ультратонкая тканевая маска с экстрактом медузы</t>
+          <t>ROUND LAB BIRCH JUICE MOISTURIZING CREAM_80ml -Увлажняющий крем с березовым соком</t>
         </is>
       </c>
       <c r="D42" s="5" t="n">
-        <v>110</v>
+        <v>259</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>342</v>
+        <v>1093</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>3604</v>
+        <v>11702</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>223</v>
+        <v>726</v>
       </c>
       <c r="H42" s="5" t="n">
-        <v>257</v>
+        <v>834</v>
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
+          <t>G&amp;E Global</t>
+        </is>
+      </c>
+      <c r="J42" s="5" t="n">
+        <v>-259</v>
+      </c>
+      <c r="K42" s="4" t="n">
+        <v>-23.7</v>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>-66979</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>HEIMISH</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="n"/>
+      <c r="D43" s="3" t="n"/>
+      <c r="E43" s="3" t="n"/>
+      <c r="F43" s="3" t="n"/>
+      <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
+      <c r="I43" s="2" t="n"/>
+      <c r="J43" s="3" t="n"/>
+      <c r="K43" s="2" t="n"/>
+      <c r="L43" s="3" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>HEIMISH</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>HEIMISH - Artless Glow Base SPF50+ PA+++(Renew) [40ml] / База под макияж SPF50+ PA+++</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="n">
+        <v>941</v>
+      </c>
+      <c r="E44" s="5" t="n">
+        <v>770</v>
+      </c>
+      <c r="F44" s="5" t="n">
+        <v>8565</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>531</v>
+      </c>
+      <c r="H44" s="5" t="n">
+        <v>611</v>
+      </c>
+      <c r="I44" s="4" t="inlineStr">
+        <is>
+          <t>Классик</t>
+        </is>
+      </c>
+      <c r="J44" s="5" t="n">
+        <v>-160</v>
+      </c>
+      <c r="K44" s="4" t="n">
+        <v>-20.7</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>-150368</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>JIGOTT</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="n"/>
+      <c r="D45" s="3" t="n"/>
+      <c r="E45" s="3" t="n"/>
+      <c r="F45" s="3" t="n"/>
+      <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
+      <c r="I45" s="2" t="n"/>
+      <c r="J45" s="3" t="n"/>
+      <c r="K45" s="2" t="n"/>
+      <c r="L45" s="3" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>JIGOTT</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>JIGOTT - Snail Reparing Cream [100ml] / Крем для лица увлажняющий антивозрастной с муцином улитки</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="n">
+        <v>500</v>
+      </c>
+      <c r="E46" s="5" t="n">
+        <v>186</v>
+      </c>
+      <c r="F46" s="5" t="n">
+        <v>2120</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>131</v>
+      </c>
+      <c r="H46" s="5" t="n">
+        <v>151</v>
+      </c>
+      <c r="I46" s="4" t="inlineStr">
+        <is>
           <t>FINESKIN (ответ)</t>
         </is>
       </c>
-      <c r="J42" s="5" t="n">
-        <v>-85</v>
-      </c>
-      <c r="K42" s="4" t="n">
-        <v>-24.9</v>
-      </c>
-      <c r="L42" s="5" t="n">
-        <v>-9384</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>JMSOLUTION</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>JMSOLUTION ACTIVE BLACK CAVIAR MASK [30ml*10ea] / Ультратонкая тканевая маска с черной икрой</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="n">
-        <v>110</v>
-      </c>
-      <c r="E43" s="5" t="n">
-        <v>342</v>
-      </c>
-      <c r="F43" s="5" t="n">
-        <v>3604</v>
-      </c>
-      <c r="G43" s="5" t="n">
-        <v>223</v>
-      </c>
-      <c r="H43" s="5" t="n">
-        <v>257</v>
-      </c>
-      <c r="I43" s="4" t="inlineStr">
+      <c r="J46" s="5" t="n">
+        <v>-35</v>
+      </c>
+      <c r="K46" s="4" t="n">
+        <v>-18.7</v>
+      </c>
+      <c r="L46" s="5" t="n">
+        <v>-17352</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>MANYO</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="n"/>
+      <c r="D47" s="3" t="n"/>
+      <c r="E47" s="3" t="n"/>
+      <c r="F47" s="3" t="n"/>
+      <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
+      <c r="I47" s="2" t="n"/>
+      <c r="J47" s="3" t="n"/>
+      <c r="K47" s="2" t="n"/>
+      <c r="L47" s="3" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>MANYO</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>MANYO - Pure Cleansing Oil [200ml] / Гидрофильное масло для глубокого очищения</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="E48" s="5" t="n">
+        <v>853</v>
+      </c>
+      <c r="F48" s="5" t="n">
+        <v>9750</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>604</v>
+      </c>
+      <c r="H48" s="5" t="n">
+        <v>695</v>
+      </c>
+      <c r="I48" s="4" t="inlineStr">
+        <is>
+          <t>Классик</t>
+        </is>
+      </c>
+      <c r="J48" s="5" t="n">
+        <v>-158</v>
+      </c>
+      <c r="K48" s="4" t="n">
+        <v>-18.5</v>
+      </c>
+      <c r="L48" s="5" t="n">
+        <v>-12626</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="n"/>
+      <c r="D49" s="3" t="n"/>
+      <c r="E49" s="3" t="n"/>
+      <c r="F49" s="3" t="n"/>
+      <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
+      <c r="I49" s="2" t="n"/>
+      <c r="J49" s="3" t="n"/>
+      <c r="K49" s="2" t="n"/>
+      <c r="L49" s="3" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>PETITFEE - Gold Hydrogel Eye Patch [1 Pairs] / гидрогелевые патчи для глаз с золотом 1 пара</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="n">
+        <v>428</v>
+      </c>
+      <c r="E50" s="5" t="n">
+        <v>71</v>
+      </c>
+      <c r="F50" s="5" t="n">
+        <v>819</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="H50" s="5" t="n">
+        <v>58</v>
+      </c>
+      <c r="I50" s="4" t="inlineStr">
         <is>
           <t>FINESKIN (ответ)</t>
         </is>
       </c>
-      <c r="J43" s="5" t="n">
-        <v>-85</v>
-      </c>
-      <c r="K43" s="4" t="n">
-        <v>-24.9</v>
-      </c>
-      <c r="L43" s="5" t="n">
-        <v>-9384</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="n"/>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>ROUND LAB</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="n"/>
-      <c r="D44" s="3" t="n"/>
-      <c r="E44" s="3" t="n"/>
-      <c r="F44" s="3" t="n"/>
-      <c r="G44" s="3" t="n"/>
-      <c r="H44" s="3" t="n"/>
-      <c r="I44" s="2" t="n"/>
-      <c r="J44" s="3" t="n"/>
-      <c r="K44" s="2" t="n"/>
-      <c r="L44" s="3" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>ROUND LAB</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="inlineStr">
-        <is>
-          <t>ROUND LAB BIRCH JUICE MOISTURIZING CREAM_80ml -Увлажняющий крем с березовым соком</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="n">
-        <v>259</v>
-      </c>
-      <c r="E45" s="5" t="n">
-        <v>1093</v>
-      </c>
-      <c r="F45" s="5" t="n">
-        <v>11702</v>
-      </c>
-      <c r="G45" s="5" t="n">
-        <v>726</v>
-      </c>
-      <c r="H45" s="5" t="n">
-        <v>834</v>
-      </c>
-      <c r="I45" s="4" t="inlineStr">
-        <is>
-          <t>G&amp;E Global</t>
-        </is>
-      </c>
-      <c r="J45" s="5" t="n">
-        <v>-259</v>
-      </c>
-      <c r="K45" s="4" t="n">
-        <v>-23.7</v>
-      </c>
-      <c r="L45" s="5" t="n">
-        <v>-66979</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="n"/>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>HEIMISH</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="n"/>
-      <c r="D46" s="3" t="n"/>
-      <c r="E46" s="3" t="n"/>
-      <c r="F46" s="3" t="n"/>
-      <c r="G46" s="3" t="n"/>
-      <c r="H46" s="3" t="n"/>
-      <c r="I46" s="2" t="n"/>
-      <c r="J46" s="3" t="n"/>
-      <c r="K46" s="2" t="n"/>
-      <c r="L46" s="3" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="4" t="n">
-        <v>36</v>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>HEIMISH</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="inlineStr">
-        <is>
-          <t>HEIMISH - Artless Glow Base SPF50+ PA+++(Renew) [40ml] / База под макияж SPF50+ PA+++</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="n">
-        <v>941</v>
-      </c>
-      <c r="E47" s="5" t="n">
-        <v>770</v>
-      </c>
-      <c r="F47" s="5" t="n">
-        <v>8565</v>
-      </c>
-      <c r="G47" s="5" t="n">
-        <v>531</v>
-      </c>
-      <c r="H47" s="5" t="n">
-        <v>611</v>
-      </c>
-      <c r="I47" s="4" t="inlineStr">
-        <is>
-          <t>Классик</t>
-        </is>
-      </c>
-      <c r="J47" s="5" t="n">
-        <v>-160</v>
-      </c>
-      <c r="K47" s="4" t="n">
-        <v>-20.7</v>
-      </c>
-      <c r="L47" s="5" t="n">
-        <v>-150368</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="n"/>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>JIGOTT</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="n"/>
-      <c r="D48" s="3" t="n"/>
-      <c r="E48" s="3" t="n"/>
-      <c r="F48" s="3" t="n"/>
-      <c r="G48" s="3" t="n"/>
-      <c r="H48" s="3" t="n"/>
-      <c r="I48" s="2" t="n"/>
-      <c r="J48" s="3" t="n"/>
-      <c r="K48" s="2" t="n"/>
-      <c r="L48" s="3" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="4" t="n">
-        <v>37</v>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>JIGOTT</t>
-        </is>
-      </c>
-      <c r="C49" s="4" t="inlineStr">
-        <is>
-          <t>JIGOTT - Snail Reparing Cream [100ml] / Крем для лица увлажняющий антивозрастной с муцином улитки</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="n">
-        <v>500</v>
-      </c>
-      <c r="E49" s="5" t="n">
-        <v>186</v>
-      </c>
-      <c r="F49" s="5" t="n">
-        <v>2120</v>
-      </c>
-      <c r="G49" s="5" t="n">
-        <v>131</v>
-      </c>
-      <c r="H49" s="5" t="n">
-        <v>151</v>
-      </c>
-      <c r="I49" s="4" t="inlineStr">
-        <is>
-          <t>FINESKIN (ответ)</t>
-        </is>
-      </c>
-      <c r="J49" s="5" t="n">
-        <v>-35</v>
-      </c>
-      <c r="K49" s="4" t="n">
-        <v>-18.7</v>
-      </c>
-      <c r="L49" s="5" t="n">
-        <v>-17352</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="n"/>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>MANYO</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="n"/>
-      <c r="D50" s="3" t="n"/>
-      <c r="E50" s="3" t="n"/>
-      <c r="F50" s="3" t="n"/>
-      <c r="G50" s="3" t="n"/>
-      <c r="H50" s="3" t="n"/>
-      <c r="I50" s="2" t="n"/>
-      <c r="J50" s="3" t="n"/>
-      <c r="K50" s="2" t="n"/>
-      <c r="L50" s="3" t="n"/>
+      <c r="J50" s="5" t="n">
+        <v>-13</v>
+      </c>
+      <c r="K50" s="4" t="n">
+        <v>-18</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>-5498</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="n">
@@ -7175,49 +7175,49 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>MANYO</t>
+          <t>PETITFEE</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>MANYO - Pure Cleansing Oil [200ml] / Гидрофильное масло для глубокого очищения</t>
+          <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Eye Patch [1 pairs]/ Гидрогелевые патчи для глаз с черным жемчугом и золотом 1 пара</t>
         </is>
       </c>
       <c r="D51" s="5" t="n">
-        <v>80</v>
+        <v>320</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>853</v>
+        <v>71</v>
       </c>
       <c r="F51" s="5" t="n">
-        <v>9750</v>
+        <v>819</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>604</v>
+        <v>51</v>
       </c>
       <c r="H51" s="5" t="n">
-        <v>695</v>
+        <v>58</v>
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>Классик</t>
+          <t>FINESKIN (ответ)</t>
         </is>
       </c>
       <c r="J51" s="5" t="n">
-        <v>-158</v>
+        <v>-13</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>-18.5</v>
+        <v>-18</v>
       </c>
       <c r="L51" s="5" t="n">
-        <v>-12626</v>
+        <v>-4110</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n"/>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>ROUND LAB</t>
         </is>
       </c>
       <c r="C52" s="2" t="n"/>
@@ -7237,167 +7237,167 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>ROUND LAB</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Eye Patch [1 pairs]/ Гидрогелевые патчи для глаз с черным жемчугом и золотом 1 пара</t>
+          <t>ROUND LAB MUGWORT CALMING CLEANSER_150ml - Очищающая пенка для умывания лица от прыщей и акне</t>
         </is>
       </c>
       <c r="D53" s="5" t="n">
-        <v>320</v>
+        <v>1422</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>71</v>
+        <v>512</v>
       </c>
       <c r="F53" s="5" t="n">
-        <v>819</v>
+        <v>5963</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>51</v>
+        <v>370</v>
       </c>
       <c r="H53" s="5" t="n">
-        <v>58</v>
+        <v>425</v>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
+          <t>G&amp;E Global</t>
+        </is>
+      </c>
+      <c r="J53" s="5" t="n">
+        <v>-87</v>
+      </c>
+      <c r="K53" s="4" t="n">
+        <v>-17</v>
+      </c>
+      <c r="L53" s="5" t="n">
+        <v>-123939</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>DEOPROCE</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="n"/>
+      <c r="D54" s="3" t="n"/>
+      <c r="E54" s="3" t="n"/>
+      <c r="F54" s="3" t="n"/>
+      <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
+      <c r="I54" s="2" t="n"/>
+      <c r="J54" s="3" t="n"/>
+      <c r="K54" s="2" t="n"/>
+      <c r="L54" s="3" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>DEOPROCE</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>DEOPROCE SHAMPOO - BLACK GARLIC INTENSME ENERGY [200ml]/ Шампунь с черным чесноком против выпадения волос</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="n">
+        <v>240</v>
+      </c>
+      <c r="E55" s="5" t="n">
+        <v>151</v>
+      </c>
+      <c r="F55" s="5" t="n">
+        <v>1781</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>110</v>
+      </c>
+      <c r="H55" s="5" t="n">
+        <v>127</v>
+      </c>
+      <c r="I55" s="4" t="inlineStr">
+        <is>
           <t>FINESKIN (ответ)</t>
         </is>
       </c>
-      <c r="J53" s="5" t="n">
-        <v>-13</v>
-      </c>
-      <c r="K53" s="4" t="n">
-        <v>-18</v>
-      </c>
-      <c r="L53" s="5" t="n">
-        <v>-4110</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t>PETITFEE</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>PETITFEE - Gold Hydrogel Eye Patch [1 Pairs] / гидрогелевые патчи для глаз с золотом 1 пара</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="n">
-        <v>428</v>
-      </c>
-      <c r="E54" s="5" t="n">
-        <v>71</v>
-      </c>
-      <c r="F54" s="5" t="n">
-        <v>819</v>
-      </c>
-      <c r="G54" s="5" t="n">
-        <v>51</v>
-      </c>
-      <c r="H54" s="5" t="n">
-        <v>58</v>
-      </c>
-      <c r="I54" s="4" t="inlineStr">
+      <c r="J55" s="5" t="n">
+        <v>-24</v>
+      </c>
+      <c r="K55" s="4" t="n">
+        <v>-16</v>
+      </c>
+      <c r="L55" s="5" t="n">
+        <v>-5795</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>JMSOLUTION</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="n"/>
+      <c r="D56" s="3" t="n"/>
+      <c r="E56" s="3" t="n"/>
+      <c r="F56" s="3" t="n"/>
+      <c r="G56" s="3" t="n"/>
+      <c r="H56" s="3" t="n"/>
+      <c r="I56" s="2" t="n"/>
+      <c r="J56" s="3" t="n"/>
+      <c r="K56" s="2" t="n"/>
+      <c r="L56" s="3" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>JMSOLUTION</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>JMSOLUTION  JMSOLUTION - Glory Aqua TOCOPHEROL VITAMIN C MASK PLUS [30ml*10ea] / Тканевая маска</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="n">
+        <v>110</v>
+      </c>
+      <c r="E57" s="5" t="n">
+        <v>450</v>
+      </c>
+      <c r="F57" s="5" t="n">
+        <v>5311</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>329</v>
+      </c>
+      <c r="H57" s="5" t="n">
+        <v>379</v>
+      </c>
+      <c r="I57" s="4" t="inlineStr">
         <is>
           <t>FINESKIN (ответ)</t>
         </is>
       </c>
-      <c r="J54" s="5" t="n">
-        <v>-13</v>
-      </c>
-      <c r="K54" s="4" t="n">
-        <v>-18</v>
-      </c>
-      <c r="L54" s="5" t="n">
-        <v>-5498</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="n"/>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>ROUND LAB</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="n"/>
-      <c r="D55" s="3" t="n"/>
-      <c r="E55" s="3" t="n"/>
-      <c r="F55" s="3" t="n"/>
-      <c r="G55" s="3" t="n"/>
-      <c r="H55" s="3" t="n"/>
-      <c r="I55" s="2" t="n"/>
-      <c r="J55" s="3" t="n"/>
-      <c r="K55" s="2" t="n"/>
-      <c r="L55" s="3" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="4" t="n">
-        <v>41</v>
-      </c>
-      <c r="B56" s="4" t="inlineStr">
-        <is>
-          <t>ROUND LAB</t>
-        </is>
-      </c>
-      <c r="C56" s="4" t="inlineStr">
-        <is>
-          <t>ROUND LAB MUGWORT CALMING CLEANSER_150ml - Очищающая пенка для умывания лица от прыщей и акне</t>
-        </is>
-      </c>
-      <c r="D56" s="5" t="n">
-        <v>1422</v>
-      </c>
-      <c r="E56" s="5" t="n">
-        <v>512</v>
-      </c>
-      <c r="F56" s="5" t="n">
-        <v>5963</v>
-      </c>
-      <c r="G56" s="5" t="n">
-        <v>370</v>
-      </c>
-      <c r="H56" s="5" t="n">
-        <v>425</v>
-      </c>
-      <c r="I56" s="4" t="inlineStr">
-        <is>
-          <t>G&amp;E Global</t>
-        </is>
-      </c>
-      <c r="J56" s="5" t="n">
-        <v>-87</v>
-      </c>
-      <c r="K56" s="4" t="n">
-        <v>-17</v>
-      </c>
-      <c r="L56" s="5" t="n">
-        <v>-123939</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="n"/>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>DEOPROCE</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="n"/>
-      <c r="D57" s="3" t="n"/>
-      <c r="E57" s="3" t="n"/>
-      <c r="F57" s="3" t="n"/>
-      <c r="G57" s="3" t="n"/>
-      <c r="H57" s="3" t="n"/>
-      <c r="I57" s="2" t="n"/>
-      <c r="J57" s="3" t="n"/>
-      <c r="K57" s="2" t="n"/>
-      <c r="L57" s="3" t="n"/>
+      <c r="J57" s="5" t="n">
+        <v>-72</v>
+      </c>
+      <c r="K57" s="4" t="n">
+        <v>-15.9</v>
+      </c>
+      <c r="L57" s="5" t="n">
+        <v>-7884</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="n">
@@ -7405,105 +7405,105 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>DEOPROCE</t>
+          <t>JMSOLUTION</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>DEOPROCE SHAMPOO - BLACK GARLIC INTENSME ENERGY [200ml]/ Шампунь с черным чесноком против выпадения волос</t>
+          <t>JMSOLUTION GLORY AQUA FULLERENE MASK DELUXE</t>
         </is>
       </c>
       <c r="D58" s="5" t="n">
-        <v>240</v>
+        <v>110</v>
       </c>
       <c r="E58" s="5" t="n">
-        <v>151</v>
+        <v>450</v>
       </c>
       <c r="F58" s="5" t="n">
-        <v>1781</v>
+        <v>5311</v>
       </c>
       <c r="G58" s="5" t="n">
+        <v>329</v>
+      </c>
+      <c r="H58" s="5" t="n">
+        <v>379</v>
+      </c>
+      <c r="I58" s="4" t="inlineStr">
+        <is>
+          <t>FINESKIN (ответ)</t>
+        </is>
+      </c>
+      <c r="J58" s="5" t="n">
+        <v>-72</v>
+      </c>
+      <c r="K58" s="4" t="n">
+        <v>-15.9</v>
+      </c>
+      <c r="L58" s="5" t="n">
+        <v>-7884</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>JMSOLUTION</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>JMSOLUTION PANTHELENE INTENSIVE BARRIER MASK</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="n">
         <v>110</v>
       </c>
-      <c r="H58" s="5" t="n">
-        <v>127</v>
-      </c>
-      <c r="I58" s="4" t="inlineStr">
+      <c r="E59" s="5" t="n">
+        <v>450</v>
+      </c>
+      <c r="F59" s="5" t="n">
+        <v>5311</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>329</v>
+      </c>
+      <c r="H59" s="5" t="n">
+        <v>379</v>
+      </c>
+      <c r="I59" s="4" t="inlineStr">
         <is>
           <t>FINESKIN (ответ)</t>
         </is>
       </c>
-      <c r="J58" s="5" t="n">
-        <v>-24</v>
-      </c>
-      <c r="K58" s="4" t="n">
-        <v>-16</v>
-      </c>
-      <c r="L58" s="5" t="n">
-        <v>-5795</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="n"/>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>JMSOLUTION</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="n"/>
-      <c r="D59" s="3" t="n"/>
-      <c r="E59" s="3" t="n"/>
-      <c r="F59" s="3" t="n"/>
-      <c r="G59" s="3" t="n"/>
-      <c r="H59" s="3" t="n"/>
-      <c r="I59" s="2" t="n"/>
-      <c r="J59" s="3" t="n"/>
-      <c r="K59" s="2" t="n"/>
-      <c r="L59" s="3" t="n"/>
+      <c r="J59" s="5" t="n">
+        <v>-72</v>
+      </c>
+      <c r="K59" s="4" t="n">
+        <v>-15.9</v>
+      </c>
+      <c r="L59" s="5" t="n">
+        <v>-7884</v>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" s="4" t="n">
-        <v>43</v>
-      </c>
-      <c r="B60" s="4" t="inlineStr">
-        <is>
-          <t>JMSOLUTION</t>
-        </is>
-      </c>
-      <c r="C60" s="4" t="inlineStr">
-        <is>
-          <t>JMSOLUTION GLORY AQUA FULLERENE MASK DELUXE</t>
-        </is>
-      </c>
-      <c r="D60" s="5" t="n">
-        <v>110</v>
-      </c>
-      <c r="E60" s="5" t="n">
-        <v>450</v>
-      </c>
-      <c r="F60" s="5" t="n">
-        <v>5311</v>
-      </c>
-      <c r="G60" s="5" t="n">
-        <v>329</v>
-      </c>
-      <c r="H60" s="5" t="n">
-        <v>379</v>
-      </c>
-      <c r="I60" s="4" t="inlineStr">
-        <is>
-          <t>FINESKIN (ответ)</t>
-        </is>
-      </c>
-      <c r="J60" s="5" t="n">
-        <v>-72</v>
-      </c>
-      <c r="K60" s="4" t="n">
-        <v>-15.9</v>
-      </c>
-      <c r="L60" s="5" t="n">
-        <v>-7884</v>
-      </c>
+      <c r="A60" s="2" t="n"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>FARMSTAY</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="n"/>
+      <c r="D60" s="3" t="n"/>
+      <c r="E60" s="3" t="n"/>
+      <c r="F60" s="3" t="n"/>
+      <c r="G60" s="3" t="n"/>
+      <c r="H60" s="3" t="n"/>
+      <c r="I60" s="2" t="n"/>
+      <c r="J60" s="3" t="n"/>
+      <c r="K60" s="2" t="n"/>
+      <c r="L60" s="3" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="4" t="n">
@@ -7511,42 +7511,42 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>JMSOLUTION</t>
+          <t>FARMSTAY</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>JMSOLUTION PANTHELENE INTENSIVE BARRIER MASK</t>
+          <t>FARMSTAY ESCARGOT NOBLESSE INTENSIVE AMPOULE/ сыворотка с улиткой</t>
         </is>
       </c>
       <c r="D61" s="5" t="n">
-        <v>110</v>
+        <v>901</v>
       </c>
       <c r="E61" s="5" t="n">
-        <v>450</v>
+        <v>390</v>
       </c>
       <c r="F61" s="5" t="n">
-        <v>5311</v>
+        <v>4660</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>329</v>
+        <v>289</v>
       </c>
       <c r="H61" s="5" t="n">
-        <v>379</v>
+        <v>332</v>
       </c>
       <c r="I61" s="4" t="inlineStr">
         <is>
-          <t>FINESKIN (ответ)</t>
+          <t>Классик</t>
         </is>
       </c>
       <c r="J61" s="5" t="n">
-        <v>-72</v>
+        <v>-58</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>-15.9</v>
+        <v>-14.9</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>-7884</v>
+        <v>-52440</v>
       </c>
     </row>
     <row r="62">
@@ -7555,105 +7555,105 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>JMSOLUTION</t>
+          <t>FARMSTAY</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>JMSOLUTION  JMSOLUTION - Glory Aqua TOCOPHEROL VITAMIN C MASK PLUS [30ml*10ea] / Тканевая маска</t>
+          <t>FARMSTAY - Collagen Pure Cleansing Foam [180ml]/Пенка для умывания</t>
         </is>
       </c>
       <c r="D62" s="5" t="n">
-        <v>110</v>
+        <v>300</v>
       </c>
       <c r="E62" s="5" t="n">
-        <v>450</v>
+        <v>161</v>
       </c>
       <c r="F62" s="5" t="n">
-        <v>5311</v>
+        <v>1930</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>329</v>
+        <v>120</v>
       </c>
       <c r="H62" s="5" t="n">
-        <v>379</v>
+        <v>138</v>
       </c>
       <c r="I62" s="4" t="inlineStr">
         <is>
-          <t>FINESKIN (ответ)</t>
+          <t>Классик</t>
         </is>
       </c>
       <c r="J62" s="5" t="n">
-        <v>-72</v>
+        <v>-24</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>-15.9</v>
+        <v>-14.8</v>
       </c>
       <c r="L62" s="5" t="n">
-        <v>-7884</v>
+        <v>-7158</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n"/>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="A63" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
         <is>
           <t>FARMSTAY</t>
         </is>
       </c>
-      <c r="C63" s="2" t="n"/>
-      <c r="D63" s="3" t="n"/>
-      <c r="E63" s="3" t="n"/>
-      <c r="F63" s="3" t="n"/>
-      <c r="G63" s="3" t="n"/>
-      <c r="H63" s="3" t="n"/>
-      <c r="I63" s="2" t="n"/>
-      <c r="J63" s="3" t="n"/>
-      <c r="K63" s="2" t="n"/>
-      <c r="L63" s="3" t="n"/>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>FARMSTAY - Collagen Water Full Moist Rolling Eye Serum [25ml] / Сыворотка роллер для глаз</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="n">
+        <v>156</v>
+      </c>
+      <c r="E63" s="5" t="n">
+        <v>232</v>
+      </c>
+      <c r="F63" s="5" t="n">
+        <v>2770</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>172</v>
+      </c>
+      <c r="H63" s="5" t="n">
+        <v>198</v>
+      </c>
+      <c r="I63" s="4" t="inlineStr">
+        <is>
+          <t>Классик</t>
+        </is>
+      </c>
+      <c r="J63" s="5" t="n">
+        <v>-34</v>
+      </c>
+      <c r="K63" s="4" t="n">
+        <v>-14.8</v>
+      </c>
+      <c r="L63" s="5" t="n">
+        <v>-5340</v>
+      </c>
     </row>
     <row r="64">
-      <c r="A64" s="4" t="n">
-        <v>46</v>
-      </c>
-      <c r="B64" s="4" t="inlineStr">
-        <is>
-          <t>FARMSTAY</t>
-        </is>
-      </c>
-      <c r="C64" s="4" t="inlineStr">
-        <is>
-          <t>FARMSTAY ESCARGOT NOBLESSE INTENSIVE AMPOULE/ сыворотка с улиткой</t>
-        </is>
-      </c>
-      <c r="D64" s="5" t="n">
-        <v>901</v>
-      </c>
-      <c r="E64" s="5" t="n">
-        <v>390</v>
-      </c>
-      <c r="F64" s="5" t="n">
-        <v>4660</v>
-      </c>
-      <c r="G64" s="5" t="n">
-        <v>289</v>
-      </c>
-      <c r="H64" s="5" t="n">
-        <v>332</v>
-      </c>
-      <c r="I64" s="4" t="inlineStr">
-        <is>
-          <t>Классик</t>
-        </is>
-      </c>
-      <c r="J64" s="5" t="n">
-        <v>-58</v>
-      </c>
-      <c r="K64" s="4" t="n">
-        <v>-14.9</v>
-      </c>
-      <c r="L64" s="5" t="n">
-        <v>-52440</v>
-      </c>
+      <c r="A64" s="2" t="n"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>CELIMAX</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="n"/>
+      <c r="D64" s="3" t="n"/>
+      <c r="E64" s="3" t="n"/>
+      <c r="F64" s="3" t="n"/>
+      <c r="G64" s="3" t="n"/>
+      <c r="H64" s="3" t="n"/>
+      <c r="I64" s="2" t="n"/>
+      <c r="J64" s="3" t="n"/>
+      <c r="K64" s="2" t="n"/>
+      <c r="L64" s="3" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="4" t="n">
@@ -7661,105 +7661,105 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>FARMSTAY</t>
+          <t>CELIMAX</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>FARMSTAY - Collagen Pure Cleansing Foam [180ml]/Пенка для умывания</t>
+          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD [170ml / 60pads]/Тонер-пэды от воспалений</t>
         </is>
       </c>
       <c r="D65" s="5" t="n">
-        <v>300</v>
+        <v>1500</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>161</v>
+        <v>708</v>
       </c>
       <c r="F65" s="5" t="n">
-        <v>1930</v>
+        <v>8509</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>120</v>
+        <v>528</v>
       </c>
       <c r="H65" s="5" t="n">
-        <v>138</v>
+        <v>607</v>
       </c>
       <c r="I65" s="4" t="inlineStr">
         <is>
+          <t>Papa Cosmetic</t>
+        </is>
+      </c>
+      <c r="J65" s="5" t="n">
+        <v>-101</v>
+      </c>
+      <c r="K65" s="4" t="n">
+        <v>-14.3</v>
+      </c>
+      <c r="L65" s="5" t="n">
+        <v>-151773</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>ENOUGH</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="n"/>
+      <c r="D66" s="3" t="n"/>
+      <c r="E66" s="3" t="n"/>
+      <c r="F66" s="3" t="n"/>
+      <c r="G66" s="3" t="n"/>
+      <c r="H66" s="3" t="n"/>
+      <c r="I66" s="2" t="n"/>
+      <c r="J66" s="3" t="n"/>
+      <c r="K66" s="2" t="n"/>
+      <c r="L66" s="3" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>ENOUGH</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ENOUGH Collagen whitening cover tip concealer #01 [9g]/Консилер для лица (основная карточка) </t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="E67" s="5" t="n">
+        <v>183</v>
+      </c>
+      <c r="F67" s="5" t="n">
+        <v>2250</v>
+      </c>
+      <c r="G67" s="5" t="n">
+        <v>140</v>
+      </c>
+      <c r="H67" s="5" t="n">
+        <v>160</v>
+      </c>
+      <c r="I67" s="4" t="inlineStr">
+        <is>
           <t>Классик</t>
         </is>
       </c>
-      <c r="J65" s="5" t="n">
-        <v>-24</v>
-      </c>
-      <c r="K65" s="4" t="n">
-        <v>-14.8</v>
-      </c>
-      <c r="L65" s="5" t="n">
-        <v>-7158</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="4" t="n">
-        <v>48</v>
-      </c>
-      <c r="B66" s="4" t="inlineStr">
-        <is>
-          <t>FARMSTAY</t>
-        </is>
-      </c>
-      <c r="C66" s="4" t="inlineStr">
-        <is>
-          <t>FARMSTAY - Collagen Water Full Moist Rolling Eye Serum [25ml] / Сыворотка роллер для глаз</t>
-        </is>
-      </c>
-      <c r="D66" s="5" t="n">
-        <v>156</v>
-      </c>
-      <c r="E66" s="5" t="n">
-        <v>232</v>
-      </c>
-      <c r="F66" s="5" t="n">
-        <v>2770</v>
-      </c>
-      <c r="G66" s="5" t="n">
-        <v>172</v>
-      </c>
-      <c r="H66" s="5" t="n">
-        <v>198</v>
-      </c>
-      <c r="I66" s="4" t="inlineStr">
-        <is>
-          <t>Классик</t>
-        </is>
-      </c>
-      <c r="J66" s="5" t="n">
-        <v>-34</v>
-      </c>
-      <c r="K66" s="4" t="n">
-        <v>-14.8</v>
-      </c>
-      <c r="L66" s="5" t="n">
-        <v>-5340</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="n"/>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>CELIMAX</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="n"/>
-      <c r="D67" s="3" t="n"/>
-      <c r="E67" s="3" t="n"/>
-      <c r="F67" s="3" t="n"/>
-      <c r="G67" s="3" t="n"/>
-      <c r="H67" s="3" t="n"/>
-      <c r="I67" s="2" t="n"/>
-      <c r="J67" s="3" t="n"/>
-      <c r="K67" s="2" t="n"/>
-      <c r="L67" s="3" t="n"/>
+      <c r="J67" s="5" t="n">
+        <v>-23</v>
+      </c>
+      <c r="K67" s="4" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="L67" s="5" t="n">
+        <v>-4563</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="n">
@@ -7767,105 +7767,105 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>CELIMAX</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD [170ml / 60pads]/Тонер-пэды от воспалений</t>
+          <t>ENOUGH Collagen whitening cover tip concealer #02 [9g]/Консилер для лица (основная карточка)</t>
         </is>
       </c>
       <c r="D68" s="5" t="n">
-        <v>1500</v>
+        <v>300</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>708</v>
+        <v>183</v>
       </c>
       <c r="F68" s="5" t="n">
-        <v>8509</v>
+        <v>2250</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>528</v>
+        <v>140</v>
       </c>
       <c r="H68" s="5" t="n">
-        <v>607</v>
+        <v>160</v>
       </c>
       <c r="I68" s="4" t="inlineStr">
         <is>
-          <t>Papa Cosmetic</t>
+          <t>Классик</t>
         </is>
       </c>
       <c r="J68" s="5" t="n">
-        <v>-101</v>
+        <v>-23</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>-14.3</v>
+        <v>-12.5</v>
       </c>
       <c r="L68" s="5" t="n">
-        <v>-151773</v>
+        <v>-6844</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n"/>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="A69" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
         <is>
           <t>ENOUGH</t>
         </is>
       </c>
-      <c r="C69" s="2" t="n"/>
-      <c r="D69" s="3" t="n"/>
-      <c r="E69" s="3" t="n"/>
-      <c r="F69" s="3" t="n"/>
-      <c r="G69" s="3" t="n"/>
-      <c r="H69" s="3" t="n"/>
-      <c r="I69" s="2" t="n"/>
-      <c r="J69" s="3" t="n"/>
-      <c r="K69" s="2" t="n"/>
-      <c r="L69" s="3" t="n"/>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>ENOUGH Collagen whitening cover tip concealer #03 [9g]/ Консилер для лица (основаная карточка)</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="n">
+        <v>260</v>
+      </c>
+      <c r="E69" s="5" t="n">
+        <v>183</v>
+      </c>
+      <c r="F69" s="5" t="n">
+        <v>2250</v>
+      </c>
+      <c r="G69" s="5" t="n">
+        <v>140</v>
+      </c>
+      <c r="H69" s="5" t="n">
+        <v>160</v>
+      </c>
+      <c r="I69" s="4" t="inlineStr">
+        <is>
+          <t>Классик</t>
+        </is>
+      </c>
+      <c r="J69" s="5" t="n">
+        <v>-23</v>
+      </c>
+      <c r="K69" s="4" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="L69" s="5" t="n">
+        <v>-5932</v>
+      </c>
     </row>
     <row r="70">
-      <c r="A70" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="B70" s="4" t="inlineStr">
-        <is>
-          <t>ENOUGH</t>
-        </is>
-      </c>
-      <c r="C70" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ENOUGH Collagen whitening cover tip concealer #01 [9g]/Консилер для лица (основная карточка) </t>
-        </is>
-      </c>
-      <c r="D70" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="E70" s="5" t="n">
-        <v>183</v>
-      </c>
-      <c r="F70" s="5" t="n">
-        <v>2250</v>
-      </c>
-      <c r="G70" s="5" t="n">
-        <v>140</v>
-      </c>
-      <c r="H70" s="5" t="n">
-        <v>160</v>
-      </c>
-      <c r="I70" s="4" t="inlineStr">
-        <is>
-          <t>Классик</t>
-        </is>
-      </c>
-      <c r="J70" s="5" t="n">
-        <v>-23</v>
-      </c>
-      <c r="K70" s="4" t="n">
-        <v>-12.5</v>
-      </c>
-      <c r="L70" s="5" t="n">
-        <v>-4563</v>
-      </c>
+      <c r="A70" s="2" t="n"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>DEOPROCE</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="n"/>
+      <c r="D70" s="3" t="n"/>
+      <c r="E70" s="3" t="n"/>
+      <c r="F70" s="3" t="n"/>
+      <c r="G70" s="3" t="n"/>
+      <c r="H70" s="3" t="n"/>
+      <c r="I70" s="2" t="n"/>
+      <c r="J70" s="3" t="n"/>
+      <c r="K70" s="2" t="n"/>
+      <c r="L70" s="3" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="4" t="n">
@@ -7873,42 +7873,42 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>ENOUGH</t>
+          <t>DEOPROCE</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>ENOUGH Collagen whitening cover tip concealer #02 [9g]/Консилер для лица (основная карточка)</t>
+          <t>DEOPROCE RINSE - BLACK GARLIC INTENSME ENERGY [1000ml] / Бальзам от выпадения волос Чёрный чеснок</t>
         </is>
       </c>
       <c r="D71" s="5" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E71" s="5" t="n">
-        <v>183</v>
+        <v>359</v>
       </c>
       <c r="F71" s="5" t="n">
-        <v>2250</v>
+        <v>4431</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>140</v>
+        <v>275</v>
       </c>
       <c r="H71" s="5" t="n">
-        <v>160</v>
+        <v>316</v>
       </c>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t>Классик</t>
+          <t>FINESKIN (ответ)</t>
         </is>
       </c>
       <c r="J71" s="5" t="n">
-        <v>-23</v>
+        <v>-43</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>-12.5</v>
+        <v>-12</v>
       </c>
       <c r="L71" s="5" t="n">
-        <v>-6844</v>
+        <v>-17200</v>
       </c>
     </row>
     <row r="72">
@@ -7917,49 +7917,49 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>ENOUGH</t>
+          <t>DEOPROCE</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>ENOUGH Collagen whitening cover tip concealer #03 [9g]/ Консилер для лица (основаная карточка)</t>
+          <t>DEOPROCE SHAMPOO - BLACK GARLIC INTENSME ENERGY [1000ml]/ Шампунь с черным чесноком против выпадения волос</t>
         </is>
       </c>
       <c r="D72" s="5" t="n">
-        <v>260</v>
+        <v>400</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>183</v>
+        <v>368</v>
       </c>
       <c r="F72" s="5" t="n">
-        <v>2250</v>
+        <v>4547</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>140</v>
+        <v>282</v>
       </c>
       <c r="H72" s="5" t="n">
-        <v>160</v>
+        <v>324</v>
       </c>
       <c r="I72" s="4" t="inlineStr">
         <is>
-          <t>Классик</t>
+          <t>FINESKIN (ответ)</t>
         </is>
       </c>
       <c r="J72" s="5" t="n">
-        <v>-23</v>
+        <v>-44</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>-12.5</v>
+        <v>-11.9</v>
       </c>
       <c r="L72" s="5" t="n">
-        <v>-5932</v>
+        <v>-17488</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n"/>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>DEOPROCE</t>
+          <t>LEBELAGE</t>
         </is>
       </c>
       <c r="C73" s="2" t="n"/>
@@ -7979,167 +7979,167 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>DEOPROCE</t>
+          <t>LEBELAGE</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>DEOPROCE RINSE - BLACK GARLIC INTENSME ENERGY [1000ml] / Бальзам от выпадения волос Чёрный чеснок</t>
+          <t>LEBELAGE - Dr. Peptide Derma Eye Cream [40ml] / Крем для глаз антивозрастной с пептидами</t>
         </is>
       </c>
       <c r="D74" s="5" t="n">
         <v>400</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>359</v>
+        <v>108</v>
       </c>
       <c r="F74" s="5" t="n">
-        <v>4431</v>
+        <v>1350</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>275</v>
+        <v>84</v>
       </c>
       <c r="H74" s="5" t="n">
-        <v>316</v>
+        <v>96</v>
       </c>
       <c r="I74" s="4" t="inlineStr">
         <is>
-          <t>FINESKIN (ответ)</t>
+          <t>Классик</t>
         </is>
       </c>
       <c r="J74" s="5" t="n">
-        <v>-43</v>
+        <v>-12</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="L74" s="5" t="n">
-        <v>-17200</v>
+        <v>-4758</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="4" t="n">
+      <c r="A75" s="2" t="n"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>ROUND LAB</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="n"/>
+      <c r="D75" s="3" t="n"/>
+      <c r="E75" s="3" t="n"/>
+      <c r="F75" s="3" t="n"/>
+      <c r="G75" s="3" t="n"/>
+      <c r="H75" s="3" t="n"/>
+      <c r="I75" s="2" t="n"/>
+      <c r="J75" s="3" t="n"/>
+      <c r="K75" s="2" t="n"/>
+      <c r="L75" s="3" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="n">
         <v>54</v>
       </c>
-      <c r="B75" s="4" t="inlineStr">
-        <is>
-          <t>DEOPROCE</t>
-        </is>
-      </c>
-      <c r="C75" s="4" t="inlineStr">
-        <is>
-          <t>DEOPROCE SHAMPOO - BLACK GARLIC INTENSME ENERGY [1000ml]/ Шампунь с черным чесноком против выпадения волос</t>
-        </is>
-      </c>
-      <c r="D75" s="5" t="n">
-        <v>400</v>
-      </c>
-      <c r="E75" s="5" t="n">
-        <v>368</v>
-      </c>
-      <c r="F75" s="5" t="n">
-        <v>4547</v>
-      </c>
-      <c r="G75" s="5" t="n">
-        <v>282</v>
-      </c>
-      <c r="H75" s="5" t="n">
-        <v>324</v>
-      </c>
-      <c r="I75" s="4" t="inlineStr">
-        <is>
-          <t>FINESKIN (ответ)</t>
-        </is>
-      </c>
-      <c r="J75" s="5" t="n">
-        <v>-44</v>
-      </c>
-      <c r="K75" s="4" t="n">
-        <v>-11.9</v>
-      </c>
-      <c r="L75" s="5" t="n">
-        <v>-17488</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="n"/>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>LEBELAGE</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="n"/>
-      <c r="D76" s="3" t="n"/>
-      <c r="E76" s="3" t="n"/>
-      <c r="F76" s="3" t="n"/>
-      <c r="G76" s="3" t="n"/>
-      <c r="H76" s="3" t="n"/>
-      <c r="I76" s="2" t="n"/>
-      <c r="J76" s="3" t="n"/>
-      <c r="K76" s="2" t="n"/>
-      <c r="L76" s="3" t="n"/>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>ROUND LAB</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>ROUND LAB 1025 DOKDO CLEANSER_150ml - Увлажняющая пенка для умывания лица</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="n">
+        <v>7126</v>
+      </c>
+      <c r="E76" s="5" t="n">
+        <v>463</v>
+      </c>
+      <c r="F76" s="5" t="n">
+        <v>5857</v>
+      </c>
+      <c r="G76" s="5" t="n">
+        <v>363</v>
+      </c>
+      <c r="H76" s="5" t="n">
+        <v>418</v>
+      </c>
+      <c r="I76" s="4" t="inlineStr">
+        <is>
+          <t>G&amp;E Global</t>
+        </is>
+      </c>
+      <c r="J76" s="5" t="n">
+        <v>-46</v>
+      </c>
+      <c r="K76" s="4" t="n">
+        <v>-9.800000000000001</v>
+      </c>
+      <c r="L76" s="5" t="n">
+        <v>-324845</v>
+      </c>
     </row>
     <row r="77">
-      <c r="A77" s="4" t="n">
+      <c r="A77" s="2" t="n"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>FARMSTAY</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="n"/>
+      <c r="D77" s="3" t="n"/>
+      <c r="E77" s="3" t="n"/>
+      <c r="F77" s="3" t="n"/>
+      <c r="G77" s="3" t="n"/>
+      <c r="H77" s="3" t="n"/>
+      <c r="I77" s="2" t="n"/>
+      <c r="J77" s="3" t="n"/>
+      <c r="K77" s="2" t="n"/>
+      <c r="L77" s="3" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="B77" s="4" t="inlineStr">
-        <is>
-          <t>LEBELAGE</t>
-        </is>
-      </c>
-      <c r="C77" s="4" t="inlineStr">
-        <is>
-          <t>LEBELAGE - Dr. Peptide Derma Eye Cream [40ml] / Крем для глаз антивозрастной с пептидами</t>
-        </is>
-      </c>
-      <c r="D77" s="5" t="n">
-        <v>400</v>
-      </c>
-      <c r="E77" s="5" t="n">
-        <v>108</v>
-      </c>
-      <c r="F77" s="5" t="n">
-        <v>1350</v>
-      </c>
-      <c r="G77" s="5" t="n">
-        <v>84</v>
-      </c>
-      <c r="H77" s="5" t="n">
-        <v>96</v>
-      </c>
-      <c r="I77" s="4" t="inlineStr">
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>FARMSTAY</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>FARMSTAY - Escargot Noblesse Intensive Cream [50g] / Крем с муцином королевской улитки</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="n">
+        <v>860</v>
+      </c>
+      <c r="E78" s="5" t="n">
+        <v>314</v>
+      </c>
+      <c r="F78" s="5" t="n">
+        <v>4010</v>
+      </c>
+      <c r="G78" s="5" t="n">
+        <v>249</v>
+      </c>
+      <c r="H78" s="5" t="n">
+        <v>286</v>
+      </c>
+      <c r="I78" s="4" t="inlineStr">
         <is>
           <t>Классик</t>
         </is>
       </c>
-      <c r="J77" s="5" t="n">
-        <v>-12</v>
-      </c>
-      <c r="K77" s="4" t="n">
-        <v>-11</v>
-      </c>
-      <c r="L77" s="5" t="n">
-        <v>-4758</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="n"/>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>ROUND LAB</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="n"/>
-      <c r="D78" s="3" t="n"/>
-      <c r="E78" s="3" t="n"/>
-      <c r="F78" s="3" t="n"/>
-      <c r="G78" s="3" t="n"/>
-      <c r="H78" s="3" t="n"/>
-      <c r="I78" s="2" t="n"/>
-      <c r="J78" s="3" t="n"/>
-      <c r="K78" s="2" t="n"/>
-      <c r="L78" s="3" t="n"/>
+      <c r="J78" s="5" t="n">
+        <v>-28</v>
+      </c>
+      <c r="K78" s="4" t="n">
+        <v>-8.9</v>
+      </c>
+      <c r="L78" s="5" t="n">
+        <v>-24017</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="n">
@@ -8147,49 +8147,49 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>ROUND LAB</t>
+          <t>FARMSTAY</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>ROUND LAB 1025 DOKDO CLEANSER_150ml - Увлажняющая пенка для умывания лица</t>
+          <t>FARMSTAY - Collagen &amp; Hyaluronic Acid All-In One Ampoule [250ml] / Сыворотка с коллагеном и гиалуроновой кислотой</t>
         </is>
       </c>
       <c r="D79" s="5" t="n">
-        <v>7126</v>
+        <v>6179</v>
       </c>
       <c r="E79" s="5" t="n">
-        <v>463</v>
+        <v>348</v>
       </c>
       <c r="F79" s="5" t="n">
-        <v>5857</v>
+        <v>4660</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>363</v>
+        <v>289</v>
       </c>
       <c r="H79" s="5" t="n">
-        <v>418</v>
+        <v>332</v>
       </c>
       <c r="I79" s="4" t="inlineStr">
         <is>
-          <t>G&amp;E Global</t>
+          <t>Классик</t>
         </is>
       </c>
       <c r="J79" s="5" t="n">
-        <v>-46</v>
+        <v>-16</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>-9.800000000000001</v>
+        <v>-4.5</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>-324845</v>
+        <v>-95787</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n"/>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>FARMSTAY</t>
+          <t>ELIZAVECCA</t>
         </is>
       </c>
       <c r="C80" s="2" t="n"/>
@@ -8209,291 +8209,291 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>FARMSTAY</t>
+          <t>ELIZAVECCA</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>FARMSTAY - Escargot Noblesse Intensive Cream [50g] / Крем с муцином королевской улитки</t>
+          <t>ELIZAVECCA - CER-100 Collagen Ceramide Coating Protein Treatment [100ml] / Коллагеновая маска для волос</t>
         </is>
       </c>
       <c r="D81" s="5" t="n">
-        <v>860</v>
+        <v>300</v>
       </c>
       <c r="E81" s="5" t="n">
-        <v>314</v>
+        <v>242</v>
       </c>
       <c r="F81" s="5" t="n">
-        <v>4010</v>
+        <v>3276</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>249</v>
+        <v>203</v>
       </c>
       <c r="H81" s="5" t="n">
-        <v>286</v>
+        <v>234</v>
       </c>
       <c r="I81" s="4" t="inlineStr">
         <is>
+          <t>FINESKIN (ответ)</t>
+        </is>
+      </c>
+      <c r="J81" s="5" t="n">
+        <v>-9</v>
+      </c>
+      <c r="K81" s="4" t="n">
+        <v>-3.6</v>
+      </c>
+      <c r="L81" s="5" t="n">
+        <v>-2595</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>CELIMAX</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="n"/>
+      <c r="D82" s="3" t="n"/>
+      <c r="E82" s="3" t="n"/>
+      <c r="F82" s="3" t="n"/>
+      <c r="G82" s="3" t="n"/>
+      <c r="H82" s="3" t="n"/>
+      <c r="I82" s="2" t="n"/>
+      <c r="J82" s="3" t="n"/>
+      <c r="K82" s="2" t="n"/>
+      <c r="L82" s="3" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>CELIMAX</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>Celimax Dual Barrier Creamy Toner, тонер 150 мл</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="n">
+        <v>4520</v>
+      </c>
+      <c r="E83" s="5" t="n">
+        <v>664</v>
+      </c>
+      <c r="F83" s="5" t="n">
+        <v>9000</v>
+      </c>
+      <c r="G83" s="5" t="n">
+        <v>558</v>
+      </c>
+      <c r="H83" s="5" t="n">
+        <v>642</v>
+      </c>
+      <c r="I83" s="4" t="inlineStr">
+        <is>
+          <t>Papa Cosmetic</t>
+        </is>
+      </c>
+      <c r="J83" s="5" t="n">
+        <v>-22</v>
+      </c>
+      <c r="K83" s="4" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="L83" s="5" t="n">
+        <v>-100163</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>ENOUGH</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="n"/>
+      <c r="D84" s="3" t="n"/>
+      <c r="E84" s="3" t="n"/>
+      <c r="F84" s="3" t="n"/>
+      <c r="G84" s="3" t="n"/>
+      <c r="H84" s="3" t="n"/>
+      <c r="I84" s="2" t="n"/>
+      <c r="J84" s="3" t="n"/>
+      <c r="K84" s="2" t="n"/>
+      <c r="L84" s="3" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="n">
+        <v>59</v>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>ENOUGH</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>ENOUGH - Collagen Whitening Moisture Cream 3in1 [50g] / Антивозрастной отбеливающий крем с коллагеном</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="n">
+        <v>344</v>
+      </c>
+      <c r="E85" s="5" t="n">
+        <v>184</v>
+      </c>
+      <c r="F85" s="5" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G85" s="5" t="n">
+        <v>155</v>
+      </c>
+      <c r="H85" s="5" t="n">
+        <v>178</v>
+      </c>
+      <c r="I85" s="4" t="inlineStr">
+        <is>
           <t>Классик</t>
         </is>
       </c>
-      <c r="J81" s="5" t="n">
-        <v>-28</v>
-      </c>
-      <c r="K81" s="4" t="n">
-        <v>-8.9</v>
-      </c>
-      <c r="L81" s="5" t="n">
-        <v>-24017</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="4" t="n">
-        <v>58</v>
-      </c>
-      <c r="B82" s="4" t="inlineStr">
-        <is>
-          <t>FARMSTAY</t>
-        </is>
-      </c>
-      <c r="C82" s="4" t="inlineStr">
-        <is>
-          <t>FARMSTAY - Collagen &amp; Hyaluronic Acid All-In One Ampoule [250ml] / Сыворотка с коллагеном и гиалуроновой кислотой</t>
-        </is>
-      </c>
-      <c r="D82" s="5" t="n">
-        <v>6179</v>
-      </c>
-      <c r="E82" s="5" t="n">
-        <v>348</v>
-      </c>
-      <c r="F82" s="5" t="n">
-        <v>4660</v>
-      </c>
-      <c r="G82" s="5" t="n">
-        <v>289</v>
-      </c>
-      <c r="H82" s="5" t="n">
-        <v>332</v>
-      </c>
-      <c r="I82" s="4" t="inlineStr">
-        <is>
-          <t>Классик</t>
-        </is>
-      </c>
-      <c r="J82" s="5" t="n">
-        <v>-16</v>
-      </c>
-      <c r="K82" s="4" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="L82" s="5" t="n">
-        <v>-95787</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="n"/>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>ELIZAVECCA</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="n"/>
-      <c r="D83" s="3" t="n"/>
-      <c r="E83" s="3" t="n"/>
-      <c r="F83" s="3" t="n"/>
-      <c r="G83" s="3" t="n"/>
-      <c r="H83" s="3" t="n"/>
-      <c r="I83" s="2" t="n"/>
-      <c r="J83" s="3" t="n"/>
-      <c r="K83" s="2" t="n"/>
-      <c r="L83" s="3" t="n"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="4" t="n">
-        <v>59</v>
-      </c>
-      <c r="B84" s="4" t="inlineStr">
-        <is>
-          <t>ELIZAVECCA</t>
-        </is>
-      </c>
-      <c r="C84" s="4" t="inlineStr">
-        <is>
-          <t>ELIZAVECCA - CER-100 Collagen Ceramide Coating Protein Treatment [100ml] / Коллагеновая маска для волос</t>
-        </is>
-      </c>
-      <c r="D84" s="5" t="n">
-        <v>300</v>
-      </c>
-      <c r="E84" s="5" t="n">
-        <v>242</v>
-      </c>
-      <c r="F84" s="5" t="n">
-        <v>3276</v>
-      </c>
-      <c r="G84" s="5" t="n">
-        <v>203</v>
-      </c>
-      <c r="H84" s="5" t="n">
-        <v>234</v>
-      </c>
-      <c r="I84" s="4" t="inlineStr">
+      <c r="J85" s="5" t="n">
+        <v>-6</v>
+      </c>
+      <c r="K85" s="4" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="L85" s="5" t="n">
+        <v>-1937</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>SKIN1004</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="n"/>
+      <c r="D86" s="3" t="n"/>
+      <c r="E86" s="3" t="n"/>
+      <c r="F86" s="3" t="n"/>
+      <c r="G86" s="3" t="n"/>
+      <c r="H86" s="3" t="n"/>
+      <c r="I86" s="2" t="n"/>
+      <c r="J86" s="3" t="n"/>
+      <c r="K86" s="2" t="n"/>
+      <c r="L86" s="3" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>SKIN1004</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>SKIN1004 - Madagascar Centella Ampoule [30ml] / Сыворотка для лица успокаивающая из экстракта центеллы.</t>
+        </is>
+      </c>
+      <c r="D87" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="E87" s="5" t="n">
+        <v>368</v>
+      </c>
+      <c r="F87" s="5" t="n">
+        <v>5038</v>
+      </c>
+      <c r="G87" s="5" t="n">
+        <v>312</v>
+      </c>
+      <c r="H87" s="5" t="n">
+        <v>359</v>
+      </c>
+      <c r="I87" s="4" t="inlineStr">
         <is>
           <t>FINESKIN (ответ)</t>
         </is>
       </c>
-      <c r="J84" s="5" t="n">
+      <c r="J87" s="5" t="n">
         <v>-9</v>
       </c>
-      <c r="K84" s="4" t="n">
-        <v>-3.6</v>
-      </c>
-      <c r="L84" s="5" t="n">
-        <v>-2595</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="n"/>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>ENOUGH</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="n"/>
-      <c r="D85" s="3" t="n"/>
-      <c r="E85" s="3" t="n"/>
-      <c r="F85" s="3" t="n"/>
-      <c r="G85" s="3" t="n"/>
-      <c r="H85" s="3" t="n"/>
-      <c r="I85" s="2" t="n"/>
-      <c r="J85" s="3" t="n"/>
-      <c r="K85" s="2" t="n"/>
-      <c r="L85" s="3" t="n"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="B86" s="4" t="inlineStr">
-        <is>
-          <t>ENOUGH</t>
-        </is>
-      </c>
-      <c r="C86" s="4" t="inlineStr">
-        <is>
-          <t>ENOUGH - Collagen Whitening Moisture Cream 3in1 [50g] / Антивозрастной отбеливающий крем с коллагеном</t>
-        </is>
-      </c>
-      <c r="D86" s="5" t="n">
-        <v>344</v>
-      </c>
-      <c r="E86" s="5" t="n">
-        <v>184</v>
-      </c>
-      <c r="F86" s="5" t="n">
-        <v>2500</v>
-      </c>
-      <c r="G86" s="5" t="n">
-        <v>155</v>
-      </c>
-      <c r="H86" s="5" t="n">
-        <v>178</v>
-      </c>
-      <c r="I86" s="4" t="inlineStr">
-        <is>
-          <t>Классик</t>
-        </is>
-      </c>
-      <c r="J86" s="5" t="n">
-        <v>-6</v>
-      </c>
-      <c r="K86" s="4" t="n">
-        <v>-3.1</v>
-      </c>
-      <c r="L86" s="5" t="n">
-        <v>-1937</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="n"/>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>SKIN1004</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="n"/>
-      <c r="D87" s="3" t="n"/>
-      <c r="E87" s="3" t="n"/>
-      <c r="F87" s="3" t="n"/>
-      <c r="G87" s="3" t="n"/>
-      <c r="H87" s="3" t="n"/>
-      <c r="I87" s="2" t="n"/>
-      <c r="J87" s="3" t="n"/>
-      <c r="K87" s="2" t="n"/>
-      <c r="L87" s="3" t="n"/>
+      <c r="K87" s="4" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="L87" s="5" t="n">
+        <v>-260</v>
+      </c>
     </row>
     <row r="88">
-      <c r="A88" s="4" t="n">
+      <c r="A88" s="2" t="n"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="n"/>
+      <c r="D88" s="3" t="n"/>
+      <c r="E88" s="3" t="n"/>
+      <c r="F88" s="3" t="n"/>
+      <c r="G88" s="3" t="n"/>
+      <c r="H88" s="3" t="n"/>
+      <c r="I88" s="2" t="n"/>
+      <c r="J88" s="3" t="n"/>
+      <c r="K88" s="2" t="n"/>
+      <c r="L88" s="3" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="B88" s="4" t="inlineStr">
-        <is>
-          <t>SKIN1004</t>
-        </is>
-      </c>
-      <c r="C88" s="4" t="inlineStr">
-        <is>
-          <t>SKIN1004 - Madagascar Centella Ampoule [30ml] / Сыворотка для лица успокаивающая из экстракта центеллы.</t>
-        </is>
-      </c>
-      <c r="D88" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="E88" s="5" t="n">
-        <v>368</v>
-      </c>
-      <c r="F88" s="5" t="n">
-        <v>5038</v>
-      </c>
-      <c r="G88" s="5" t="n">
-        <v>312</v>
-      </c>
-      <c r="H88" s="5" t="n">
-        <v>359</v>
-      </c>
-      <c r="I88" s="4" t="inlineStr">
-        <is>
-          <t>FINESKIN (ответ)</t>
-        </is>
-      </c>
-      <c r="J88" s="5" t="n">
-        <v>-9</v>
-      </c>
-      <c r="K88" s="4" t="n">
-        <v>-2.4</v>
-      </c>
-      <c r="L88" s="5" t="n">
-        <v>-260</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="n"/>
-      <c r="B89" s="2" t="inlineStr">
+      <c r="B89" s="4" t="inlineStr">
         <is>
           <t>PETITFEE</t>
         </is>
       </c>
-      <c r="C89" s="2" t="n"/>
-      <c r="D89" s="3" t="n"/>
-      <c r="E89" s="3" t="n"/>
-      <c r="F89" s="3" t="n"/>
-      <c r="G89" s="3" t="n"/>
-      <c r="H89" s="3" t="n"/>
-      <c r="I89" s="2" t="n"/>
-      <c r="J89" s="3" t="n"/>
-      <c r="K89" s="2" t="n"/>
-      <c r="L89" s="3" t="n"/>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>PETITFEE - Gold &amp; Snail Hydrogel Eye Patch [60ea] / Гидрогелевые патчи для глаз с золотом и улиткой</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="n">
+        <v>144</v>
+      </c>
+      <c r="E89" s="5" t="n">
+        <v>415</v>
+      </c>
+      <c r="F89" s="5" t="n">
+        <v>5690</v>
+      </c>
+      <c r="G89" s="5" t="n">
+        <v>353</v>
+      </c>
+      <c r="H89" s="5" t="n">
+        <v>406</v>
+      </c>
+      <c r="I89" s="4" t="inlineStr">
+        <is>
+          <t>J2K (ответ)</t>
+        </is>
+      </c>
+      <c r="J89" s="5" t="n">
+        <v>-10</v>
+      </c>
+      <c r="K89" s="4" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="L89" s="5" t="n">
+        <v>-1406</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="n">
@@ -8540,314 +8540,314 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="4" t="n">
+      <c r="A91" s="2" t="n"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>CELIMAX</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="n"/>
+      <c r="D91" s="3" t="n"/>
+      <c r="E91" s="3" t="n"/>
+      <c r="F91" s="3" t="n"/>
+      <c r="G91" s="3" t="n"/>
+      <c r="H91" s="3" t="n"/>
+      <c r="I91" s="2" t="n"/>
+      <c r="J91" s="3" t="n"/>
+      <c r="K91" s="2" t="n"/>
+      <c r="L91" s="3" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="n">
         <v>63</v>
       </c>
-      <c r="B91" s="4" t="inlineStr">
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>CELIMAX</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>CELIMAX THE REAL NONI MOISTURE BALANCING TONER (NEW) [150ml]/Восстанавливающий тонер с экстрактом нони</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="E92" s="5" t="n">
+        <v>720</v>
+      </c>
+      <c r="F92" s="5" t="n">
+        <v>9886</v>
+      </c>
+      <c r="G92" s="5" t="n">
+        <v>613</v>
+      </c>
+      <c r="H92" s="5" t="n">
+        <v>705</v>
+      </c>
+      <c r="I92" s="4" t="inlineStr">
+        <is>
+          <t>Papa Cosmetic</t>
+        </is>
+      </c>
+      <c r="J92" s="5" t="n">
+        <v>-15</v>
+      </c>
+      <c r="K92" s="4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L92" s="5" t="n">
+        <v>-338</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n"/>
+      <c r="B93" s="2" t="inlineStr">
         <is>
           <t>PETITFEE</t>
         </is>
       </c>
-      <c r="C91" s="4" t="inlineStr">
-        <is>
-          <t>PETITFEE - Gold &amp; Snail Hydrogel Eye Patch [60ea] / Гидрогелевые патчи для глаз с золотом и улиткой</t>
-        </is>
-      </c>
-      <c r="D91" s="5" t="n">
-        <v>144</v>
-      </c>
-      <c r="E91" s="5" t="n">
-        <v>415</v>
-      </c>
-      <c r="F91" s="5" t="n">
-        <v>5690</v>
-      </c>
-      <c r="G91" s="5" t="n">
-        <v>353</v>
-      </c>
-      <c r="H91" s="5" t="n">
-        <v>406</v>
-      </c>
-      <c r="I91" s="4" t="inlineStr">
+      <c r="C93" s="2" t="n"/>
+      <c r="D93" s="3" t="n"/>
+      <c r="E93" s="3" t="n"/>
+      <c r="F93" s="3" t="n"/>
+      <c r="G93" s="3" t="n"/>
+      <c r="H93" s="3" t="n"/>
+      <c r="I93" s="2" t="n"/>
+      <c r="J93" s="3" t="n"/>
+      <c r="K93" s="2" t="n"/>
+      <c r="L93" s="3" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="n">
+        <v>64</v>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>PETITFEE - Gold Hydrogel Mask Pack [5pcs] / Гидрогелевая маска для лица с золотом</t>
+        </is>
+      </c>
+      <c r="D94" s="5" t="n">
+        <v>390</v>
+      </c>
+      <c r="E94" s="5" t="n">
+        <v>507</v>
+      </c>
+      <c r="F94" s="5" t="n">
+        <v>6990</v>
+      </c>
+      <c r="G94" s="5" t="n">
+        <v>433</v>
+      </c>
+      <c r="H94" s="5" t="n">
+        <v>498</v>
+      </c>
+      <c r="I94" s="4" t="inlineStr">
         <is>
           <t>J2K (ответ)</t>
         </is>
       </c>
-      <c r="J91" s="5" t="n">
-        <v>-10</v>
-      </c>
-      <c r="K91" s="4" t="n">
-        <v>-2.3</v>
-      </c>
-      <c r="L91" s="5" t="n">
-        <v>-1406</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="n"/>
-      <c r="B92" s="2" t="inlineStr">
+      <c r="J94" s="5" t="n">
+        <v>-9</v>
+      </c>
+      <c r="K94" s="4" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="L94" s="5" t="n">
+        <v>-3421</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n"/>
+      <c r="B95" s="2" t="inlineStr">
         <is>
           <t>CELIMAX</t>
         </is>
       </c>
-      <c r="C92" s="2" t="n"/>
-      <c r="D92" s="3" t="n"/>
-      <c r="E92" s="3" t="n"/>
-      <c r="F92" s="3" t="n"/>
-      <c r="G92" s="3" t="n"/>
-      <c r="H92" s="3" t="n"/>
-      <c r="I92" s="2" t="n"/>
-      <c r="J92" s="3" t="n"/>
-      <c r="K92" s="2" t="n"/>
-      <c r="L92" s="3" t="n"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="4" t="n">
-        <v>64</v>
-      </c>
-      <c r="B93" s="4" t="inlineStr">
+      <c r="C95" s="2" t="n"/>
+      <c r="D95" s="3" t="n"/>
+      <c r="E95" s="3" t="n"/>
+      <c r="F95" s="3" t="n"/>
+      <c r="G95" s="3" t="n"/>
+      <c r="H95" s="3" t="n"/>
+      <c r="I95" s="2" t="n"/>
+      <c r="J95" s="3" t="n"/>
+      <c r="K95" s="2" t="n"/>
+      <c r="L95" s="3" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
         <is>
           <t>CELIMAX</t>
         </is>
       </c>
-      <c r="C93" s="4" t="inlineStr">
-        <is>
-          <t>CELIMAX THE REAL NONI MOISTURE BALANCING TONER (NEW) [150ml]/Восстанавливающий тонер с экстрактом нони</t>
-        </is>
-      </c>
-      <c r="D93" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="E93" s="5" t="n">
-        <v>720</v>
-      </c>
-      <c r="F93" s="5" t="n">
-        <v>9886</v>
-      </c>
-      <c r="G93" s="5" t="n">
-        <v>613</v>
-      </c>
-      <c r="H93" s="5" t="n">
-        <v>705</v>
-      </c>
-      <c r="I93" s="4" t="inlineStr">
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>CELIMAX DUAL BARRIER SKIN WEARABLE CREAM [50ml]/Крем для восстановления защитного барьера кожи лица</t>
+        </is>
+      </c>
+      <c r="D96" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="E96" s="5" t="n">
+        <v>864</v>
+      </c>
+      <c r="F96" s="5" t="n">
+        <v>11932</v>
+      </c>
+      <c r="G96" s="5" t="n">
+        <v>740</v>
+      </c>
+      <c r="H96" s="5" t="n">
+        <v>851</v>
+      </c>
+      <c r="I96" s="4" t="inlineStr">
         <is>
           <t>Papa Cosmetic</t>
         </is>
       </c>
-      <c r="J93" s="5" t="n">
-        <v>-15</v>
-      </c>
-      <c r="K93" s="4" t="n">
-        <v>-2</v>
-      </c>
-      <c r="L93" s="5" t="n">
-        <v>-338</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="n"/>
-      <c r="B94" s="2" t="inlineStr">
+      <c r="J96" s="5" t="n">
+        <v>-13</v>
+      </c>
+      <c r="K96" s="4" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="L96" s="5" t="n">
+        <v>-1203</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>VT COSMETICS</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="n"/>
+      <c r="D97" s="3" t="n"/>
+      <c r="E97" s="3" t="n"/>
+      <c r="F97" s="3" t="n"/>
+      <c r="G97" s="3" t="n"/>
+      <c r="H97" s="3" t="n"/>
+      <c r="I97" s="2" t="n"/>
+      <c r="J97" s="3" t="n"/>
+      <c r="K97" s="2" t="n"/>
+      <c r="L97" s="3" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="n">
+        <v>66</v>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>VT COSMETICS</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr">
+        <is>
+          <t>VT REEDLE SHOT 100 / Бустер-сыворотка с микроиглами</t>
+        </is>
+      </c>
+      <c r="D98" s="5" t="n">
+        <v>397</v>
+      </c>
+      <c r="E98" s="5" t="n">
+        <v>974</v>
+      </c>
+      <c r="F98" s="5" t="n">
+        <v>13568</v>
+      </c>
+      <c r="G98" s="5" t="n">
+        <v>841</v>
+      </c>
+      <c r="H98" s="5" t="n">
+        <v>967</v>
+      </c>
+      <c r="I98" s="4" t="inlineStr">
+        <is>
+          <t>FINESKIN (ответ)</t>
+        </is>
+      </c>
+      <c r="J98" s="5" t="n">
+        <v>-7</v>
+      </c>
+      <c r="K98" s="4" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="L98" s="5" t="n">
+        <v>-2637</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n"/>
+      <c r="B99" s="2" t="inlineStr">
         <is>
           <t>PETITFEE</t>
         </is>
       </c>
-      <c r="C94" s="2" t="n"/>
-      <c r="D94" s="3" t="n"/>
-      <c r="E94" s="3" t="n"/>
-      <c r="F94" s="3" t="n"/>
-      <c r="G94" s="3" t="n"/>
-      <c r="H94" s="3" t="n"/>
-      <c r="I94" s="2" t="n"/>
-      <c r="J94" s="3" t="n"/>
-      <c r="K94" s="2" t="n"/>
-      <c r="L94" s="3" t="n"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="4" t="n">
-        <v>65</v>
-      </c>
-      <c r="B95" s="4" t="inlineStr">
+      <c r="C99" s="2" t="n"/>
+      <c r="D99" s="3" t="n"/>
+      <c r="E99" s="3" t="n"/>
+      <c r="F99" s="3" t="n"/>
+      <c r="G99" s="3" t="n"/>
+      <c r="H99" s="3" t="n"/>
+      <c r="I99" s="2" t="n"/>
+      <c r="J99" s="3" t="n"/>
+      <c r="K99" s="2" t="n"/>
+      <c r="L99" s="3" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="B100" s="4" t="inlineStr">
         <is>
           <t>PETITFEE</t>
         </is>
       </c>
-      <c r="C95" s="4" t="inlineStr">
-        <is>
-          <t>PETITFEE - Gold Hydrogel Mask Pack [5pcs] / Гидрогелевая маска для лица с золотом</t>
-        </is>
-      </c>
-      <c r="D95" s="5" t="n">
-        <v>390</v>
-      </c>
-      <c r="E95" s="5" t="n">
-        <v>507</v>
-      </c>
-      <c r="F95" s="5" t="n">
-        <v>6990</v>
-      </c>
-      <c r="G95" s="5" t="n">
-        <v>433</v>
-      </c>
-      <c r="H95" s="5" t="n">
-        <v>498</v>
-      </c>
-      <c r="I95" s="4" t="inlineStr">
+      <c r="C100" s="4" t="inlineStr">
+        <is>
+          <t>PETITFEE - Bera Glucan Deep Firming Eye Patch [60ea] / Тканевые патчи для век увлажняющие</t>
+        </is>
+      </c>
+      <c r="D100" s="5" t="n">
+        <v>180</v>
+      </c>
+      <c r="E100" s="5" t="n">
+        <v>487</v>
+      </c>
+      <c r="F100" s="5" t="n">
+        <v>6790</v>
+      </c>
+      <c r="G100" s="5" t="n">
+        <v>421</v>
+      </c>
+      <c r="H100" s="5" t="n">
+        <v>484</v>
+      </c>
+      <c r="I100" s="4" t="inlineStr">
         <is>
           <t>J2K (ответ)</t>
         </is>
       </c>
-      <c r="J95" s="5" t="n">
-        <v>-9</v>
-      </c>
-      <c r="K95" s="4" t="n">
-        <v>-1.7</v>
-      </c>
-      <c r="L95" s="5" t="n">
-        <v>-3421</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="n"/>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>CELIMAX</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="n"/>
-      <c r="D96" s="3" t="n"/>
-      <c r="E96" s="3" t="n"/>
-      <c r="F96" s="3" t="n"/>
-      <c r="G96" s="3" t="n"/>
-      <c r="H96" s="3" t="n"/>
-      <c r="I96" s="2" t="n"/>
-      <c r="J96" s="3" t="n"/>
-      <c r="K96" s="2" t="n"/>
-      <c r="L96" s="3" t="n"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="4" t="n">
-        <v>66</v>
-      </c>
-      <c r="B97" s="4" t="inlineStr">
-        <is>
-          <t>CELIMAX</t>
-        </is>
-      </c>
-      <c r="C97" s="4" t="inlineStr">
-        <is>
-          <t>CELIMAX DUAL BARRIER SKIN WEARABLE CREAM [50ml]/Крем для восстановления защитного барьера кожи лица</t>
-        </is>
-      </c>
-      <c r="D97" s="5" t="n">
-        <v>90</v>
-      </c>
-      <c r="E97" s="5" t="n">
-        <v>864</v>
-      </c>
-      <c r="F97" s="5" t="n">
-        <v>11932</v>
-      </c>
-      <c r="G97" s="5" t="n">
-        <v>740</v>
-      </c>
-      <c r="H97" s="5" t="n">
-        <v>851</v>
-      </c>
-      <c r="I97" s="4" t="inlineStr">
-        <is>
-          <t>Papa Cosmetic</t>
-        </is>
-      </c>
-      <c r="J97" s="5" t="n">
-        <v>-13</v>
-      </c>
-      <c r="K97" s="4" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="L97" s="5" t="n">
-        <v>-1203</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="n"/>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>VT COSMETICS</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="n"/>
-      <c r="D98" s="3" t="n"/>
-      <c r="E98" s="3" t="n"/>
-      <c r="F98" s="3" t="n"/>
-      <c r="G98" s="3" t="n"/>
-      <c r="H98" s="3" t="n"/>
-      <c r="I98" s="2" t="n"/>
-      <c r="J98" s="3" t="n"/>
-      <c r="K98" s="2" t="n"/>
-      <c r="L98" s="3" t="n"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="4" t="n">
-        <v>67</v>
-      </c>
-      <c r="B99" s="4" t="inlineStr">
-        <is>
-          <t>VT COSMETICS</t>
-        </is>
-      </c>
-      <c r="C99" s="4" t="inlineStr">
-        <is>
-          <t>VT REEDLE SHOT 100 / Бустер-сыворотка с микроиглами</t>
-        </is>
-      </c>
-      <c r="D99" s="5" t="n">
-        <v>397</v>
-      </c>
-      <c r="E99" s="5" t="n">
-        <v>974</v>
-      </c>
-      <c r="F99" s="5" t="n">
-        <v>13568</v>
-      </c>
-      <c r="G99" s="5" t="n">
-        <v>841</v>
-      </c>
-      <c r="H99" s="5" t="n">
-        <v>967</v>
-      </c>
-      <c r="I99" s="4" t="inlineStr">
-        <is>
-          <t>FINESKIN (ответ)</t>
-        </is>
-      </c>
-      <c r="J99" s="5" t="n">
-        <v>-7</v>
-      </c>
-      <c r="K99" s="4" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="L99" s="5" t="n">
-        <v>-2637</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="n"/>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>PETITFEE</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="n"/>
-      <c r="D100" s="3" t="n"/>
-      <c r="E100" s="3" t="n"/>
-      <c r="F100" s="3" t="n"/>
-      <c r="G100" s="3" t="n"/>
-      <c r="H100" s="3" t="n"/>
-      <c r="I100" s="2" t="n"/>
-      <c r="J100" s="3" t="n"/>
-      <c r="K100" s="2" t="n"/>
-      <c r="L100" s="3" t="n"/>
+      <c r="J100" s="5" t="n">
+        <v>-3</v>
+      </c>
+      <c r="K100" s="4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="L100" s="5" t="n">
+        <v>-461</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="n">
@@ -8860,11 +8860,11 @@
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>PETITFEE - Bera Glucan Deep Firming Eye Patch [60ea] / Тканевые патчи для век увлажняющие</t>
+          <t>PETITFEE - Pink Vita Brightening Eye Patch [60ea] / Тканевые патчи для век увлажняющие</t>
         </is>
       </c>
       <c r="D101" s="5" t="n">
-        <v>180</v>
+        <v>117</v>
       </c>
       <c r="E101" s="5" t="n">
         <v>487</v>
@@ -8890,77 +8890,33 @@
         <v>-0.5</v>
       </c>
       <c r="L101" s="5" t="n">
-        <v>-461</v>
+        <v>-300</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="4" t="n">
-        <v>69</v>
-      </c>
-      <c r="B102" s="4" t="inlineStr">
-        <is>
-          <t>PETITFEE</t>
-        </is>
-      </c>
-      <c r="C102" s="4" t="inlineStr">
-        <is>
-          <t>PETITFEE - Pink Vita Brightening Eye Patch [60ea] / Тканевые патчи для век увлажняющие</t>
-        </is>
-      </c>
-      <c r="D102" s="5" t="n">
-        <v>117</v>
-      </c>
-      <c r="E102" s="5" t="n">
-        <v>487</v>
-      </c>
-      <c r="F102" s="5" t="n">
-        <v>6790</v>
-      </c>
-      <c r="G102" s="5" t="n">
-        <v>421</v>
-      </c>
-      <c r="H102" s="5" t="n">
-        <v>484</v>
-      </c>
-      <c r="I102" s="4" t="inlineStr">
-        <is>
-          <t>J2K (ответ)</t>
-        </is>
-      </c>
-      <c r="J102" s="5" t="n">
-        <v>-3</v>
-      </c>
-      <c r="K102" s="4" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="L102" s="5" t="n">
-        <v>-300</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="9" t="inlineStr"/>
-      <c r="B103" s="9" t="inlineStr">
+      <c r="A102" s="9" t="inlineStr"/>
+      <c r="B102" s="9" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="C103" s="9" t="inlineStr">
-        <is>
-          <t>позиций: 69</t>
-        </is>
-      </c>
-      <c r="D103" s="10" t="n">
-        <v>68808</v>
-      </c>
-      <c r="E103" s="10" t="inlineStr"/>
-      <c r="F103" s="10" t="inlineStr"/>
-      <c r="G103" s="10" t="inlineStr"/>
-      <c r="H103" s="10" t="inlineStr"/>
-      <c r="I103" s="9" t="inlineStr"/>
-      <c r="J103" s="10" t="inlineStr"/>
-      <c r="K103" s="9" t="inlineStr"/>
-      <c r="L103" s="10" t="n">
-        <v>-5274370</v>
+      <c r="C102" s="9" t="inlineStr">
+        <is>
+          <t>позиций: 68</t>
+        </is>
+      </c>
+      <c r="D102" s="10" t="n">
+        <v>68738</v>
+      </c>
+      <c r="E102" s="10" t="inlineStr"/>
+      <c r="F102" s="10" t="inlineStr"/>
+      <c r="G102" s="10" t="inlineStr"/>
+      <c r="H102" s="10" t="inlineStr"/>
+      <c r="I102" s="9" t="inlineStr"/>
+      <c r="J102" s="10" t="inlineStr"/>
+      <c r="K102" s="9" t="inlineStr"/>
+      <c r="L102" s="10" t="n">
+        <v>-3399947</v>
       </c>
     </row>
   </sheetData>
@@ -8974,7 +8930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L38"/>
+  <dimension ref="A1:L39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -10142,187 +10098,231 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
+          <t>CELIMAX PORE+DARK SPOT BRIGHTENING SERUM_30ml [30ml]/Сыворотка для выравнивания тона и рельефа кожи лица</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="n">
+        <v>70</v>
+      </c>
+      <c r="E33" s="7" t="n">
+        <v>688</v>
+      </c>
+      <c r="F33" s="7" t="n">
+        <v>9900</v>
+      </c>
+      <c r="G33" s="7" t="n">
+        <v>614</v>
+      </c>
+      <c r="H33" s="7" t="n">
+        <v>706</v>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>G&amp;E Global</t>
+        </is>
+      </c>
+      <c r="J33" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="K33" s="6" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L33" s="7" t="n">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>CELIMAX</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
           <t>CELIMAX PORE+DARK SPOT BRIGHTENING PAD [100ml / 40pads]/Тонер-пэды для выравнивания тона и рельефа кожи</t>
         </is>
       </c>
-      <c r="D33" s="7" t="n">
+      <c r="D34" s="7" t="n">
         <v>1375</v>
       </c>
-      <c r="E33" s="7" t="n">
+      <c r="E34" s="7" t="n">
         <v>556</v>
       </c>
-      <c r="F33" s="7" t="n">
+      <c r="F34" s="7" t="n">
         <v>7950</v>
       </c>
-      <c r="G33" s="7" t="n">
+      <c r="G34" s="7" t="n">
         <v>493</v>
       </c>
-      <c r="H33" s="7" t="n">
+      <c r="H34" s="7" t="n">
         <v>567</v>
       </c>
-      <c r="I33" s="6" t="inlineStr">
+      <c r="I34" s="6" t="inlineStr">
         <is>
           <t>G&amp;E Global</t>
         </is>
       </c>
-      <c r="J33" s="7" t="n">
+      <c r="J34" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="K33" s="6" t="n">
+      <c r="K34" s="6" t="n">
         <v>1.9</v>
       </c>
-      <c r="L33" s="7" t="n">
+      <c r="L34" s="7" t="n">
         <v>14651</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="n"/>
-      <c r="B34" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="n"/>
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>VT COSMETICS</t>
         </is>
       </c>
-      <c r="C34" s="2" t="n"/>
-      <c r="D34" s="3" t="n"/>
-      <c r="E34" s="3" t="n"/>
-      <c r="F34" s="3" t="n"/>
-      <c r="G34" s="3" t="n"/>
-      <c r="H34" s="3" t="n"/>
-      <c r="I34" s="2" t="n"/>
-      <c r="J34" s="3" t="n"/>
-      <c r="K34" s="2" t="n"/>
-      <c r="L34" s="3" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="6" t="n">
-        <v>22</v>
-      </c>
-      <c r="B35" s="6" t="inlineStr">
+      <c r="C35" s="2" t="n"/>
+      <c r="D35" s="3" t="n"/>
+      <c r="E35" s="3" t="n"/>
+      <c r="F35" s="3" t="n"/>
+      <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
+      <c r="I35" s="2" t="n"/>
+      <c r="J35" s="3" t="n"/>
+      <c r="K35" s="2" t="n"/>
+      <c r="L35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>VT COSMETICS</t>
         </is>
       </c>
-      <c r="C35" s="6" t="inlineStr">
+      <c r="C36" s="6" t="inlineStr">
         <is>
           <t>VT PDRN ESSENCE 100 / Укрепляющая бустер-эссенция с ПДРН</t>
         </is>
       </c>
-      <c r="D35" s="7" t="n">
+      <c r="D36" s="7" t="n">
         <v>1009</v>
       </c>
-      <c r="E35" s="7" t="n">
+      <c r="E36" s="7" t="n">
         <v>1336</v>
       </c>
-      <c r="F35" s="7" t="n">
+      <c r="F36" s="7" t="n">
         <v>19080</v>
       </c>
-      <c r="G35" s="7" t="n">
+      <c r="G36" s="7" t="n">
         <v>1183</v>
       </c>
-      <c r="H35" s="7" t="n">
+      <c r="H36" s="7" t="n">
         <v>1360</v>
       </c>
-      <c r="I35" s="6" t="inlineStr">
+      <c r="I36" s="6" t="inlineStr">
         <is>
           <t>FINESKIN (ответ)</t>
         </is>
       </c>
-      <c r="J35" s="7" t="n">
+      <c r="J36" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="K35" s="6" t="n">
+      <c r="K36" s="6" t="n">
         <v>1.8</v>
       </c>
-      <c r="L35" s="7" t="n">
+      <c r="L36" s="7" t="n">
         <v>24674</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="n"/>
-      <c r="B36" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="n"/>
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>PETITFEE</t>
         </is>
       </c>
-      <c r="C36" s="2" t="n"/>
-      <c r="D36" s="3" t="n"/>
-      <c r="E36" s="3" t="n"/>
-      <c r="F36" s="3" t="n"/>
-      <c r="G36" s="3" t="n"/>
-      <c r="H36" s="3" t="n"/>
-      <c r="I36" s="2" t="n"/>
-      <c r="J36" s="3" t="n"/>
-      <c r="K36" s="2" t="n"/>
-      <c r="L36" s="3" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="6" t="n">
-        <v>23</v>
-      </c>
-      <c r="B37" s="6" t="inlineStr">
+      <c r="C37" s="2" t="n"/>
+      <c r="D37" s="3" t="n"/>
+      <c r="E37" s="3" t="n"/>
+      <c r="F37" s="3" t="n"/>
+      <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
+      <c r="I37" s="2" t="n"/>
+      <c r="J37" s="3" t="n"/>
+      <c r="K37" s="2" t="n"/>
+      <c r="L37" s="3" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>PETITFEE</t>
         </is>
       </c>
-      <c r="C37" s="6" t="inlineStr">
+      <c r="C38" s="6" t="inlineStr">
         <is>
           <t>PETITFEE - Cacao Energizing Hydrogel Mask Pack [5pcs] / Тонизирующая гидрогелевая маска для лица с экстрактом какао</t>
         </is>
       </c>
-      <c r="D37" s="7" t="n">
+      <c r="D38" s="7" t="n">
         <v>90</v>
       </c>
-      <c r="E37" s="7" t="n">
+      <c r="E38" s="7" t="n">
         <v>497</v>
       </c>
-      <c r="F37" s="7" t="n">
+      <c r="F38" s="7" t="n">
         <v>6990</v>
       </c>
-      <c r="G37" s="7" t="n">
+      <c r="G38" s="7" t="n">
         <v>433</v>
       </c>
-      <c r="H37" s="7" t="n">
+      <c r="H38" s="7" t="n">
         <v>498</v>
       </c>
-      <c r="I37" s="6" t="inlineStr">
+      <c r="I38" s="6" t="inlineStr">
         <is>
           <t>J2K (ответ)</t>
         </is>
       </c>
-      <c r="J37" s="7" t="n">
+      <c r="J38" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="K37" s="6" t="n">
+      <c r="K38" s="6" t="n">
         <v>0.3</v>
       </c>
-      <c r="L37" s="7" t="n">
+      <c r="L38" s="7" t="n">
         <v>137</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="9" t="inlineStr"/>
-      <c r="B38" s="9" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr"/>
+      <c r="B39" s="9" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="C38" s="9" t="inlineStr">
-        <is>
-          <t>позиций: 23</t>
-        </is>
-      </c>
-      <c r="D38" s="10" t="n">
-        <v>27450</v>
-      </c>
-      <c r="E38" s="10" t="inlineStr"/>
-      <c r="F38" s="10" t="inlineStr"/>
-      <c r="G38" s="10" t="inlineStr"/>
-      <c r="H38" s="10" t="inlineStr"/>
-      <c r="I38" s="9" t="inlineStr"/>
-      <c r="J38" s="10" t="inlineStr"/>
-      <c r="K38" s="9" t="inlineStr"/>
-      <c r="L38" s="10" t="n">
-        <v>2465356</v>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>позиций: 24</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="n">
+        <v>27520</v>
+      </c>
+      <c r="E39" s="10" t="inlineStr"/>
+      <c r="F39" s="10" t="inlineStr"/>
+      <c r="G39" s="10" t="inlineStr"/>
+      <c r="H39" s="10" t="inlineStr"/>
+      <c r="I39" s="9" t="inlineStr"/>
+      <c r="J39" s="10" t="inlineStr"/>
+      <c r="K39" s="9" t="inlineStr"/>
+      <c r="L39" s="10" t="n">
+        <v>2466636</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Склад против Кореи.xlsx
+++ b/outputs/Склад против Кореи.xlsx
@@ -574,27 +574,27 @@
         <v>864</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>11932</v>
+        <v>11900</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>Papa Cosmetic</t>
+          <t>PAPA COSMETIC (ответ)</t>
         </is>
       </c>
       <c r="J3" s="5" t="n">
-        <v>-13</v>
+        <v>-16</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>-1.5</v>
+        <v>-1.8</v>
       </c>
       <c r="L3" s="5" t="n">
-        <v>-1203</v>
+        <v>-1408</v>
       </c>
     </row>
     <row r="4">
@@ -882,27 +882,27 @@
         <v>720</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>9886</v>
+        <v>9875</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>Papa Cosmetic</t>
+          <t>PAPA COSMETIC (ответ)</t>
         </is>
       </c>
       <c r="J10" s="5" t="n">
         <v>-15</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-2</v>
+        <v>-2.2</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>-338</v>
+        <v>-356</v>
       </c>
     </row>
     <row r="11">
@@ -1506,36 +1506,48 @@
       <c r="L26" s="3" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" t="n">
+      <c r="A27" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>ETUDE</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>ETUDE - Baking Powder Crunch Pore Scrub [200ml] / Очищающий скраб для лица с содой</t>
         </is>
       </c>
-      <c r="D27" s="8" t="n">
+      <c r="D27" s="5" t="n">
         <v>7279</v>
       </c>
-      <c r="E27" s="8" t="n">
+      <c r="E27" s="5" t="n">
         <v>361</v>
       </c>
-      <c r="F27" s="8" t="inlineStr"/>
-      <c r="G27" s="8" t="inlineStr"/>
-      <c r="H27" s="8" t="inlineStr"/>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>нет предложения</t>
-        </is>
-      </c>
-      <c r="J27" s="8" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" s="8" t="inlineStr"/>
+      <c r="F27" s="5" t="n">
+        <v>4400</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>273</v>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>314</v>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>PAPA COSMETIC (ответ)</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="n">
+        <v>-47</v>
+      </c>
+      <c r="K27" s="4" t="n">
+        <v>-13.1</v>
+      </c>
+      <c r="L27" s="5" t="n">
+        <v>-344369</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n"/>
@@ -3578,100 +3590,136 @@
       <c r="L78" s="3" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" t="n">
+      <c r="A79" s="4" t="n">
         <v>67</v>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B79" s="4" t="inlineStr">
         <is>
           <t>MANYO</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C79" s="4" t="inlineStr">
         <is>
           <t>MANYO - Bifida Biome Ampoule Lotion [300ml] / Укрепляющий лосьон с бифидобактериями</t>
         </is>
       </c>
-      <c r="D79" s="8" t="n">
+      <c r="D79" s="5" t="n">
         <v>624</v>
       </c>
-      <c r="E79" s="8" t="n">
+      <c r="E79" s="5" t="n">
         <v>735</v>
       </c>
-      <c r="F79" s="8" t="inlineStr"/>
-      <c r="G79" s="8" t="inlineStr"/>
-      <c r="H79" s="8" t="inlineStr"/>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>нет предложения</t>
-        </is>
-      </c>
-      <c r="J79" s="8" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" s="8" t="inlineStr"/>
+      <c r="F79" s="5" t="n">
+        <v>9500</v>
+      </c>
+      <c r="G79" s="5" t="n">
+        <v>589</v>
+      </c>
+      <c r="H79" s="5" t="n">
+        <v>677</v>
+      </c>
+      <c r="I79" s="4" t="inlineStr">
+        <is>
+          <t>PAPA COSMETIC (ответ)</t>
+        </is>
+      </c>
+      <c r="J79" s="5" t="n">
+        <v>-58</v>
+      </c>
+      <c r="K79" s="4" t="n">
+        <v>-7.9</v>
+      </c>
+      <c r="L79" s="5" t="n">
+        <v>-36186</v>
+      </c>
     </row>
     <row r="80">
-      <c r="A80" t="n">
+      <c r="A80" s="4" t="n">
         <v>68</v>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B80" s="4" t="inlineStr">
         <is>
           <t>MANYO</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="C80" s="4" t="inlineStr">
         <is>
           <t>MANYO - Bifida Biome Complex Ampoule [50ml] / Антивозрастная сыворотка для лица</t>
         </is>
       </c>
-      <c r="D80" s="8" t="n">
+      <c r="D80" s="5" t="n">
         <v>1355</v>
       </c>
-      <c r="E80" s="8" t="n">
+      <c r="E80" s="5" t="n">
         <v>900</v>
       </c>
-      <c r="F80" s="8" t="inlineStr"/>
-      <c r="G80" s="8" t="inlineStr"/>
-      <c r="H80" s="8" t="inlineStr"/>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>нет предложения</t>
-        </is>
-      </c>
-      <c r="J80" s="8" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" s="8" t="inlineStr"/>
+      <c r="F80" s="5" t="n">
+        <v>8740</v>
+      </c>
+      <c r="G80" s="5" t="n">
+        <v>542</v>
+      </c>
+      <c r="H80" s="5" t="n">
+        <v>623</v>
+      </c>
+      <c r="I80" s="4" t="inlineStr">
+        <is>
+          <t>PAPA COSMETIC (ответ)</t>
+        </is>
+      </c>
+      <c r="J80" s="5" t="n">
+        <v>-277</v>
+      </c>
+      <c r="K80" s="4" t="n">
+        <v>-30.7</v>
+      </c>
+      <c r="L80" s="5" t="n">
+        <v>-374817</v>
+      </c>
     </row>
     <row r="81">
-      <c r="A81" t="n">
+      <c r="A81" s="6" t="n">
         <v>69</v>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B81" s="6" t="inlineStr">
         <is>
           <t>MANYO</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C81" s="6" t="inlineStr">
         <is>
           <t>MANYO - Galac Whitening Vita Serum [50ml] / Осветляющая сыворотка с Витамином C</t>
         </is>
       </c>
-      <c r="D81" s="8" t="n">
+      <c r="D81" s="7" t="n">
         <v>759</v>
       </c>
-      <c r="E81" s="8" t="n">
+      <c r="E81" s="7" t="n">
         <v>647</v>
       </c>
-      <c r="F81" s="8" t="inlineStr"/>
-      <c r="G81" s="8" t="inlineStr"/>
-      <c r="H81" s="8" t="inlineStr"/>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>нет предложения</t>
-        </is>
-      </c>
-      <c r="J81" s="8" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" s="8" t="inlineStr"/>
+      <c r="F81" s="7" t="n">
+        <v>9500</v>
+      </c>
+      <c r="G81" s="7" t="n">
+        <v>589</v>
+      </c>
+      <c r="H81" s="7" t="n">
+        <v>677</v>
+      </c>
+      <c r="I81" s="6" t="inlineStr">
+        <is>
+          <t>PAPA COSMETIC (ответ)</t>
+        </is>
+      </c>
+      <c r="J81" s="7" t="n">
+        <v>31</v>
+      </c>
+      <c r="K81" s="6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L81" s="7" t="n">
+        <v>23165</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="n">
@@ -3694,92 +3742,116 @@
         <v>853</v>
       </c>
       <c r="F82" s="5" t="n">
-        <v>9750</v>
+        <v>9500</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>604</v>
+        <v>589</v>
       </c>
       <c r="H82" s="5" t="n">
-        <v>695</v>
+        <v>677</v>
       </c>
       <c r="I82" s="4" t="inlineStr">
         <is>
-          <t>Классик</t>
+          <t>PAPA COSMETIC (ответ)</t>
         </is>
       </c>
       <c r="J82" s="5" t="n">
-        <v>-158</v>
+        <v>-176</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>-18.5</v>
+        <v>-20.6</v>
       </c>
       <c r="L82" s="5" t="n">
-        <v>-12626</v>
+        <v>-14052</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="n">
+      <c r="A83" s="4" t="n">
         <v>71</v>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B83" s="4" t="inlineStr">
         <is>
           <t>MANYO</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="C83" s="4" t="inlineStr">
         <is>
           <t>MANYO BIFIDA COMPLEX AMPOULE GEL CLEANSER [400ml] / Гель для умывания с бифидобактериями</t>
         </is>
       </c>
-      <c r="D83" s="8" t="n">
+      <c r="D83" s="5" t="n">
         <v>650</v>
       </c>
-      <c r="E83" s="8" t="n">
+      <c r="E83" s="5" t="n">
         <v>740</v>
       </c>
-      <c r="F83" s="8" t="inlineStr"/>
-      <c r="G83" s="8" t="inlineStr"/>
-      <c r="H83" s="8" t="inlineStr"/>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>нет предложения</t>
-        </is>
-      </c>
-      <c r="J83" s="8" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" s="8" t="inlineStr"/>
+      <c r="F83" s="5" t="n">
+        <v>8740</v>
+      </c>
+      <c r="G83" s="5" t="n">
+        <v>542</v>
+      </c>
+      <c r="H83" s="5" t="n">
+        <v>623</v>
+      </c>
+      <c r="I83" s="4" t="inlineStr">
+        <is>
+          <t>PAPA COSMETIC (ответ)</t>
+        </is>
+      </c>
+      <c r="J83" s="5" t="n">
+        <v>-117</v>
+      </c>
+      <c r="K83" s="4" t="n">
+        <v>-15.8</v>
+      </c>
+      <c r="L83" s="5" t="n">
+        <v>-75886</v>
+      </c>
     </row>
     <row r="84">
-      <c r="A84" t="n">
+      <c r="A84" s="6" t="n">
         <v>72</v>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B84" s="6" t="inlineStr">
         <is>
           <t>MANYO</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="C84" s="6" t="inlineStr">
         <is>
           <t>MANYO BIFIDA INFUSION SHOT AMPOULE 1DX [50ml] / Сыворотка с микроиглами и пробиотиками</t>
         </is>
       </c>
-      <c r="D84" s="8" t="n">
+      <c r="D84" s="7" t="n">
         <v>614</v>
       </c>
-      <c r="E84" s="8" t="n">
+      <c r="E84" s="7" t="n">
         <v>997</v>
       </c>
-      <c r="F84" s="8" t="inlineStr"/>
-      <c r="G84" s="8" t="inlineStr"/>
-      <c r="H84" s="8" t="inlineStr"/>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>нет предложения</t>
-        </is>
-      </c>
-      <c r="J84" s="8" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" s="8" t="inlineStr"/>
+      <c r="F84" s="7" t="n">
+        <v>14820</v>
+      </c>
+      <c r="G84" s="7" t="n">
+        <v>919</v>
+      </c>
+      <c r="H84" s="7" t="n">
+        <v>1057</v>
+      </c>
+      <c r="I84" s="6" t="inlineStr">
+        <is>
+          <t>PAPA COSMETIC (ответ)</t>
+        </is>
+      </c>
+      <c r="J84" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="K84" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="L84" s="7" t="n">
+        <v>36788</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n"/>
@@ -5232,7 +5304,7 @@
       <c r="J121" s="10" t="inlineStr"/>
       <c r="K121" s="9" t="inlineStr"/>
       <c r="L121" s="10" t="n">
-        <v>-933311</v>
+        <v>-1706265</v>
       </c>
     </row>
   </sheetData>
@@ -5246,7 +5318,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L102"/>
+  <dimension ref="A1:L110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5354,7 +5426,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT - Hyaluronic Acid Real Ampoule Mask [27ml] / Ампульная маска с гиалуроновой кислотой</t>
+          <t>JIGOTT - Pearl Real Ampoule Mask [27ml] / ампульная маска для лица с жемчугом</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
@@ -5398,7 +5470,7 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT - Camellia Real Ampoule Mask [27ml] / Ампульная маска с экстрактом камелии</t>
+          <t>JIGOTT - Vitamin Real Ampoule Mask [27ml] / Ампульная маска с витаминами</t>
         </is>
       </c>
       <c r="D4" s="5" t="n">
@@ -5442,7 +5514,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT - Caviar Real Ampoule Mask [27ml] / Ампульная маска с экстрактом икры</t>
+          <t>JIGOTT - Red Ginseng Real Ampoule Mask [27ml] / Ампульная маска с красным женьшенем</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
@@ -5486,7 +5558,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT - Collagen Real Ampoule Mask [27ml] / Ампульная маска с коллагеном</t>
+          <t>JIGOTT - Potato Real Ampoule Mask [27ml] / Ампульная маска с экстрактом картофеля</t>
         </is>
       </c>
       <c r="D6" s="5" t="n">
@@ -5530,7 +5602,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT - Cucumber Real Ampoule Mask [27ml] / Тканевая маска с экстрактом огурца</t>
+          <t>JIGOTT - Pomegranate Real Ampoule Mask [27ml] / Ампульная маска с экстрактом граната</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
@@ -5574,7 +5646,7 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT - Green Tea Real Ampoule Mask [27ml] / Ампульная маска с экстрактом зеленого чая</t>
+          <t>JIGOTT - Placenta Real Ampoule Mask [27ml] / Ампульная маска с плацентой</t>
         </is>
       </c>
       <c r="D8" s="5" t="n">
@@ -5618,7 +5690,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT - Honey Real Ampoule Mask [27ml] / Ампульная маска с экстрактом меда</t>
+          <t>JIGOTT - Hyaluronic Acid Real Ampoule Mask [27ml] / Ампульная маска с гиалуроновой кислотой</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -5662,7 +5734,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT - Black Snail Real Ampoule Mask [27ml] / Ампульная маска с экстрактом слизи черной улитки</t>
+          <t>JIGOTT - Honey Real Ampoule Mask [27ml] / Ампульная маска с экстрактом меда</t>
         </is>
       </c>
       <c r="D10" s="5" t="n">
@@ -5706,7 +5778,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT - Lotus Real Ampoule Mask [27ml] / Ампульная маска с экстрактом лотоса</t>
+          <t>JIGOTT - Green Tea Real Ampoule Mask [27ml] / Ампульная маска с экстрактом зеленого чая</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -5750,7 +5822,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT - Placenta Real Ampoule Mask [27ml] / Ампульная маска с плацентой</t>
+          <t>JIGOTT - Cucumber Real Ampoule Mask [27ml] / Тканевая маска с экстрактом огурца</t>
         </is>
       </c>
       <c r="D12" s="5" t="n">
@@ -5794,7 +5866,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT - Pomegranate Real Ampoule Mask [27ml] / Ампульная маска с экстрактом граната</t>
+          <t>JIGOTT - Collagen Real Ampoule Mask [27ml] / Ампульная маска с коллагеном</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
@@ -5838,7 +5910,7 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT - Potato Real Ampoule Mask [27ml] / Ампульная маска с экстрактом картофеля</t>
+          <t>JIGOTT - Caviar Real Ampoule Mask [27ml] / Ампульная маска с экстрактом икры</t>
         </is>
       </c>
       <c r="D14" s="5" t="n">
@@ -5882,7 +5954,7 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT - Red Ginseng Real Ampoule Mask [27ml] / Ампульная маска с красным женьшенем</t>
+          <t>JIGOTT - Camellia Real Ampoule Mask [27ml] / Ампульная маска с экстрактом камелии</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
@@ -5926,7 +5998,7 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT - Vitamin Real Ampoule Mask [27ml] / Ампульная маска с витаминами</t>
+          <t>JIGOTT - Black Snail Real Ampoule Mask [27ml] / Ампульная маска с экстрактом слизи черной улитки</t>
         </is>
       </c>
       <c r="D16" s="5" t="n">
@@ -5970,7 +6042,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT - Pearl Real Ampoule Mask [27ml] / ампульная маска для лица с жемчугом</t>
+          <t>JIGOTT - Aloe Real Ampoule Mask [27ml] / Ампульная маска с экстрактом алое</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
@@ -6014,7 +6086,7 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT - Aloe Real Ampoule Mask [27ml] / Ампульная маска с экстрактом алое</t>
+          <t>JIGOTT - Lotus Real Ampoule Mask [27ml] / Ампульная маска с экстрактом лотоса</t>
         </is>
       </c>
       <c r="D18" s="5" t="n">
@@ -6058,7 +6130,7 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT - Daily Real Cica Toner [300ml] / Тонер для лица с центеллой азиатской</t>
+          <t>JIGOTT - Ultimate Real Collagen Toner [300ml] / тонер с коллагеном антивозрастной</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
@@ -6102,7 +6174,7 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT - Ultimate Real Collagen Toner [300ml] / тонер с коллагеном антивозрастной</t>
+          <t>JIGOTT - Daily Real Cica Toner [300ml] / Тонер для лица с центеллой азиатской</t>
         </is>
       </c>
       <c r="D20" s="5" t="n">
@@ -6377,7 +6449,7 @@
       <c r="A27" s="2" t="n"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>SOME BY MI</t>
+          <t>MANYO</t>
         </is>
       </c>
       <c r="C27" s="2" t="n"/>
@@ -6397,49 +6469,49 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>SOME BY MI</t>
+          <t>MANYO</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>SOME BY MI - AHA-BHA-PHA 30 Days Miracle Cream [60g] / Крем для лица</t>
+          <t>MANYO - Bifida Biome Complex Ampoule [50ml] / Антивозрастная сыворотка для лица</t>
         </is>
       </c>
       <c r="D28" s="5" t="n">
-        <v>55</v>
+        <v>1355</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>1057</v>
+        <v>900</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>10685</v>
+        <v>8740</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>662</v>
+        <v>542</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>762</v>
+        <v>623</v>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>FINESKIN (ответ)</t>
+          <t>PAPA COSMETIC (ответ)</t>
         </is>
       </c>
       <c r="J28" s="5" t="n">
-        <v>-295</v>
+        <v>-277</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-27.9</v>
+        <v>-30.7</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>-16245</v>
+        <v>-374817</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>ROUND LAB</t>
+          <t>SOME BY MI</t>
         </is>
       </c>
       <c r="C29" s="2" t="n"/>
@@ -6459,49 +6531,49 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>ROUND LAB</t>
+          <t>SOME BY MI</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>ROUND LAB PINE CALMING CICA AMPOULE_30ml - Сыворотка для жирной кожи лица увлажняющая с центеллой</t>
+          <t>SOME BY MI - AHA-BHA-PHA 30 Days Miracle Cream [60g] / Крем для лица</t>
         </is>
       </c>
       <c r="D30" s="5" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>820</v>
+        <v>1057</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>8293</v>
+        <v>10685</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>514</v>
+        <v>662</v>
       </c>
       <c r="H30" s="5" t="n">
-        <v>591</v>
+        <v>762</v>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>G&amp;E Global</t>
+          <t>FINESKIN (ответ)</t>
         </is>
       </c>
       <c r="J30" s="5" t="n">
-        <v>-228</v>
+        <v>-295</v>
       </c>
       <c r="K30" s="4" t="n">
         <v>-27.9</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>-7310</v>
+        <v>-16245</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>ROUND LAB</t>
         </is>
       </c>
       <c r="C31" s="2" t="n"/>
@@ -6521,49 +6593,49 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>ROUND LAB</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>PETITFEE - Aura Quartz Hydrogel Eye Patch [60ea]</t>
+          <t>ROUND LAB PINE CALMING CICA AMPOULE_30ml - Сыворотка для жирной кожи лица увлажняющая с центеллой</t>
         </is>
       </c>
       <c r="D32" s="5" t="n">
-        <v>89</v>
+        <v>32</v>
       </c>
       <c r="E32" s="5" t="n">
+        <v>820</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>8293</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>514</v>
+      </c>
+      <c r="H32" s="5" t="n">
         <v>591</v>
       </c>
-      <c r="F32" s="5" t="n">
-        <v>6190</v>
-      </c>
-      <c r="G32" s="5" t="n">
-        <v>384</v>
-      </c>
-      <c r="H32" s="5" t="n">
-        <v>441</v>
-      </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>J2K (ответ)</t>
+          <t>G&amp;E Global</t>
         </is>
       </c>
       <c r="J32" s="5" t="n">
-        <v>-150</v>
+        <v>-228</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-25.4</v>
+        <v>-27.9</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>-13345</v>
+        <v>-7310</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>PETITFEE</t>
         </is>
       </c>
       <c r="C33" s="2" t="n"/>
@@ -6583,49 +6655,49 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>PETITFEE</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT - Snail Lifting Cream [70ml] / Крем для лица увлажняющий антивозрастной</t>
+          <t>PETITFEE - Aura Quartz Hydrogel Eye Patch [60ea]</t>
         </is>
       </c>
       <c r="D34" s="5" t="n">
-        <v>7463</v>
+        <v>89</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>202</v>
+        <v>591</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>2120</v>
+        <v>6190</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>131</v>
+        <v>384</v>
       </c>
       <c r="H34" s="5" t="n">
-        <v>151</v>
+        <v>441</v>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>FINESKIN (ответ)</t>
+          <t>J2K (ответ)</t>
         </is>
       </c>
       <c r="J34" s="5" t="n">
-        <v>-51</v>
+        <v>-150</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-25.3</v>
+        <v>-25.4</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>-381464</v>
+        <v>-13345</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>JMSOLUTION</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C35" s="2" t="n"/>
@@ -6645,91 +6717,65 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
+          <t>JIGOTT</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>JIGOTT - Snail Lifting Cream [70ml] / Крем для лица увлажняющий антивозрастной</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>7463</v>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>202</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>2120</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>131</v>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>151</v>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>FINESKIN (ответ)</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="n">
+        <v>-51</v>
+      </c>
+      <c r="K36" s="4" t="n">
+        <v>-25.3</v>
+      </c>
+      <c r="L36" s="5" t="n">
+        <v>-381464</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>JMSOLUTION</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>JMSOLUTION - Active Birds Nest Moisture Mask [30ml*10ea] / Ультратонкая тканевая маска с ласточкиным гнездом</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="n">
-        <v>110</v>
-      </c>
-      <c r="E36" s="5" t="n">
-        <v>342</v>
-      </c>
-      <c r="F36" s="5" t="n">
-        <v>3604</v>
-      </c>
-      <c r="G36" s="5" t="n">
-        <v>223</v>
-      </c>
-      <c r="H36" s="5" t="n">
-        <v>257</v>
-      </c>
-      <c r="I36" s="4" t="inlineStr">
-        <is>
-          <t>FINESKIN (ответ)</t>
-        </is>
-      </c>
-      <c r="J36" s="5" t="n">
-        <v>-85</v>
-      </c>
-      <c r="K36" s="4" t="n">
-        <v>-24.9</v>
-      </c>
-      <c r="L36" s="5" t="n">
-        <v>-9384</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="4" t="n">
-        <v>29</v>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>JMSOLUTION</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>JMSOLUTION - Active Jellyfish Vital Mask [30ml*10ea] / Ультратонкая тканевая маска с экстрактом медузы</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="n">
-        <v>110</v>
-      </c>
-      <c r="E37" s="5" t="n">
-        <v>342</v>
-      </c>
-      <c r="F37" s="5" t="n">
-        <v>3604</v>
-      </c>
-      <c r="G37" s="5" t="n">
-        <v>223</v>
-      </c>
-      <c r="H37" s="5" t="n">
-        <v>257</v>
-      </c>
-      <c r="I37" s="4" t="inlineStr">
-        <is>
-          <t>FINESKIN (ответ)</t>
-        </is>
-      </c>
-      <c r="J37" s="5" t="n">
-        <v>-85</v>
-      </c>
-      <c r="K37" s="4" t="n">
-        <v>-24.9</v>
-      </c>
-      <c r="L37" s="5" t="n">
-        <v>-9384</v>
-      </c>
+      <c r="C37" s="2" t="n"/>
+      <c r="D37" s="3" t="n"/>
+      <c r="E37" s="3" t="n"/>
+      <c r="F37" s="3" t="n"/>
+      <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
+      <c r="I37" s="2" t="n"/>
+      <c r="J37" s="3" t="n"/>
+      <c r="K37" s="2" t="n"/>
+      <c r="L37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
@@ -6738,7 +6784,7 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>JMSOLUTION ACTIVE BLACK CAVIAR MASK [30ml*10ea] / Ультратонкая тканевая маска с черной икрой</t>
+          <t>JMSOLUTION GREEN DEAR TIGER CICA MASK PURE 30ml*10ea / Регенерирующая маска для лица с центеллой</t>
         </is>
       </c>
       <c r="D38" s="5" t="n">
@@ -6773,7 +6819,7 @@
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
@@ -6782,7 +6828,7 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>JMSOLUTION GREEN DEAR TIGER CICA MASK PURE 30ml*10ea / Регенерирующая маска для лица с центеллой</t>
+          <t>JMSOLUTION ACTIVE BLACK CAVIAR MASK [30ml*10ea] / Ультратонкая тканевая маска с черной икрой</t>
         </is>
       </c>
       <c r="D39" s="5" t="n">
@@ -6817,7 +6863,7 @@
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
@@ -6826,7 +6872,7 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>JMSOLUTION - Active Golden Caviar Nourishing Mask [30ml*10ea] / Ультратонкая тканевая маска с золотом и икрой</t>
+          <t>JMSOLUTION - Active Jellyfish Vital Mask [30ml*10ea] / Ультратонкая тканевая маска с экстрактом медузы</t>
         </is>
       </c>
       <c r="D40" s="5" t="n">
@@ -6860,22 +6906,48 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n"/>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>ROUND LAB</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="n"/>
-      <c r="D41" s="3" t="n"/>
-      <c r="E41" s="3" t="n"/>
-      <c r="F41" s="3" t="n"/>
-      <c r="G41" s="3" t="n"/>
-      <c r="H41" s="3" t="n"/>
-      <c r="I41" s="2" t="n"/>
-      <c r="J41" s="3" t="n"/>
-      <c r="K41" s="2" t="n"/>
-      <c r="L41" s="3" t="n"/>
+      <c r="A41" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>JMSOLUTION</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>JMSOLUTION - Active Golden Caviar Nourishing Mask [30ml*10ea] / Ультратонкая тканевая маска с золотом и икрой</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>110</v>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>342</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>3604</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>223</v>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v>257</v>
+      </c>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>FINESKIN (ответ)</t>
+        </is>
+      </c>
+      <c r="J41" s="5" t="n">
+        <v>-85</v>
+      </c>
+      <c r="K41" s="4" t="n">
+        <v>-24.9</v>
+      </c>
+      <c r="L41" s="5" t="n">
+        <v>-9384</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
@@ -6883,49 +6955,49 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>ROUND LAB</t>
+          <t>JMSOLUTION</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>ROUND LAB BIRCH JUICE MOISTURIZING CREAM_80ml -Увлажняющий крем с березовым соком</t>
+          <t>JMSOLUTION - Active Birds Nest Moisture Mask [30ml*10ea] / Ультратонкая тканевая маска с ласточкиным гнездом</t>
         </is>
       </c>
       <c r="D42" s="5" t="n">
-        <v>259</v>
+        <v>110</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>1093</v>
+        <v>342</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>11702</v>
+        <v>3604</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>726</v>
+        <v>223</v>
       </c>
       <c r="H42" s="5" t="n">
-        <v>834</v>
+        <v>257</v>
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>G&amp;E Global</t>
+          <t>FINESKIN (ответ)</t>
         </is>
       </c>
       <c r="J42" s="5" t="n">
-        <v>-259</v>
+        <v>-85</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>-23.7</v>
+        <v>-24.9</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>-66979</v>
+        <v>-9384</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n"/>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>HEIMISH</t>
+          <t>ROUND LAB</t>
         </is>
       </c>
       <c r="C43" s="2" t="n"/>
@@ -6945,49 +7017,49 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>HEIMISH</t>
+          <t>ROUND LAB</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>HEIMISH - Artless Glow Base SPF50+ PA+++(Renew) [40ml] / База под макияж SPF50+ PA+++</t>
+          <t>ROUND LAB BIRCH JUICE MOISTURIZING CREAM_80ml -Увлажняющий крем с березовым соком</t>
         </is>
       </c>
       <c r="D44" s="5" t="n">
-        <v>941</v>
+        <v>259</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>770</v>
+        <v>1093</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>8565</v>
+        <v>11702</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>531</v>
+        <v>726</v>
       </c>
       <c r="H44" s="5" t="n">
-        <v>611</v>
+        <v>834</v>
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>Классик</t>
+          <t>G&amp;E Global</t>
         </is>
       </c>
       <c r="J44" s="5" t="n">
-        <v>-160</v>
+        <v>-259</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>-20.7</v>
+        <v>-23.7</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>-150368</v>
+        <v>-66979</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n"/>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>HEIMISH</t>
         </is>
       </c>
       <c r="C45" s="2" t="n"/>
@@ -7007,42 +7079,42 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>HEIMISH</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT - Snail Reparing Cream [100ml] / Крем для лица увлажняющий антивозрастной с муцином улитки</t>
+          <t>HEIMISH - Artless Glow Base SPF50+ PA+++(Renew) [40ml] / База под макияж SPF50+ PA+++</t>
         </is>
       </c>
       <c r="D46" s="5" t="n">
-        <v>500</v>
+        <v>941</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>186</v>
+        <v>770</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>2120</v>
+        <v>8565</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>131</v>
+        <v>531</v>
       </c>
       <c r="H46" s="5" t="n">
-        <v>151</v>
+        <v>611</v>
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>FINESKIN (ответ)</t>
+          <t>Классик</t>
         </is>
       </c>
       <c r="J46" s="5" t="n">
-        <v>-35</v>
+        <v>-160</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>-18.7</v>
+        <v>-20.7</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>-17352</v>
+        <v>-150368</v>
       </c>
     </row>
     <row r="47">
@@ -7084,34 +7156,34 @@
         <v>853</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>9750</v>
+        <v>9500</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>604</v>
+        <v>589</v>
       </c>
       <c r="H48" s="5" t="n">
-        <v>695</v>
+        <v>677</v>
       </c>
       <c r="I48" s="4" t="inlineStr">
         <is>
-          <t>Классик</t>
+          <t>PAPA COSMETIC (ответ)</t>
         </is>
       </c>
       <c r="J48" s="5" t="n">
-        <v>-158</v>
+        <v>-176</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>-18.5</v>
+        <v>-20.6</v>
       </c>
       <c r="L48" s="5" t="n">
-        <v>-12626</v>
+        <v>-14052</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n"/>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C49" s="2" t="n"/>
@@ -7131,105 +7203,105 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
+          <t>JIGOTT</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>JIGOTT - Snail Reparing Cream [100ml] / Крем для лица увлажняющий антивозрастной с муцином улитки</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="n">
+        <v>500</v>
+      </c>
+      <c r="E50" s="5" t="n">
+        <v>186</v>
+      </c>
+      <c r="F50" s="5" t="n">
+        <v>2120</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>131</v>
+      </c>
+      <c r="H50" s="5" t="n">
+        <v>151</v>
+      </c>
+      <c r="I50" s="4" t="inlineStr">
+        <is>
+          <t>FINESKIN (ответ)</t>
+        </is>
+      </c>
+      <c r="J50" s="5" t="n">
+        <v>-35</v>
+      </c>
+      <c r="K50" s="4" t="n">
+        <v>-18.7</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>-17352</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>PETITFEE</t>
         </is>
       </c>
-      <c r="C50" s="4" t="inlineStr">
+      <c r="C51" s="2" t="n"/>
+      <c r="D51" s="3" t="n"/>
+      <c r="E51" s="3" t="n"/>
+      <c r="F51" s="3" t="n"/>
+      <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
+      <c r="I51" s="2" t="n"/>
+      <c r="J51" s="3" t="n"/>
+      <c r="K51" s="2" t="n"/>
+      <c r="L51" s="3" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
         <is>
           <t>PETITFEE - Gold Hydrogel Eye Patch [1 Pairs] / гидрогелевые патчи для глаз с золотом 1 пара</t>
         </is>
       </c>
-      <c r="D50" s="5" t="n">
+      <c r="D52" s="5" t="n">
         <v>428</v>
       </c>
-      <c r="E50" s="5" t="n">
+      <c r="E52" s="5" t="n">
         <v>71</v>
       </c>
-      <c r="F50" s="5" t="n">
+      <c r="F52" s="5" t="n">
         <v>819</v>
       </c>
-      <c r="G50" s="5" t="n">
+      <c r="G52" s="5" t="n">
         <v>51</v>
       </c>
-      <c r="H50" s="5" t="n">
+      <c r="H52" s="5" t="n">
         <v>58</v>
       </c>
-      <c r="I50" s="4" t="inlineStr">
+      <c r="I52" s="4" t="inlineStr">
         <is>
           <t>FINESKIN (ответ)</t>
         </is>
       </c>
-      <c r="J50" s="5" t="n">
+      <c r="J52" s="5" t="n">
         <v>-13</v>
       </c>
-      <c r="K50" s="4" t="n">
+      <c r="K52" s="4" t="n">
         <v>-18</v>
       </c>
-      <c r="L50" s="5" t="n">
+      <c r="L52" s="5" t="n">
         <v>-5498</v>
       </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="4" t="n">
-        <v>38</v>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>PETITFEE</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Eye Patch [1 pairs]/ Гидрогелевые патчи для глаз с черным жемчугом и золотом 1 пара</t>
-        </is>
-      </c>
-      <c r="D51" s="5" t="n">
-        <v>320</v>
-      </c>
-      <c r="E51" s="5" t="n">
-        <v>71</v>
-      </c>
-      <c r="F51" s="5" t="n">
-        <v>819</v>
-      </c>
-      <c r="G51" s="5" t="n">
-        <v>51</v>
-      </c>
-      <c r="H51" s="5" t="n">
-        <v>58</v>
-      </c>
-      <c r="I51" s="4" t="inlineStr">
-        <is>
-          <t>FINESKIN (ответ)</t>
-        </is>
-      </c>
-      <c r="J51" s="5" t="n">
-        <v>-13</v>
-      </c>
-      <c r="K51" s="4" t="n">
-        <v>-18</v>
-      </c>
-      <c r="L51" s="5" t="n">
-        <v>-4110</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="n"/>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>ROUND LAB</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="n"/>
-      <c r="D52" s="3" t="n"/>
-      <c r="E52" s="3" t="n"/>
-      <c r="F52" s="3" t="n"/>
-      <c r="G52" s="3" t="n"/>
-      <c r="H52" s="3" t="n"/>
-      <c r="I52" s="2" t="n"/>
-      <c r="J52" s="3" t="n"/>
-      <c r="K52" s="2" t="n"/>
-      <c r="L52" s="3" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n">
@@ -7237,49 +7309,49 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>ROUND LAB</t>
+          <t>PETITFEE</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>ROUND LAB MUGWORT CALMING CLEANSER_150ml - Очищающая пенка для умывания лица от прыщей и акне</t>
+          <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Eye Patch [1 pairs]/ Гидрогелевые патчи для глаз с черным жемчугом и золотом 1 пара</t>
         </is>
       </c>
       <c r="D53" s="5" t="n">
-        <v>1422</v>
+        <v>320</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>512</v>
+        <v>71</v>
       </c>
       <c r="F53" s="5" t="n">
-        <v>5963</v>
+        <v>819</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>370</v>
+        <v>51</v>
       </c>
       <c r="H53" s="5" t="n">
-        <v>425</v>
+        <v>58</v>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>G&amp;E Global</t>
+          <t>FINESKIN (ответ)</t>
         </is>
       </c>
       <c r="J53" s="5" t="n">
-        <v>-87</v>
+        <v>-13</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="L53" s="5" t="n">
-        <v>-123939</v>
+        <v>-4110</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n"/>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>DEOPROCE</t>
+          <t>ROUND LAB</t>
         </is>
       </c>
       <c r="C54" s="2" t="n"/>
@@ -7299,49 +7371,49 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>DEOPROCE</t>
+          <t>ROUND LAB</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>DEOPROCE SHAMPOO - BLACK GARLIC INTENSME ENERGY [200ml]/ Шампунь с черным чесноком против выпадения волос</t>
+          <t>ROUND LAB MUGWORT CALMING CLEANSER_150ml - Очищающая пенка для умывания лица от прыщей и акне</t>
         </is>
       </c>
       <c r="D55" s="5" t="n">
-        <v>240</v>
+        <v>1422</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>151</v>
+        <v>512</v>
       </c>
       <c r="F55" s="5" t="n">
-        <v>1781</v>
+        <v>5963</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>110</v>
+        <v>370</v>
       </c>
       <c r="H55" s="5" t="n">
-        <v>127</v>
+        <v>425</v>
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>FINESKIN (ответ)</t>
+          <t>G&amp;E Global</t>
         </is>
       </c>
       <c r="J55" s="5" t="n">
-        <v>-24</v>
+        <v>-87</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="L55" s="5" t="n">
-        <v>-5795</v>
+        <v>-123939</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n"/>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>JMSOLUTION</t>
+          <t>DEOPROCE</t>
         </is>
       </c>
       <c r="C56" s="2" t="n"/>
@@ -7361,91 +7433,65 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
+          <t>DEOPROCE</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>DEOPROCE SHAMPOO - BLACK GARLIC INTENSME ENERGY [200ml]/ Шампунь с черным чесноком против выпадения волос</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="n">
+        <v>240</v>
+      </c>
+      <c r="E57" s="5" t="n">
+        <v>151</v>
+      </c>
+      <c r="F57" s="5" t="n">
+        <v>1781</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>110</v>
+      </c>
+      <c r="H57" s="5" t="n">
+        <v>127</v>
+      </c>
+      <c r="I57" s="4" t="inlineStr">
+        <is>
+          <t>FINESKIN (ответ)</t>
+        </is>
+      </c>
+      <c r="J57" s="5" t="n">
+        <v>-24</v>
+      </c>
+      <c r="K57" s="4" t="n">
+        <v>-16</v>
+      </c>
+      <c r="L57" s="5" t="n">
+        <v>-5795</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>JMSOLUTION</t>
         </is>
       </c>
-      <c r="C57" s="4" t="inlineStr">
-        <is>
-          <t>JMSOLUTION  JMSOLUTION - Glory Aqua TOCOPHEROL VITAMIN C MASK PLUS [30ml*10ea] / Тканевая маска</t>
-        </is>
-      </c>
-      <c r="D57" s="5" t="n">
-        <v>110</v>
-      </c>
-      <c r="E57" s="5" t="n">
-        <v>450</v>
-      </c>
-      <c r="F57" s="5" t="n">
-        <v>5311</v>
-      </c>
-      <c r="G57" s="5" t="n">
-        <v>329</v>
-      </c>
-      <c r="H57" s="5" t="n">
-        <v>379</v>
-      </c>
-      <c r="I57" s="4" t="inlineStr">
-        <is>
-          <t>FINESKIN (ответ)</t>
-        </is>
-      </c>
-      <c r="J57" s="5" t="n">
-        <v>-72</v>
-      </c>
-      <c r="K57" s="4" t="n">
-        <v>-15.9</v>
-      </c>
-      <c r="L57" s="5" t="n">
-        <v>-7884</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="B58" s="4" t="inlineStr">
-        <is>
-          <t>JMSOLUTION</t>
-        </is>
-      </c>
-      <c r="C58" s="4" t="inlineStr">
-        <is>
-          <t>JMSOLUTION GLORY AQUA FULLERENE MASK DELUXE</t>
-        </is>
-      </c>
-      <c r="D58" s="5" t="n">
-        <v>110</v>
-      </c>
-      <c r="E58" s="5" t="n">
-        <v>450</v>
-      </c>
-      <c r="F58" s="5" t="n">
-        <v>5311</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>329</v>
-      </c>
-      <c r="H58" s="5" t="n">
-        <v>379</v>
-      </c>
-      <c r="I58" s="4" t="inlineStr">
-        <is>
-          <t>FINESKIN (ответ)</t>
-        </is>
-      </c>
-      <c r="J58" s="5" t="n">
-        <v>-72</v>
-      </c>
-      <c r="K58" s="4" t="n">
-        <v>-15.9</v>
-      </c>
-      <c r="L58" s="5" t="n">
-        <v>-7884</v>
-      </c>
+      <c r="C58" s="2" t="n"/>
+      <c r="D58" s="3" t="n"/>
+      <c r="E58" s="3" t="n"/>
+      <c r="F58" s="3" t="n"/>
+      <c r="G58" s="3" t="n"/>
+      <c r="H58" s="3" t="n"/>
+      <c r="I58" s="2" t="n"/>
+      <c r="J58" s="3" t="n"/>
+      <c r="K58" s="2" t="n"/>
+      <c r="L58" s="3" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="4" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
@@ -7488,22 +7534,48 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n"/>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>FARMSTAY</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="n"/>
-      <c r="D60" s="3" t="n"/>
-      <c r="E60" s="3" t="n"/>
-      <c r="F60" s="3" t="n"/>
-      <c r="G60" s="3" t="n"/>
-      <c r="H60" s="3" t="n"/>
-      <c r="I60" s="2" t="n"/>
-      <c r="J60" s="3" t="n"/>
-      <c r="K60" s="2" t="n"/>
-      <c r="L60" s="3" t="n"/>
+      <c r="A60" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>JMSOLUTION</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>JMSOLUTION  JMSOLUTION - Glory Aqua TOCOPHEROL VITAMIN C MASK PLUS [30ml*10ea] / Тканевая маска</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="n">
+        <v>110</v>
+      </c>
+      <c r="E60" s="5" t="n">
+        <v>450</v>
+      </c>
+      <c r="F60" s="5" t="n">
+        <v>5311</v>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>329</v>
+      </c>
+      <c r="H60" s="5" t="n">
+        <v>379</v>
+      </c>
+      <c r="I60" s="4" t="inlineStr">
+        <is>
+          <t>FINESKIN (ответ)</t>
+        </is>
+      </c>
+      <c r="J60" s="5" t="n">
+        <v>-72</v>
+      </c>
+      <c r="K60" s="4" t="n">
+        <v>-15.9</v>
+      </c>
+      <c r="L60" s="5" t="n">
+        <v>-7884</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="n">
@@ -7511,137 +7583,111 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>FARMSTAY</t>
+          <t>JMSOLUTION</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>FARMSTAY ESCARGOT NOBLESSE INTENSIVE AMPOULE/ сыворотка с улиткой</t>
+          <t>JMSOLUTION GLORY AQUA FULLERENE MASK DELUXE</t>
         </is>
       </c>
       <c r="D61" s="5" t="n">
-        <v>901</v>
+        <v>110</v>
       </c>
       <c r="E61" s="5" t="n">
-        <v>390</v>
+        <v>450</v>
       </c>
       <c r="F61" s="5" t="n">
-        <v>4660</v>
+        <v>5311</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>289</v>
+        <v>329</v>
       </c>
       <c r="H61" s="5" t="n">
-        <v>332</v>
+        <v>379</v>
       </c>
       <c r="I61" s="4" t="inlineStr">
         <is>
-          <t>Классик</t>
+          <t>FINESKIN (ответ)</t>
         </is>
       </c>
       <c r="J61" s="5" t="n">
-        <v>-58</v>
+        <v>-72</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>-14.9</v>
+        <v>-15.9</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>-52440</v>
+        <v>-7884</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="B62" s="4" t="inlineStr">
-        <is>
-          <t>FARMSTAY</t>
-        </is>
-      </c>
-      <c r="C62" s="4" t="inlineStr">
-        <is>
-          <t>FARMSTAY - Collagen Pure Cleansing Foam [180ml]/Пенка для умывания</t>
-        </is>
-      </c>
-      <c r="D62" s="5" t="n">
-        <v>300</v>
-      </c>
-      <c r="E62" s="5" t="n">
-        <v>161</v>
-      </c>
-      <c r="F62" s="5" t="n">
-        <v>1930</v>
-      </c>
-      <c r="G62" s="5" t="n">
-        <v>120</v>
-      </c>
-      <c r="H62" s="5" t="n">
-        <v>138</v>
-      </c>
-      <c r="I62" s="4" t="inlineStr">
-        <is>
-          <t>Классик</t>
-        </is>
-      </c>
-      <c r="J62" s="5" t="n">
-        <v>-24</v>
-      </c>
-      <c r="K62" s="4" t="n">
-        <v>-14.8</v>
-      </c>
-      <c r="L62" s="5" t="n">
-        <v>-7158</v>
-      </c>
+      <c r="A62" s="2" t="n"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>MANYO</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="n"/>
+      <c r="D62" s="3" t="n"/>
+      <c r="E62" s="3" t="n"/>
+      <c r="F62" s="3" t="n"/>
+      <c r="G62" s="3" t="n"/>
+      <c r="H62" s="3" t="n"/>
+      <c r="I62" s="2" t="n"/>
+      <c r="J62" s="3" t="n"/>
+      <c r="K62" s="2" t="n"/>
+      <c r="L62" s="3" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="4" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>FARMSTAY</t>
+          <t>MANYO</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>FARMSTAY - Collagen Water Full Moist Rolling Eye Serum [25ml] / Сыворотка роллер для глаз</t>
+          <t>MANYO BIFIDA COMPLEX AMPOULE GEL CLEANSER [400ml] / Гель для умывания с бифидобактериями</t>
         </is>
       </c>
       <c r="D63" s="5" t="n">
-        <v>156</v>
+        <v>650</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>232</v>
+        <v>740</v>
       </c>
       <c r="F63" s="5" t="n">
-        <v>2770</v>
+        <v>8740</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>172</v>
+        <v>542</v>
       </c>
       <c r="H63" s="5" t="n">
-        <v>198</v>
+        <v>623</v>
       </c>
       <c r="I63" s="4" t="inlineStr">
         <is>
-          <t>Классик</t>
+          <t>PAPA COSMETIC (ответ)</t>
         </is>
       </c>
       <c r="J63" s="5" t="n">
-        <v>-34</v>
+        <v>-117</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>-14.8</v>
+        <v>-15.8</v>
       </c>
       <c r="L63" s="5" t="n">
-        <v>-5340</v>
+        <v>-75886</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n"/>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>CELIMAX</t>
+          <t>FARMSTAY</t>
         </is>
       </c>
       <c r="C64" s="2" t="n"/>
@@ -7657,65 +7703,91 @@
     </row>
     <row r="65">
       <c r="A65" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>FARMSTAY</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>FARMSTAY ESCARGOT NOBLESSE INTENSIVE AMPOULE/ сыворотка с улиткой</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="n">
+        <v>901</v>
+      </c>
+      <c r="E65" s="5" t="n">
+        <v>390</v>
+      </c>
+      <c r="F65" s="5" t="n">
+        <v>4660</v>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v>289</v>
+      </c>
+      <c r="H65" s="5" t="n">
+        <v>332</v>
+      </c>
+      <c r="I65" s="4" t="inlineStr">
+        <is>
+          <t>Классик</t>
+        </is>
+      </c>
+      <c r="J65" s="5" t="n">
+        <v>-58</v>
+      </c>
+      <c r="K65" s="4" t="n">
+        <v>-14.9</v>
+      </c>
+      <c r="L65" s="5" t="n">
+        <v>-52440</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="n">
         <v>47</v>
       </c>
-      <c r="B65" s="4" t="inlineStr">
-        <is>
-          <t>CELIMAX</t>
-        </is>
-      </c>
-      <c r="C65" s="4" t="inlineStr">
-        <is>
-          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD [170ml / 60pads]/Тонер-пэды от воспалений</t>
-        </is>
-      </c>
-      <c r="D65" s="5" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E65" s="5" t="n">
-        <v>708</v>
-      </c>
-      <c r="F65" s="5" t="n">
-        <v>8509</v>
-      </c>
-      <c r="G65" s="5" t="n">
-        <v>528</v>
-      </c>
-      <c r="H65" s="5" t="n">
-        <v>607</v>
-      </c>
-      <c r="I65" s="4" t="inlineStr">
-        <is>
-          <t>Papa Cosmetic</t>
-        </is>
-      </c>
-      <c r="J65" s="5" t="n">
-        <v>-101</v>
-      </c>
-      <c r="K65" s="4" t="n">
-        <v>-14.3</v>
-      </c>
-      <c r="L65" s="5" t="n">
-        <v>-151773</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="n"/>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>ENOUGH</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="n"/>
-      <c r="D66" s="3" t="n"/>
-      <c r="E66" s="3" t="n"/>
-      <c r="F66" s="3" t="n"/>
-      <c r="G66" s="3" t="n"/>
-      <c r="H66" s="3" t="n"/>
-      <c r="I66" s="2" t="n"/>
-      <c r="J66" s="3" t="n"/>
-      <c r="K66" s="2" t="n"/>
-      <c r="L66" s="3" t="n"/>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>FARMSTAY</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>FARMSTAY - Collagen Water Full Moist Rolling Eye Serum [25ml] / Сыворотка роллер для глаз</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="n">
+        <v>156</v>
+      </c>
+      <c r="E66" s="5" t="n">
+        <v>232</v>
+      </c>
+      <c r="F66" s="5" t="n">
+        <v>2770</v>
+      </c>
+      <c r="G66" s="5" t="n">
+        <v>172</v>
+      </c>
+      <c r="H66" s="5" t="n">
+        <v>198</v>
+      </c>
+      <c r="I66" s="4" t="inlineStr">
+        <is>
+          <t>Классик</t>
+        </is>
+      </c>
+      <c r="J66" s="5" t="n">
+        <v>-34</v>
+      </c>
+      <c r="K66" s="4" t="n">
+        <v>-14.8</v>
+      </c>
+      <c r="L66" s="5" t="n">
+        <v>-5340</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="n">
@@ -7723,28 +7795,28 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>ENOUGH</t>
+          <t>FARMSTAY</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENOUGH Collagen whitening cover tip concealer #01 [9g]/Консилер для лица (основная карточка) </t>
+          <t>FARMSTAY - Collagen Pure Cleansing Foam [180ml]/Пенка для умывания</t>
         </is>
       </c>
       <c r="D67" s="5" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E67" s="5" t="n">
-        <v>183</v>
+        <v>161</v>
       </c>
       <c r="F67" s="5" t="n">
-        <v>2250</v>
+        <v>1930</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="H67" s="5" t="n">
-        <v>160</v>
+        <v>138</v>
       </c>
       <c r="I67" s="4" t="inlineStr">
         <is>
@@ -7752,108 +7824,82 @@
         </is>
       </c>
       <c r="J67" s="5" t="n">
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>-12.5</v>
+        <v>-14.8</v>
       </c>
       <c r="L67" s="5" t="n">
-        <v>-4563</v>
+        <v>-7158</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="4" t="n">
-        <v>49</v>
-      </c>
-      <c r="B68" s="4" t="inlineStr">
-        <is>
-          <t>ENOUGH</t>
-        </is>
-      </c>
-      <c r="C68" s="4" t="inlineStr">
-        <is>
-          <t>ENOUGH Collagen whitening cover tip concealer #02 [9g]/Консилер для лица (основная карточка)</t>
-        </is>
-      </c>
-      <c r="D68" s="5" t="n">
-        <v>300</v>
-      </c>
-      <c r="E68" s="5" t="n">
-        <v>183</v>
-      </c>
-      <c r="F68" s="5" t="n">
-        <v>2250</v>
-      </c>
-      <c r="G68" s="5" t="n">
-        <v>140</v>
-      </c>
-      <c r="H68" s="5" t="n">
-        <v>160</v>
-      </c>
-      <c r="I68" s="4" t="inlineStr">
-        <is>
-          <t>Классик</t>
-        </is>
-      </c>
-      <c r="J68" s="5" t="n">
-        <v>-23</v>
-      </c>
-      <c r="K68" s="4" t="n">
-        <v>-12.5</v>
-      </c>
-      <c r="L68" s="5" t="n">
-        <v>-6844</v>
-      </c>
+      <c r="A68" s="2" t="n"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>CELIMAX</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="n"/>
+      <c r="D68" s="3" t="n"/>
+      <c r="E68" s="3" t="n"/>
+      <c r="F68" s="3" t="n"/>
+      <c r="G68" s="3" t="n"/>
+      <c r="H68" s="3" t="n"/>
+      <c r="I68" s="2" t="n"/>
+      <c r="J68" s="3" t="n"/>
+      <c r="K68" s="2" t="n"/>
+      <c r="L68" s="3" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="4" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>ENOUGH</t>
+          <t>CELIMAX</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>ENOUGH Collagen whitening cover tip concealer #03 [9g]/ Консилер для лица (основаная карточка)</t>
+          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD [170ml / 60pads]/Тонер-пэды от воспалений</t>
         </is>
       </c>
       <c r="D69" s="5" t="n">
-        <v>260</v>
+        <v>1500</v>
       </c>
       <c r="E69" s="5" t="n">
-        <v>183</v>
+        <v>708</v>
       </c>
       <c r="F69" s="5" t="n">
-        <v>2250</v>
+        <v>8509</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>140</v>
+        <v>528</v>
       </c>
       <c r="H69" s="5" t="n">
-        <v>160</v>
+        <v>607</v>
       </c>
       <c r="I69" s="4" t="inlineStr">
         <is>
-          <t>Классик</t>
+          <t>Papa Cosmetic</t>
         </is>
       </c>
       <c r="J69" s="5" t="n">
-        <v>-23</v>
+        <v>-101</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>-12.5</v>
+        <v>-14.3</v>
       </c>
       <c r="L69" s="5" t="n">
-        <v>-5932</v>
+        <v>-151773</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n"/>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>DEOPROCE</t>
+          <t>ETUDE</t>
         </is>
       </c>
       <c r="C70" s="2" t="n"/>
@@ -7869,233 +7915,259 @@
     </row>
     <row r="71">
       <c r="A71" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>ETUDE</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>ETUDE - Baking Powder Crunch Pore Scrub [200ml] / Очищающий скраб для лица с содой</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="n">
+        <v>7279</v>
+      </c>
+      <c r="E71" s="5" t="n">
+        <v>361</v>
+      </c>
+      <c r="F71" s="5" t="n">
+        <v>4400</v>
+      </c>
+      <c r="G71" s="5" t="n">
+        <v>273</v>
+      </c>
+      <c r="H71" s="5" t="n">
+        <v>314</v>
+      </c>
+      <c r="I71" s="4" t="inlineStr">
+        <is>
+          <t>PAPA COSMETIC (ответ)</t>
+        </is>
+      </c>
+      <c r="J71" s="5" t="n">
+        <v>-47</v>
+      </c>
+      <c r="K71" s="4" t="n">
+        <v>-13.1</v>
+      </c>
+      <c r="L71" s="5" t="n">
+        <v>-344369</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>ENOUGH</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="n"/>
+      <c r="D72" s="3" t="n"/>
+      <c r="E72" s="3" t="n"/>
+      <c r="F72" s="3" t="n"/>
+      <c r="G72" s="3" t="n"/>
+      <c r="H72" s="3" t="n"/>
+      <c r="I72" s="2" t="n"/>
+      <c r="J72" s="3" t="n"/>
+      <c r="K72" s="2" t="n"/>
+      <c r="L72" s="3" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="n">
         <v>51</v>
       </c>
-      <c r="B71" s="4" t="inlineStr">
-        <is>
-          <t>DEOPROCE</t>
-        </is>
-      </c>
-      <c r="C71" s="4" t="inlineStr">
-        <is>
-          <t>DEOPROCE RINSE - BLACK GARLIC INTENSME ENERGY [1000ml] / Бальзам от выпадения волос Чёрный чеснок</t>
-        </is>
-      </c>
-      <c r="D71" s="5" t="n">
-        <v>400</v>
-      </c>
-      <c r="E71" s="5" t="n">
-        <v>359</v>
-      </c>
-      <c r="F71" s="5" t="n">
-        <v>4431</v>
-      </c>
-      <c r="G71" s="5" t="n">
-        <v>275</v>
-      </c>
-      <c r="H71" s="5" t="n">
-        <v>316</v>
-      </c>
-      <c r="I71" s="4" t="inlineStr">
-        <is>
-          <t>FINESKIN (ответ)</t>
-        </is>
-      </c>
-      <c r="J71" s="5" t="n">
-        <v>-43</v>
-      </c>
-      <c r="K71" s="4" t="n">
-        <v>-12</v>
-      </c>
-      <c r="L71" s="5" t="n">
-        <v>-17200</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="4" t="n">
-        <v>52</v>
-      </c>
-      <c r="B72" s="4" t="inlineStr">
-        <is>
-          <t>DEOPROCE</t>
-        </is>
-      </c>
-      <c r="C72" s="4" t="inlineStr">
-        <is>
-          <t>DEOPROCE SHAMPOO - BLACK GARLIC INTENSME ENERGY [1000ml]/ Шампунь с черным чесноком против выпадения волос</t>
-        </is>
-      </c>
-      <c r="D72" s="5" t="n">
-        <v>400</v>
-      </c>
-      <c r="E72" s="5" t="n">
-        <v>368</v>
-      </c>
-      <c r="F72" s="5" t="n">
-        <v>4547</v>
-      </c>
-      <c r="G72" s="5" t="n">
-        <v>282</v>
-      </c>
-      <c r="H72" s="5" t="n">
-        <v>324</v>
-      </c>
-      <c r="I72" s="4" t="inlineStr">
-        <is>
-          <t>FINESKIN (ответ)</t>
-        </is>
-      </c>
-      <c r="J72" s="5" t="n">
-        <v>-44</v>
-      </c>
-      <c r="K72" s="4" t="n">
-        <v>-11.9</v>
-      </c>
-      <c r="L72" s="5" t="n">
-        <v>-17488</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="n"/>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>LEBELAGE</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="n"/>
-      <c r="D73" s="3" t="n"/>
-      <c r="E73" s="3" t="n"/>
-      <c r="F73" s="3" t="n"/>
-      <c r="G73" s="3" t="n"/>
-      <c r="H73" s="3" t="n"/>
-      <c r="I73" s="2" t="n"/>
-      <c r="J73" s="3" t="n"/>
-      <c r="K73" s="2" t="n"/>
-      <c r="L73" s="3" t="n"/>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>ENOUGH</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>ENOUGH Collagen whitening cover tip concealer #02 [9g]/Консилер для лица (основная карточка)</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="n">
+        <v>300</v>
+      </c>
+      <c r="E73" s="5" t="n">
+        <v>183</v>
+      </c>
+      <c r="F73" s="5" t="n">
+        <v>2250</v>
+      </c>
+      <c r="G73" s="5" t="n">
+        <v>140</v>
+      </c>
+      <c r="H73" s="5" t="n">
+        <v>160</v>
+      </c>
+      <c r="I73" s="4" t="inlineStr">
+        <is>
+          <t>Классик</t>
+        </is>
+      </c>
+      <c r="J73" s="5" t="n">
+        <v>-23</v>
+      </c>
+      <c r="K73" s="4" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="L73" s="5" t="n">
+        <v>-6844</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>ENOUGH</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ENOUGH Collagen whitening cover tip concealer #01 [9g]/Консилер для лица (основная карточка) </t>
+        </is>
+      </c>
+      <c r="D74" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="E74" s="5" t="n">
+        <v>183</v>
+      </c>
+      <c r="F74" s="5" t="n">
+        <v>2250</v>
+      </c>
+      <c r="G74" s="5" t="n">
+        <v>140</v>
+      </c>
+      <c r="H74" s="5" t="n">
+        <v>160</v>
+      </c>
+      <c r="I74" s="4" t="inlineStr">
+        <is>
+          <t>Классик</t>
+        </is>
+      </c>
+      <c r="J74" s="5" t="n">
+        <v>-23</v>
+      </c>
+      <c r="K74" s="4" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="L74" s="5" t="n">
+        <v>-4563</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="n">
         <v>53</v>
       </c>
-      <c r="B74" s="4" t="inlineStr">
-        <is>
-          <t>LEBELAGE</t>
-        </is>
-      </c>
-      <c r="C74" s="4" t="inlineStr">
-        <is>
-          <t>LEBELAGE - Dr. Peptide Derma Eye Cream [40ml] / Крем для глаз антивозрастной с пептидами</t>
-        </is>
-      </c>
-      <c r="D74" s="5" t="n">
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>ENOUGH</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>ENOUGH Collagen whitening cover tip concealer #03 [9g]/ Консилер для лица (основаная карточка)</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="n">
+        <v>260</v>
+      </c>
+      <c r="E75" s="5" t="n">
+        <v>183</v>
+      </c>
+      <c r="F75" s="5" t="n">
+        <v>2250</v>
+      </c>
+      <c r="G75" s="5" t="n">
+        <v>140</v>
+      </c>
+      <c r="H75" s="5" t="n">
+        <v>160</v>
+      </c>
+      <c r="I75" s="4" t="inlineStr">
+        <is>
+          <t>Классик</t>
+        </is>
+      </c>
+      <c r="J75" s="5" t="n">
+        <v>-23</v>
+      </c>
+      <c r="K75" s="4" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="L75" s="5" t="n">
+        <v>-5932</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>DEOPROCE</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="n"/>
+      <c r="D76" s="3" t="n"/>
+      <c r="E76" s="3" t="n"/>
+      <c r="F76" s="3" t="n"/>
+      <c r="G76" s="3" t="n"/>
+      <c r="H76" s="3" t="n"/>
+      <c r="I76" s="2" t="n"/>
+      <c r="J76" s="3" t="n"/>
+      <c r="K76" s="2" t="n"/>
+      <c r="L76" s="3" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>DEOPROCE</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>DEOPROCE RINSE - BLACK GARLIC INTENSME ENERGY [1000ml] / Бальзам от выпадения волос Чёрный чеснок</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="n">
         <v>400</v>
       </c>
-      <c r="E74" s="5" t="n">
-        <v>108</v>
-      </c>
-      <c r="F74" s="5" t="n">
-        <v>1350</v>
-      </c>
-      <c r="G74" s="5" t="n">
-        <v>84</v>
-      </c>
-      <c r="H74" s="5" t="n">
-        <v>96</v>
-      </c>
-      <c r="I74" s="4" t="inlineStr">
-        <is>
-          <t>Классик</t>
-        </is>
-      </c>
-      <c r="J74" s="5" t="n">
+      <c r="E77" s="5" t="n">
+        <v>359</v>
+      </c>
+      <c r="F77" s="5" t="n">
+        <v>4431</v>
+      </c>
+      <c r="G77" s="5" t="n">
+        <v>275</v>
+      </c>
+      <c r="H77" s="5" t="n">
+        <v>316</v>
+      </c>
+      <c r="I77" s="4" t="inlineStr">
+        <is>
+          <t>FINESKIN (ответ)</t>
+        </is>
+      </c>
+      <c r="J77" s="5" t="n">
+        <v>-43</v>
+      </c>
+      <c r="K77" s="4" t="n">
         <v>-12</v>
       </c>
-      <c r="K74" s="4" t="n">
-        <v>-11</v>
-      </c>
-      <c r="L74" s="5" t="n">
-        <v>-4758</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="n"/>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>ROUND LAB</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="n"/>
-      <c r="D75" s="3" t="n"/>
-      <c r="E75" s="3" t="n"/>
-      <c r="F75" s="3" t="n"/>
-      <c r="G75" s="3" t="n"/>
-      <c r="H75" s="3" t="n"/>
-      <c r="I75" s="2" t="n"/>
-      <c r="J75" s="3" t="n"/>
-      <c r="K75" s="2" t="n"/>
-      <c r="L75" s="3" t="n"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="4" t="n">
-        <v>54</v>
-      </c>
-      <c r="B76" s="4" t="inlineStr">
-        <is>
-          <t>ROUND LAB</t>
-        </is>
-      </c>
-      <c r="C76" s="4" t="inlineStr">
-        <is>
-          <t>ROUND LAB 1025 DOKDO CLEANSER_150ml - Увлажняющая пенка для умывания лица</t>
-        </is>
-      </c>
-      <c r="D76" s="5" t="n">
-        <v>7126</v>
-      </c>
-      <c r="E76" s="5" t="n">
-        <v>463</v>
-      </c>
-      <c r="F76" s="5" t="n">
-        <v>5857</v>
-      </c>
-      <c r="G76" s="5" t="n">
-        <v>363</v>
-      </c>
-      <c r="H76" s="5" t="n">
-        <v>418</v>
-      </c>
-      <c r="I76" s="4" t="inlineStr">
-        <is>
-          <t>G&amp;E Global</t>
-        </is>
-      </c>
-      <c r="J76" s="5" t="n">
-        <v>-46</v>
-      </c>
-      <c r="K76" s="4" t="n">
-        <v>-9.800000000000001</v>
-      </c>
-      <c r="L76" s="5" t="n">
-        <v>-324845</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="n"/>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>FARMSTAY</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="n"/>
-      <c r="D77" s="3" t="n"/>
-      <c r="E77" s="3" t="n"/>
-      <c r="F77" s="3" t="n"/>
-      <c r="G77" s="3" t="n"/>
-      <c r="H77" s="3" t="n"/>
-      <c r="I77" s="2" t="n"/>
-      <c r="J77" s="3" t="n"/>
-      <c r="K77" s="2" t="n"/>
-      <c r="L77" s="3" t="n"/>
+      <c r="L77" s="5" t="n">
+        <v>-17200</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="n">
@@ -8103,440 +8175,414 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
+          <t>DEOPROCE</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>DEOPROCE SHAMPOO - BLACK GARLIC INTENSME ENERGY [1000ml]/ Шампунь с черным чесноком против выпадения волос</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="n">
+        <v>400</v>
+      </c>
+      <c r="E78" s="5" t="n">
+        <v>368</v>
+      </c>
+      <c r="F78" s="5" t="n">
+        <v>4547</v>
+      </c>
+      <c r="G78" s="5" t="n">
+        <v>282</v>
+      </c>
+      <c r="H78" s="5" t="n">
+        <v>324</v>
+      </c>
+      <c r="I78" s="4" t="inlineStr">
+        <is>
+          <t>FINESKIN (ответ)</t>
+        </is>
+      </c>
+      <c r="J78" s="5" t="n">
+        <v>-44</v>
+      </c>
+      <c r="K78" s="4" t="n">
+        <v>-11.9</v>
+      </c>
+      <c r="L78" s="5" t="n">
+        <v>-17488</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>LEBELAGE</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="n"/>
+      <c r="D79" s="3" t="n"/>
+      <c r="E79" s="3" t="n"/>
+      <c r="F79" s="3" t="n"/>
+      <c r="G79" s="3" t="n"/>
+      <c r="H79" s="3" t="n"/>
+      <c r="I79" s="2" t="n"/>
+      <c r="J79" s="3" t="n"/>
+      <c r="K79" s="2" t="n"/>
+      <c r="L79" s="3" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>LEBELAGE</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>LEBELAGE - Dr. Peptide Derma Eye Cream [40ml] / Крем для глаз антивозрастной с пептидами</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="n">
+        <v>400</v>
+      </c>
+      <c r="E80" s="5" t="n">
+        <v>108</v>
+      </c>
+      <c r="F80" s="5" t="n">
+        <v>1350</v>
+      </c>
+      <c r="G80" s="5" t="n">
+        <v>84</v>
+      </c>
+      <c r="H80" s="5" t="n">
+        <v>96</v>
+      </c>
+      <c r="I80" s="4" t="inlineStr">
+        <is>
+          <t>Классик</t>
+        </is>
+      </c>
+      <c r="J80" s="5" t="n">
+        <v>-12</v>
+      </c>
+      <c r="K80" s="4" t="n">
+        <v>-11</v>
+      </c>
+      <c r="L80" s="5" t="n">
+        <v>-4758</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>ROUND LAB</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="n"/>
+      <c r="D81" s="3" t="n"/>
+      <c r="E81" s="3" t="n"/>
+      <c r="F81" s="3" t="n"/>
+      <c r="G81" s="3" t="n"/>
+      <c r="H81" s="3" t="n"/>
+      <c r="I81" s="2" t="n"/>
+      <c r="J81" s="3" t="n"/>
+      <c r="K81" s="2" t="n"/>
+      <c r="L81" s="3" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="n">
+        <v>57</v>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>ROUND LAB</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>ROUND LAB 1025 DOKDO CLEANSER_150ml - Увлажняющая пенка для умывания лица</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="n">
+        <v>7126</v>
+      </c>
+      <c r="E82" s="5" t="n">
+        <v>463</v>
+      </c>
+      <c r="F82" s="5" t="n">
+        <v>5857</v>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>363</v>
+      </c>
+      <c r="H82" s="5" t="n">
+        <v>418</v>
+      </c>
+      <c r="I82" s="4" t="inlineStr">
+        <is>
+          <t>G&amp;E Global</t>
+        </is>
+      </c>
+      <c r="J82" s="5" t="n">
+        <v>-46</v>
+      </c>
+      <c r="K82" s="4" t="n">
+        <v>-9.800000000000001</v>
+      </c>
+      <c r="L82" s="5" t="n">
+        <v>-324845</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>FARMSTAY</t>
         </is>
       </c>
-      <c r="C78" s="4" t="inlineStr">
+      <c r="C83" s="2" t="n"/>
+      <c r="D83" s="3" t="n"/>
+      <c r="E83" s="3" t="n"/>
+      <c r="F83" s="3" t="n"/>
+      <c r="G83" s="3" t="n"/>
+      <c r="H83" s="3" t="n"/>
+      <c r="I83" s="2" t="n"/>
+      <c r="J83" s="3" t="n"/>
+      <c r="K83" s="2" t="n"/>
+      <c r="L83" s="3" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>FARMSTAY</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
         <is>
           <t>FARMSTAY - Escargot Noblesse Intensive Cream [50g] / Крем с муцином королевской улитки</t>
         </is>
       </c>
-      <c r="D78" s="5" t="n">
+      <c r="D84" s="5" t="n">
         <v>860</v>
       </c>
-      <c r="E78" s="5" t="n">
+      <c r="E84" s="5" t="n">
         <v>314</v>
       </c>
-      <c r="F78" s="5" t="n">
+      <c r="F84" s="5" t="n">
         <v>4010</v>
       </c>
-      <c r="G78" s="5" t="n">
+      <c r="G84" s="5" t="n">
         <v>249</v>
       </c>
-      <c r="H78" s="5" t="n">
+      <c r="H84" s="5" t="n">
         <v>286</v>
       </c>
-      <c r="I78" s="4" t="inlineStr">
+      <c r="I84" s="4" t="inlineStr">
         <is>
           <t>Классик</t>
         </is>
       </c>
-      <c r="J78" s="5" t="n">
+      <c r="J84" s="5" t="n">
         <v>-28</v>
       </c>
-      <c r="K78" s="4" t="n">
+      <c r="K84" s="4" t="n">
         <v>-8.9</v>
       </c>
-      <c r="L78" s="5" t="n">
+      <c r="L84" s="5" t="n">
         <v>-24017</v>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="4" t="n">
-        <v>56</v>
-      </c>
-      <c r="B79" s="4" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="n"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>MANYO</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="n"/>
+      <c r="D85" s="3" t="n"/>
+      <c r="E85" s="3" t="n"/>
+      <c r="F85" s="3" t="n"/>
+      <c r="G85" s="3" t="n"/>
+      <c r="H85" s="3" t="n"/>
+      <c r="I85" s="2" t="n"/>
+      <c r="J85" s="3" t="n"/>
+      <c r="K85" s="2" t="n"/>
+      <c r="L85" s="3" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="n">
+        <v>59</v>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>MANYO</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>MANYO - Bifida Biome Ampoule Lotion [300ml] / Укрепляющий лосьон с бифидобактериями</t>
+        </is>
+      </c>
+      <c r="D86" s="5" t="n">
+        <v>624</v>
+      </c>
+      <c r="E86" s="5" t="n">
+        <v>735</v>
+      </c>
+      <c r="F86" s="5" t="n">
+        <v>9500</v>
+      </c>
+      <c r="G86" s="5" t="n">
+        <v>589</v>
+      </c>
+      <c r="H86" s="5" t="n">
+        <v>677</v>
+      </c>
+      <c r="I86" s="4" t="inlineStr">
+        <is>
+          <t>PAPA COSMETIC (ответ)</t>
+        </is>
+      </c>
+      <c r="J86" s="5" t="n">
+        <v>-58</v>
+      </c>
+      <c r="K86" s="4" t="n">
+        <v>-7.9</v>
+      </c>
+      <c r="L86" s="5" t="n">
+        <v>-36186</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n"/>
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>FARMSTAY</t>
         </is>
       </c>
-      <c r="C79" s="4" t="inlineStr">
+      <c r="C87" s="2" t="n"/>
+      <c r="D87" s="3" t="n"/>
+      <c r="E87" s="3" t="n"/>
+      <c r="F87" s="3" t="n"/>
+      <c r="G87" s="3" t="n"/>
+      <c r="H87" s="3" t="n"/>
+      <c r="I87" s="2" t="n"/>
+      <c r="J87" s="3" t="n"/>
+      <c r="K87" s="2" t="n"/>
+      <c r="L87" s="3" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>FARMSTAY</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
         <is>
           <t>FARMSTAY - Collagen &amp; Hyaluronic Acid All-In One Ampoule [250ml] / Сыворотка с коллагеном и гиалуроновой кислотой</t>
         </is>
       </c>
-      <c r="D79" s="5" t="n">
+      <c r="D88" s="5" t="n">
         <v>6179</v>
       </c>
-      <c r="E79" s="5" t="n">
+      <c r="E88" s="5" t="n">
         <v>348</v>
       </c>
-      <c r="F79" s="5" t="n">
+      <c r="F88" s="5" t="n">
         <v>4660</v>
       </c>
-      <c r="G79" s="5" t="n">
+      <c r="G88" s="5" t="n">
         <v>289</v>
       </c>
-      <c r="H79" s="5" t="n">
+      <c r="H88" s="5" t="n">
         <v>332</v>
       </c>
-      <c r="I79" s="4" t="inlineStr">
+      <c r="I88" s="4" t="inlineStr">
         <is>
           <t>Классик</t>
         </is>
       </c>
-      <c r="J79" s="5" t="n">
+      <c r="J88" s="5" t="n">
         <v>-16</v>
       </c>
-      <c r="K79" s="4" t="n">
+      <c r="K88" s="4" t="n">
         <v>-4.5</v>
       </c>
-      <c r="L79" s="5" t="n">
+      <c r="L88" s="5" t="n">
         <v>-95787</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="n"/>
-      <c r="B80" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="n"/>
+      <c r="B89" s="2" t="inlineStr">
         <is>
           <t>ELIZAVECCA</t>
         </is>
       </c>
-      <c r="C80" s="2" t="n"/>
-      <c r="D80" s="3" t="n"/>
-      <c r="E80" s="3" t="n"/>
-      <c r="F80" s="3" t="n"/>
-      <c r="G80" s="3" t="n"/>
-      <c r="H80" s="3" t="n"/>
-      <c r="I80" s="2" t="n"/>
-      <c r="J80" s="3" t="n"/>
-      <c r="K80" s="2" t="n"/>
-      <c r="L80" s="3" t="n"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="4" t="n">
-        <v>57</v>
-      </c>
-      <c r="B81" s="4" t="inlineStr">
-        <is>
-          <t>ELIZAVECCA</t>
-        </is>
-      </c>
-      <c r="C81" s="4" t="inlineStr">
-        <is>
-          <t>ELIZAVECCA - CER-100 Collagen Ceramide Coating Protein Treatment [100ml] / Коллагеновая маска для волос</t>
-        </is>
-      </c>
-      <c r="D81" s="5" t="n">
-        <v>300</v>
-      </c>
-      <c r="E81" s="5" t="n">
-        <v>242</v>
-      </c>
-      <c r="F81" s="5" t="n">
-        <v>3276</v>
-      </c>
-      <c r="G81" s="5" t="n">
-        <v>203</v>
-      </c>
-      <c r="H81" s="5" t="n">
-        <v>234</v>
-      </c>
-      <c r="I81" s="4" t="inlineStr">
-        <is>
-          <t>FINESKIN (ответ)</t>
-        </is>
-      </c>
-      <c r="J81" s="5" t="n">
-        <v>-9</v>
-      </c>
-      <c r="K81" s="4" t="n">
-        <v>-3.6</v>
-      </c>
-      <c r="L81" s="5" t="n">
-        <v>-2595</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="n"/>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>CELIMAX</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="n"/>
-      <c r="D82" s="3" t="n"/>
-      <c r="E82" s="3" t="n"/>
-      <c r="F82" s="3" t="n"/>
-      <c r="G82" s="3" t="n"/>
-      <c r="H82" s="3" t="n"/>
-      <c r="I82" s="2" t="n"/>
-      <c r="J82" s="3" t="n"/>
-      <c r="K82" s="2" t="n"/>
-      <c r="L82" s="3" t="n"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="4" t="n">
-        <v>58</v>
-      </c>
-      <c r="B83" s="4" t="inlineStr">
-        <is>
-          <t>CELIMAX</t>
-        </is>
-      </c>
-      <c r="C83" s="4" t="inlineStr">
-        <is>
-          <t>Celimax Dual Barrier Creamy Toner, тонер 150 мл</t>
-        </is>
-      </c>
-      <c r="D83" s="5" t="n">
-        <v>4520</v>
-      </c>
-      <c r="E83" s="5" t="n">
-        <v>664</v>
-      </c>
-      <c r="F83" s="5" t="n">
-        <v>9000</v>
-      </c>
-      <c r="G83" s="5" t="n">
-        <v>558</v>
-      </c>
-      <c r="H83" s="5" t="n">
-        <v>642</v>
-      </c>
-      <c r="I83" s="4" t="inlineStr">
-        <is>
-          <t>Papa Cosmetic</t>
-        </is>
-      </c>
-      <c r="J83" s="5" t="n">
-        <v>-22</v>
-      </c>
-      <c r="K83" s="4" t="n">
-        <v>-3.3</v>
-      </c>
-      <c r="L83" s="5" t="n">
-        <v>-100163</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="n"/>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>ENOUGH</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="n"/>
-      <c r="D84" s="3" t="n"/>
-      <c r="E84" s="3" t="n"/>
-      <c r="F84" s="3" t="n"/>
-      <c r="G84" s="3" t="n"/>
-      <c r="H84" s="3" t="n"/>
-      <c r="I84" s="2" t="n"/>
-      <c r="J84" s="3" t="n"/>
-      <c r="K84" s="2" t="n"/>
-      <c r="L84" s="3" t="n"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="4" t="n">
-        <v>59</v>
-      </c>
-      <c r="B85" s="4" t="inlineStr">
-        <is>
-          <t>ENOUGH</t>
-        </is>
-      </c>
-      <c r="C85" s="4" t="inlineStr">
-        <is>
-          <t>ENOUGH - Collagen Whitening Moisture Cream 3in1 [50g] / Антивозрастной отбеливающий крем с коллагеном</t>
-        </is>
-      </c>
-      <c r="D85" s="5" t="n">
-        <v>344</v>
-      </c>
-      <c r="E85" s="5" t="n">
-        <v>184</v>
-      </c>
-      <c r="F85" s="5" t="n">
-        <v>2500</v>
-      </c>
-      <c r="G85" s="5" t="n">
-        <v>155</v>
-      </c>
-      <c r="H85" s="5" t="n">
-        <v>178</v>
-      </c>
-      <c r="I85" s="4" t="inlineStr">
-        <is>
-          <t>Классик</t>
-        </is>
-      </c>
-      <c r="J85" s="5" t="n">
-        <v>-6</v>
-      </c>
-      <c r="K85" s="4" t="n">
-        <v>-3.1</v>
-      </c>
-      <c r="L85" s="5" t="n">
-        <v>-1937</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="n"/>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>SKIN1004</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="n"/>
-      <c r="D86" s="3" t="n"/>
-      <c r="E86" s="3" t="n"/>
-      <c r="F86" s="3" t="n"/>
-      <c r="G86" s="3" t="n"/>
-      <c r="H86" s="3" t="n"/>
-      <c r="I86" s="2" t="n"/>
-      <c r="J86" s="3" t="n"/>
-      <c r="K86" s="2" t="n"/>
-      <c r="L86" s="3" t="n"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="B87" s="4" t="inlineStr">
-        <is>
-          <t>SKIN1004</t>
-        </is>
-      </c>
-      <c r="C87" s="4" t="inlineStr">
-        <is>
-          <t>SKIN1004 - Madagascar Centella Ampoule [30ml] / Сыворотка для лица успокаивающая из экстракта центеллы.</t>
-        </is>
-      </c>
-      <c r="D87" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="E87" s="5" t="n">
-        <v>368</v>
-      </c>
-      <c r="F87" s="5" t="n">
-        <v>5038</v>
-      </c>
-      <c r="G87" s="5" t="n">
-        <v>312</v>
-      </c>
-      <c r="H87" s="5" t="n">
-        <v>359</v>
-      </c>
-      <c r="I87" s="4" t="inlineStr">
-        <is>
-          <t>FINESKIN (ответ)</t>
-        </is>
-      </c>
-      <c r="J87" s="5" t="n">
-        <v>-9</v>
-      </c>
-      <c r="K87" s="4" t="n">
-        <v>-2.4</v>
-      </c>
-      <c r="L87" s="5" t="n">
-        <v>-260</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="n"/>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>PETITFEE</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="n"/>
-      <c r="D88" s="3" t="n"/>
-      <c r="E88" s="3" t="n"/>
-      <c r="F88" s="3" t="n"/>
-      <c r="G88" s="3" t="n"/>
-      <c r="H88" s="3" t="n"/>
-      <c r="I88" s="2" t="n"/>
-      <c r="J88" s="3" t="n"/>
-      <c r="K88" s="2" t="n"/>
-      <c r="L88" s="3" t="n"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="4" t="n">
-        <v>61</v>
-      </c>
-      <c r="B89" s="4" t="inlineStr">
-        <is>
-          <t>PETITFEE</t>
-        </is>
-      </c>
-      <c r="C89" s="4" t="inlineStr">
-        <is>
-          <t>PETITFEE - Gold &amp; Snail Hydrogel Eye Patch [60ea] / Гидрогелевые патчи для глаз с золотом и улиткой</t>
-        </is>
-      </c>
-      <c r="D89" s="5" t="n">
-        <v>144</v>
-      </c>
-      <c r="E89" s="5" t="n">
-        <v>415</v>
-      </c>
-      <c r="F89" s="5" t="n">
-        <v>5690</v>
-      </c>
-      <c r="G89" s="5" t="n">
-        <v>353</v>
-      </c>
-      <c r="H89" s="5" t="n">
-        <v>406</v>
-      </c>
-      <c r="I89" s="4" t="inlineStr">
-        <is>
-          <t>J2K (ответ)</t>
-        </is>
-      </c>
-      <c r="J89" s="5" t="n">
-        <v>-10</v>
-      </c>
-      <c r="K89" s="4" t="n">
-        <v>-2.3</v>
-      </c>
-      <c r="L89" s="5" t="n">
-        <v>-1406</v>
-      </c>
+      <c r="C89" s="2" t="n"/>
+      <c r="D89" s="3" t="n"/>
+      <c r="E89" s="3" t="n"/>
+      <c r="F89" s="3" t="n"/>
+      <c r="G89" s="3" t="n"/>
+      <c r="H89" s="3" t="n"/>
+      <c r="I89" s="2" t="n"/>
+      <c r="J89" s="3" t="n"/>
+      <c r="K89" s="2" t="n"/>
+      <c r="L89" s="3" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="4" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>ELIZAVECCA</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>PETITFEE - Gold Hydrogel Eye Patch [60ea] / гидрогелевые патчи для глаз с золотом</t>
+          <t>ELIZAVECCA - CER-100 Collagen Ceramide Coating Protein Treatment [100ml] / Коллагеновая маска для волос</t>
         </is>
       </c>
       <c r="D90" s="5" t="n">
-        <v>405</v>
+        <v>300</v>
       </c>
       <c r="E90" s="5" t="n">
-        <v>415</v>
+        <v>242</v>
       </c>
       <c r="F90" s="5" t="n">
-        <v>5690</v>
+        <v>3276</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>353</v>
+        <v>203</v>
       </c>
       <c r="H90" s="5" t="n">
-        <v>406</v>
+        <v>234</v>
       </c>
       <c r="I90" s="4" t="inlineStr">
         <is>
-          <t>J2K (ответ)</t>
+          <t>FINESKIN (ответ)</t>
         </is>
       </c>
       <c r="J90" s="5" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>-2.3</v>
+        <v>-3.6</v>
       </c>
       <c r="L90" s="5" t="n">
-        <v>-3954</v>
+        <v>-2595</v>
       </c>
     </row>
     <row r="91">
@@ -8559,7 +8605,7 @@
     </row>
     <row r="92">
       <c r="A92" s="4" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
@@ -8568,23 +8614,23 @@
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>CELIMAX THE REAL NONI MOISTURE BALANCING TONER (NEW) [150ml]/Восстанавливающий тонер с экстрактом нони</t>
+          <t>Celimax Dual Barrier Creamy Toner, тонер 150 мл</t>
         </is>
       </c>
       <c r="D92" s="5" t="n">
-        <v>23</v>
+        <v>4520</v>
       </c>
       <c r="E92" s="5" t="n">
-        <v>720</v>
+        <v>664</v>
       </c>
       <c r="F92" s="5" t="n">
-        <v>9886</v>
+        <v>9000</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>613</v>
+        <v>558</v>
       </c>
       <c r="H92" s="5" t="n">
-        <v>705</v>
+        <v>642</v>
       </c>
       <c r="I92" s="4" t="inlineStr">
         <is>
@@ -8592,20 +8638,20 @@
         </is>
       </c>
       <c r="J92" s="5" t="n">
-        <v>-15</v>
+        <v>-22</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>-2</v>
+        <v>-3.3</v>
       </c>
       <c r="L92" s="5" t="n">
-        <v>-338</v>
+        <v>-100163</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n"/>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C93" s="2" t="n"/>
@@ -8621,53 +8667,53 @@
     </row>
     <row r="94">
       <c r="A94" s="4" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>PETITFEE - Gold Hydrogel Mask Pack [5pcs] / Гидрогелевая маска для лица с золотом</t>
+          <t>ENOUGH - Collagen Whitening Moisture Cream 3in1 [50g] / Антивозрастной отбеливающий крем с коллагеном</t>
         </is>
       </c>
       <c r="D94" s="5" t="n">
-        <v>390</v>
+        <v>344</v>
       </c>
       <c r="E94" s="5" t="n">
-        <v>507</v>
+        <v>184</v>
       </c>
       <c r="F94" s="5" t="n">
-        <v>6990</v>
+        <v>2500</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>433</v>
+        <v>155</v>
       </c>
       <c r="H94" s="5" t="n">
-        <v>498</v>
+        <v>178</v>
       </c>
       <c r="I94" s="4" t="inlineStr">
         <is>
-          <t>J2K (ответ)</t>
+          <t>Классик</t>
         </is>
       </c>
       <c r="J94" s="5" t="n">
-        <v>-9</v>
+        <v>-6</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>-1.7</v>
+        <v>-3.1</v>
       </c>
       <c r="L94" s="5" t="n">
-        <v>-3421</v>
+        <v>-1937</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n"/>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>CELIMAX</t>
+          <t>SKIN1004</t>
         </is>
       </c>
       <c r="C95" s="2" t="n"/>
@@ -8683,53 +8729,53 @@
     </row>
     <row r="96">
       <c r="A96" s="4" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>CELIMAX</t>
+          <t>SKIN1004</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>CELIMAX DUAL BARRIER SKIN WEARABLE CREAM [50ml]/Крем для восстановления защитного барьера кожи лица</t>
+          <t>SKIN1004 - Madagascar Centella Ampoule [30ml] / Сыворотка для лица успокаивающая из экстракта центеллы.</t>
         </is>
       </c>
       <c r="D96" s="5" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="E96" s="5" t="n">
-        <v>864</v>
+        <v>368</v>
       </c>
       <c r="F96" s="5" t="n">
-        <v>11932</v>
+        <v>5038</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>740</v>
+        <v>312</v>
       </c>
       <c r="H96" s="5" t="n">
-        <v>851</v>
+        <v>359</v>
       </c>
       <c r="I96" s="4" t="inlineStr">
         <is>
-          <t>Papa Cosmetic</t>
+          <t>FINESKIN (ответ)</t>
         </is>
       </c>
       <c r="J96" s="5" t="n">
-        <v>-13</v>
+        <v>-9</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>-1.5</v>
+        <v>-2.4</v>
       </c>
       <c r="L96" s="5" t="n">
-        <v>-1203</v>
+        <v>-260</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n"/>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>VT COSMETICS</t>
+          <t>PETITFEE</t>
         </is>
       </c>
       <c r="C97" s="2" t="n"/>
@@ -8745,178 +8791,452 @@
     </row>
     <row r="98">
       <c r="A98" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr">
+        <is>
+          <t>PETITFEE - Gold &amp; Snail Hydrogel Eye Patch [60ea] / Гидрогелевые патчи для глаз с золотом и улиткой</t>
+        </is>
+      </c>
+      <c r="D98" s="5" t="n">
+        <v>144</v>
+      </c>
+      <c r="E98" s="5" t="n">
+        <v>415</v>
+      </c>
+      <c r="F98" s="5" t="n">
+        <v>5690</v>
+      </c>
+      <c r="G98" s="5" t="n">
+        <v>353</v>
+      </c>
+      <c r="H98" s="5" t="n">
+        <v>406</v>
+      </c>
+      <c r="I98" s="4" t="inlineStr">
+        <is>
+          <t>J2K (ответ)</t>
+        </is>
+      </c>
+      <c r="J98" s="5" t="n">
+        <v>-10</v>
+      </c>
+      <c r="K98" s="4" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="L98" s="5" t="n">
+        <v>-1406</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="4" t="n">
         <v>66</v>
       </c>
-      <c r="B98" s="4" t="inlineStr">
-        <is>
-          <t>VT COSMETICS</t>
-        </is>
-      </c>
-      <c r="C98" s="4" t="inlineStr">
-        <is>
-          <t>VT REEDLE SHOT 100 / Бустер-сыворотка с микроиглами</t>
-        </is>
-      </c>
-      <c r="D98" s="5" t="n">
-        <v>397</v>
-      </c>
-      <c r="E98" s="5" t="n">
-        <v>974</v>
-      </c>
-      <c r="F98" s="5" t="n">
-        <v>13568</v>
-      </c>
-      <c r="G98" s="5" t="n">
-        <v>841</v>
-      </c>
-      <c r="H98" s="5" t="n">
-        <v>967</v>
-      </c>
-      <c r="I98" s="4" t="inlineStr">
-        <is>
-          <t>FINESKIN (ответ)</t>
-        </is>
-      </c>
-      <c r="J98" s="5" t="n">
-        <v>-7</v>
-      </c>
-      <c r="K98" s="4" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="L98" s="5" t="n">
-        <v>-2637</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="n"/>
-      <c r="B99" s="2" t="inlineStr">
+      <c r="B99" s="4" t="inlineStr">
         <is>
           <t>PETITFEE</t>
         </is>
       </c>
-      <c r="C99" s="2" t="n"/>
-      <c r="D99" s="3" t="n"/>
-      <c r="E99" s="3" t="n"/>
-      <c r="F99" s="3" t="n"/>
-      <c r="G99" s="3" t="n"/>
-      <c r="H99" s="3" t="n"/>
-      <c r="I99" s="2" t="n"/>
-      <c r="J99" s="3" t="n"/>
-      <c r="K99" s="2" t="n"/>
-      <c r="L99" s="3" t="n"/>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>PETITFEE - Gold Hydrogel Eye Patch [60ea] / гидрогелевые патчи для глаз с золотом</t>
+        </is>
+      </c>
+      <c r="D99" s="5" t="n">
+        <v>405</v>
+      </c>
+      <c r="E99" s="5" t="n">
+        <v>415</v>
+      </c>
+      <c r="F99" s="5" t="n">
+        <v>5690</v>
+      </c>
+      <c r="G99" s="5" t="n">
+        <v>353</v>
+      </c>
+      <c r="H99" s="5" t="n">
+        <v>406</v>
+      </c>
+      <c r="I99" s="4" t="inlineStr">
+        <is>
+          <t>J2K (ответ)</t>
+        </is>
+      </c>
+      <c r="J99" s="5" t="n">
+        <v>-10</v>
+      </c>
+      <c r="K99" s="4" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="L99" s="5" t="n">
+        <v>-3954</v>
+      </c>
     </row>
     <row r="100">
-      <c r="A100" s="4" t="n">
-        <v>67</v>
-      </c>
-      <c r="B100" s="4" t="inlineStr">
-        <is>
-          <t>PETITFEE</t>
-        </is>
-      </c>
-      <c r="C100" s="4" t="inlineStr">
-        <is>
-          <t>PETITFEE - Bera Glucan Deep Firming Eye Patch [60ea] / Тканевые патчи для век увлажняющие</t>
-        </is>
-      </c>
-      <c r="D100" s="5" t="n">
-        <v>180</v>
-      </c>
-      <c r="E100" s="5" t="n">
-        <v>487</v>
-      </c>
-      <c r="F100" s="5" t="n">
-        <v>6790</v>
-      </c>
-      <c r="G100" s="5" t="n">
-        <v>421</v>
-      </c>
-      <c r="H100" s="5" t="n">
-        <v>484</v>
-      </c>
-      <c r="I100" s="4" t="inlineStr">
-        <is>
-          <t>J2K (ответ)</t>
-        </is>
-      </c>
-      <c r="J100" s="5" t="n">
-        <v>-3</v>
-      </c>
-      <c r="K100" s="4" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="L100" s="5" t="n">
-        <v>-461</v>
-      </c>
+      <c r="A100" s="2" t="n"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>CELIMAX</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="n"/>
+      <c r="D100" s="3" t="n"/>
+      <c r="E100" s="3" t="n"/>
+      <c r="F100" s="3" t="n"/>
+      <c r="G100" s="3" t="n"/>
+      <c r="H100" s="3" t="n"/>
+      <c r="I100" s="2" t="n"/>
+      <c r="J100" s="3" t="n"/>
+      <c r="K100" s="2" t="n"/>
+      <c r="L100" s="3" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>CELIMAX</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="inlineStr">
+        <is>
+          <t>CELIMAX THE REAL NONI MOISTURE BALANCING TONER (NEW) [150ml]/Восстанавливающий тонер с экстрактом нони</t>
+        </is>
+      </c>
+      <c r="D101" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="E101" s="5" t="n">
+        <v>720</v>
+      </c>
+      <c r="F101" s="5" t="n">
+        <v>9875</v>
+      </c>
+      <c r="G101" s="5" t="n">
+        <v>612</v>
+      </c>
+      <c r="H101" s="5" t="n">
+        <v>704</v>
+      </c>
+      <c r="I101" s="4" t="inlineStr">
+        <is>
+          <t>PAPA COSMETIC (ответ)</t>
+        </is>
+      </c>
+      <c r="J101" s="5" t="n">
+        <v>-15</v>
+      </c>
+      <c r="K101" s="4" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="L101" s="5" t="n">
+        <v>-356</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="n">
         <v>68</v>
       </c>
-      <c r="B101" s="4" t="inlineStr">
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t>CELIMAX</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="inlineStr">
+        <is>
+          <t>CELIMAX DUAL BARRIER SKIN WEARABLE CREAM [50ml]/Крем для восстановления защитного барьера кожи лица</t>
+        </is>
+      </c>
+      <c r="D102" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="E102" s="5" t="n">
+        <v>864</v>
+      </c>
+      <c r="F102" s="5" t="n">
+        <v>11900</v>
+      </c>
+      <c r="G102" s="5" t="n">
+        <v>738</v>
+      </c>
+      <c r="H102" s="5" t="n">
+        <v>848</v>
+      </c>
+      <c r="I102" s="4" t="inlineStr">
+        <is>
+          <t>PAPA COSMETIC (ответ)</t>
+        </is>
+      </c>
+      <c r="J102" s="5" t="n">
+        <v>-16</v>
+      </c>
+      <c r="K102" s="4" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="L102" s="5" t="n">
+        <v>-1408</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n"/>
+      <c r="B103" s="2" t="inlineStr">
         <is>
           <t>PETITFEE</t>
         </is>
       </c>
-      <c r="C101" s="4" t="inlineStr">
+      <c r="C103" s="2" t="n"/>
+      <c r="D103" s="3" t="n"/>
+      <c r="E103" s="3" t="n"/>
+      <c r="F103" s="3" t="n"/>
+      <c r="G103" s="3" t="n"/>
+      <c r="H103" s="3" t="n"/>
+      <c r="I103" s="2" t="n"/>
+      <c r="J103" s="3" t="n"/>
+      <c r="K103" s="2" t="n"/>
+      <c r="L103" s="3" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="4" t="n">
+        <v>69</v>
+      </c>
+      <c r="B104" s="4" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="inlineStr">
+        <is>
+          <t>PETITFEE - Gold Hydrogel Mask Pack [5pcs] / Гидрогелевая маска для лица с золотом</t>
+        </is>
+      </c>
+      <c r="D104" s="5" t="n">
+        <v>390</v>
+      </c>
+      <c r="E104" s="5" t="n">
+        <v>507</v>
+      </c>
+      <c r="F104" s="5" t="n">
+        <v>6990</v>
+      </c>
+      <c r="G104" s="5" t="n">
+        <v>433</v>
+      </c>
+      <c r="H104" s="5" t="n">
+        <v>498</v>
+      </c>
+      <c r="I104" s="4" t="inlineStr">
+        <is>
+          <t>J2K (ответ)</t>
+        </is>
+      </c>
+      <c r="J104" s="5" t="n">
+        <v>-9</v>
+      </c>
+      <c r="K104" s="4" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="L104" s="5" t="n">
+        <v>-3421</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n"/>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>VT COSMETICS</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="n"/>
+      <c r="D105" s="3" t="n"/>
+      <c r="E105" s="3" t="n"/>
+      <c r="F105" s="3" t="n"/>
+      <c r="G105" s="3" t="n"/>
+      <c r="H105" s="3" t="n"/>
+      <c r="I105" s="2" t="n"/>
+      <c r="J105" s="3" t="n"/>
+      <c r="K105" s="2" t="n"/>
+      <c r="L105" s="3" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="B106" s="4" t="inlineStr">
+        <is>
+          <t>VT COSMETICS</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="inlineStr">
+        <is>
+          <t>VT REEDLE SHOT 100 / Бустер-сыворотка с микроиглами</t>
+        </is>
+      </c>
+      <c r="D106" s="5" t="n">
+        <v>397</v>
+      </c>
+      <c r="E106" s="5" t="n">
+        <v>974</v>
+      </c>
+      <c r="F106" s="5" t="n">
+        <v>13568</v>
+      </c>
+      <c r="G106" s="5" t="n">
+        <v>841</v>
+      </c>
+      <c r="H106" s="5" t="n">
+        <v>967</v>
+      </c>
+      <c r="I106" s="4" t="inlineStr">
+        <is>
+          <t>FINESKIN (ответ)</t>
+        </is>
+      </c>
+      <c r="J106" s="5" t="n">
+        <v>-7</v>
+      </c>
+      <c r="K106" s="4" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="L106" s="5" t="n">
+        <v>-2637</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n"/>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="n"/>
+      <c r="D107" s="3" t="n"/>
+      <c r="E107" s="3" t="n"/>
+      <c r="F107" s="3" t="n"/>
+      <c r="G107" s="3" t="n"/>
+      <c r="H107" s="3" t="n"/>
+      <c r="I107" s="2" t="n"/>
+      <c r="J107" s="3" t="n"/>
+      <c r="K107" s="2" t="n"/>
+      <c r="L107" s="3" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="4" t="n">
+        <v>71</v>
+      </c>
+      <c r="B108" s="4" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="inlineStr">
+        <is>
+          <t>PETITFEE - Bera Glucan Deep Firming Eye Patch [60ea] / Тканевые патчи для век увлажняющие</t>
+        </is>
+      </c>
+      <c r="D108" s="5" t="n">
+        <v>180</v>
+      </c>
+      <c r="E108" s="5" t="n">
+        <v>487</v>
+      </c>
+      <c r="F108" s="5" t="n">
+        <v>6790</v>
+      </c>
+      <c r="G108" s="5" t="n">
+        <v>421</v>
+      </c>
+      <c r="H108" s="5" t="n">
+        <v>484</v>
+      </c>
+      <c r="I108" s="4" t="inlineStr">
+        <is>
+          <t>J2K (ответ)</t>
+        </is>
+      </c>
+      <c r="J108" s="5" t="n">
+        <v>-3</v>
+      </c>
+      <c r="K108" s="4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="L108" s="5" t="n">
+        <v>-461</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="inlineStr">
         <is>
           <t>PETITFEE - Pink Vita Brightening Eye Patch [60ea] / Тканевые патчи для век увлажняющие</t>
         </is>
       </c>
-      <c r="D101" s="5" t="n">
+      <c r="D109" s="5" t="n">
         <v>117</v>
       </c>
-      <c r="E101" s="5" t="n">
+      <c r="E109" s="5" t="n">
         <v>487</v>
       </c>
-      <c r="F101" s="5" t="n">
+      <c r="F109" s="5" t="n">
         <v>6790</v>
       </c>
-      <c r="G101" s="5" t="n">
+      <c r="G109" s="5" t="n">
         <v>421</v>
       </c>
-      <c r="H101" s="5" t="n">
+      <c r="H109" s="5" t="n">
         <v>484</v>
       </c>
-      <c r="I101" s="4" t="inlineStr">
+      <c r="I109" s="4" t="inlineStr">
         <is>
           <t>J2K (ответ)</t>
         </is>
       </c>
-      <c r="J101" s="5" t="n">
+      <c r="J109" s="5" t="n">
         <v>-3</v>
       </c>
-      <c r="K101" s="4" t="n">
+      <c r="K109" s="4" t="n">
         <v>-0.5</v>
       </c>
-      <c r="L101" s="5" t="n">
+      <c r="L109" s="5" t="n">
         <v>-300</v>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="9" t="inlineStr"/>
-      <c r="B102" s="9" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="9" t="inlineStr"/>
+      <c r="B110" s="9" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="C102" s="9" t="inlineStr">
-        <is>
-          <t>позиций: 68</t>
-        </is>
-      </c>
-      <c r="D102" s="10" t="n">
-        <v>68738</v>
-      </c>
-      <c r="E102" s="10" t="inlineStr"/>
-      <c r="F102" s="10" t="inlineStr"/>
-      <c r="G102" s="10" t="inlineStr"/>
-      <c r="H102" s="10" t="inlineStr"/>
-      <c r="I102" s="9" t="inlineStr"/>
-      <c r="J102" s="10" t="inlineStr"/>
-      <c r="K102" s="9" t="inlineStr"/>
-      <c r="L102" s="10" t="n">
-        <v>-3399947</v>
+      <c r="C110" s="9" t="inlineStr">
+        <is>
+          <t>позиций: 72</t>
+        </is>
+      </c>
+      <c r="D110" s="10" t="n">
+        <v>78646</v>
+      </c>
+      <c r="E110" s="10" t="inlineStr"/>
+      <c r="F110" s="10" t="inlineStr"/>
+      <c r="G110" s="10" t="inlineStr"/>
+      <c r="H110" s="10" t="inlineStr"/>
+      <c r="I110" s="9" t="inlineStr"/>
+      <c r="J110" s="10" t="inlineStr"/>
+      <c r="K110" s="9" t="inlineStr"/>
+      <c r="L110" s="10" t="n">
+        <v>-4232854</v>
       </c>
     </row>
   </sheetData>
@@ -8930,7 +9250,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L39"/>
+  <dimension ref="A1:L44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -9356,11 +9676,11 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>PETITFEE - Chamomile Lightening Hydrogel Eye Patch [60ea] / Успокаивающие гидрогелевые патчи для глаз с экстрактом ромашки</t>
+          <t>PETITFEE - Agave Cooling Hydrogel Eye Patch [60ea] / Охлаждающие гидрогелевые патчи для глаз с экстрактом агавы</t>
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>415</v>
@@ -9386,7 +9706,7 @@
         <v>6.2</v>
       </c>
       <c r="L12" s="7" t="n">
-        <v>0</v>
+        <v>9319</v>
       </c>
     </row>
     <row r="13">
@@ -9400,11 +9720,11 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>PETITFEE - Agave Cooling Hydrogel Eye Patch [60ea] / Охлаждающие гидрогелевые патчи для глаз с экстрактом агавы</t>
+          <t>PETITFEE - Chamomile Lightening Hydrogel Eye Patch [60ea] / Успокаивающие гидрогелевые патчи для глаз с экстрактом ромашки</t>
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>360</v>
+        <v>0</v>
       </c>
       <c r="E13" s="7" t="n">
         <v>415</v>
@@ -9430,7 +9750,7 @@
         <v>6.2</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>9319</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -9444,11 +9764,11 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>PETITFEE - Artichoke Soothing Hydrogel Eye Patch [60ea] / Смягчающие гидрогелевые патчи для глаз с экстрактом артишока</t>
+          <t>PETITFEE - Cacao Energizing Hydrogel Eye Patch [60ea] / Тонизирующие гидрогелевые патчи для глаз с экстрактом какао</t>
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>156</v>
+        <v>72</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>415</v>
@@ -9474,7 +9794,7 @@
         <v>6.2</v>
       </c>
       <c r="L14" s="7" t="n">
-        <v>4038</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="15">
@@ -9488,11 +9808,11 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>PETITFEE - Cacao Energizing Hydrogel Eye Patch [60ea] / Тонизирующие гидрогелевые патчи для глаз с экстрактом какао</t>
+          <t>PETITFEE - Artichoke Soothing Hydrogel Eye Patch [60ea] / Смягчающие гидрогелевые патчи для глаз с экстрактом артишока</t>
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>72</v>
+        <v>156</v>
       </c>
       <c r="E15" s="7" t="n">
         <v>415</v>
@@ -9518,14 +9838,14 @@
         <v>6.2</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>1864</v>
+        <v>4038</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>FARMSTAY</t>
+          <t>MANYO</t>
         </is>
       </c>
       <c r="C16" s="2" t="n"/>
@@ -9545,49 +9865,49 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>FARMSTAY</t>
+          <t>MANYO</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>FARMSTAY - Gold Snail Premium Cream [50ml] / Омолаживающий крем с муцином улитки и коллоидным золотом</t>
+          <t>MANYO BIFIDA INFUSION SHOT AMPOULE 1DX [50ml] / Сыворотка с микроиглами и пробиотиками</t>
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>900</v>
+        <v>614</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>431</v>
+        <v>997</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>6390</v>
+        <v>14820</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>396</v>
+        <v>919</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>456</v>
+        <v>1057</v>
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>Классик</t>
+          <t>PAPA COSMETIC (ответ)</t>
         </is>
       </c>
       <c r="J17" s="7" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="L17" s="7" t="n">
-        <v>22101</v>
+        <v>36788</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>FARMSTAY</t>
         </is>
       </c>
       <c r="C18" s="2" t="n"/>
@@ -9607,91 +9927,65 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
+          <t>FARMSTAY</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>FARMSTAY - Gold Snail Premium Cream [50ml] / Омолаживающий крем с муцином улитки и коллоидным золотом</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="n">
+        <v>900</v>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>431</v>
+      </c>
+      <c r="F19" s="7" t="n">
+        <v>6390</v>
+      </c>
+      <c r="G19" s="7" t="n">
+        <v>396</v>
+      </c>
+      <c r="H19" s="7" t="n">
+        <v>456</v>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>Классик</t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="K19" s="6" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="L19" s="7" t="n">
+        <v>22101</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>PETITFEE</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>PETITFEE - Gold &amp; EGF Hydrogel Eye &amp; Spot Patch [60ea]/ гидрогелевые патчи с золотом и EGF</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="7" t="n">
-        <v>385</v>
-      </c>
-      <c r="F19" s="7" t="n">
-        <v>5690</v>
-      </c>
-      <c r="G19" s="7" t="n">
-        <v>353</v>
-      </c>
-      <c r="H19" s="7" t="n">
-        <v>406</v>
-      </c>
-      <c r="I19" s="6" t="inlineStr">
-        <is>
-          <t>J2K (ответ)</t>
-        </is>
-      </c>
-      <c r="J19" s="7" t="n">
-        <v>21</v>
-      </c>
-      <c r="K19" s="6" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="L19" s="7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>PETITFEE</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>PETITFEE - Collagen &amp; CoQ10 Hydrogel Eye Patch [60ea] / Гидрогелевые патчи для глаз с коллагеном и коэнзимом Q10</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="n">
-        <v>360</v>
-      </c>
-      <c r="E20" s="7" t="n">
-        <v>385</v>
-      </c>
-      <c r="F20" s="7" t="n">
-        <v>5690</v>
-      </c>
-      <c r="G20" s="7" t="n">
-        <v>353</v>
-      </c>
-      <c r="H20" s="7" t="n">
-        <v>406</v>
-      </c>
-      <c r="I20" s="6" t="inlineStr">
-        <is>
-          <t>J2K (ответ)</t>
-        </is>
-      </c>
-      <c r="J20" s="7" t="n">
-        <v>21</v>
-      </c>
-      <c r="K20" s="6" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="L20" s="7" t="n">
-        <v>7433</v>
-      </c>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="3" t="n"/>
+      <c r="E20" s="3" t="n"/>
+      <c r="F20" s="3" t="n"/>
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
+      <c r="I20" s="2" t="n"/>
+      <c r="J20" s="3" t="n"/>
+      <c r="K20" s="2" t="n"/>
+      <c r="L20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
@@ -9700,14 +9994,14 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Eye Patch [60ea] / Гидрогелевые патчи для глаз с черным жемчугом и золотом</t>
+          <t>PETITFEE - Collagen &amp; CoQ10 Hydrogel Eye Patch [60ea] / Гидрогелевые патчи для глаз с коллагеном и коэнзимом Q10</t>
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>216</v>
+        <v>360</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="F21" s="7" t="n">
         <v>5690</v>
@@ -9724,462 +10018,462 @@
         </is>
       </c>
       <c r="J21" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="K21" s="6" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="L21" s="7" t="n">
+        <v>7433</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>PETITFEE - Gold &amp; EGF Hydrogel Eye &amp; Spot Patch [60ea]/ гидрогелевые патчи с золотом и EGF</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="7" t="n">
+        <v>385</v>
+      </c>
+      <c r="F22" s="7" t="n">
+        <v>5690</v>
+      </c>
+      <c r="G22" s="7" t="n">
+        <v>353</v>
+      </c>
+      <c r="H22" s="7" t="n">
+        <v>406</v>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>J2K (ответ)</t>
+        </is>
+      </c>
+      <c r="J22" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="K22" s="6" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="L22" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>MANYO</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="3" t="n"/>
+      <c r="E23" s="3" t="n"/>
+      <c r="F23" s="3" t="n"/>
+      <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
+      <c r="I23" s="2" t="n"/>
+      <c r="J23" s="3" t="n"/>
+      <c r="K23" s="2" t="n"/>
+      <c r="L23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>MANYO</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>MANYO - Galac Whitening Vita Serum [50ml] / Осветляющая сыворотка с Витамином C</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>759</v>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>647</v>
+      </c>
+      <c r="F24" s="7" t="n">
+        <v>9500</v>
+      </c>
+      <c r="G24" s="7" t="n">
+        <v>589</v>
+      </c>
+      <c r="H24" s="7" t="n">
+        <v>677</v>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>PAPA COSMETIC (ответ)</t>
+        </is>
+      </c>
+      <c r="J24" s="7" t="n">
+        <v>31</v>
+      </c>
+      <c r="K24" s="6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L24" s="7" t="n">
+        <v>23165</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n"/>
+      <c r="D25" s="3" t="n"/>
+      <c r="E25" s="3" t="n"/>
+      <c r="F25" s="3" t="n"/>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
+      <c r="I25" s="2" t="n"/>
+      <c r="J25" s="3" t="n"/>
+      <c r="K25" s="2" t="n"/>
+      <c r="L25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Eye Patch [60ea] / Гидрогелевые патчи для глаз с черным жемчугом и золотом</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>216</v>
+      </c>
+      <c r="E26" s="7" t="n">
+        <v>388</v>
+      </c>
+      <c r="F26" s="7" t="n">
+        <v>5690</v>
+      </c>
+      <c r="G26" s="7" t="n">
+        <v>353</v>
+      </c>
+      <c r="H26" s="7" t="n">
+        <v>406</v>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>J2K (ответ)</t>
+        </is>
+      </c>
+      <c r="J26" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="K21" s="6" t="n">
+      <c r="K26" s="6" t="n">
         <v>4.7</v>
       </c>
-      <c r="L21" s="7" t="n">
+      <c r="L26" s="7" t="n">
         <v>3894</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="n"/>
-      <c r="B22" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="n"/>
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>CELIMAX</t>
         </is>
       </c>
-      <c r="C22" s="2" t="n"/>
-      <c r="D22" s="3" t="n"/>
-      <c r="E22" s="3" t="n"/>
-      <c r="F22" s="3" t="n"/>
-      <c r="G22" s="3" t="n"/>
-      <c r="H22" s="3" t="n"/>
-      <c r="I22" s="2" t="n"/>
-      <c r="J22" s="3" t="n"/>
-      <c r="K22" s="2" t="n"/>
-      <c r="L22" s="3" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>CELIMAX</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>CELIMAX THE REAL NONI ENERGY AMPOULE_30ML (NEW) [30ml]/Восстанавливающая сыворотка с экстрактом нони для лица</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="n">
-        <v>57</v>
-      </c>
-      <c r="E23" s="7" t="n">
-        <v>764</v>
-      </c>
-      <c r="F23" s="7" t="n">
-        <v>11194</v>
-      </c>
-      <c r="G23" s="7" t="n">
-        <v>694</v>
-      </c>
-      <c r="H23" s="7" t="n">
-        <v>798</v>
-      </c>
-      <c r="I23" s="6" t="inlineStr">
-        <is>
-          <t>G&amp;E Global</t>
-        </is>
-      </c>
-      <c r="J23" s="7" t="n">
-        <v>34</v>
-      </c>
-      <c r="K23" s="6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L23" s="7" t="n">
-        <v>1955</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="n"/>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>ROUND LAB</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="n"/>
-      <c r="D24" s="3" t="n"/>
-      <c r="E24" s="3" t="n"/>
-      <c r="F24" s="3" t="n"/>
-      <c r="G24" s="3" t="n"/>
-      <c r="H24" s="3" t="n"/>
-      <c r="I24" s="2" t="n"/>
-      <c r="J24" s="3" t="n"/>
-      <c r="K24" s="2" t="n"/>
-      <c r="L24" s="3" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>ROUND LAB</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>ROUND LAB 1025 DOKDO TONER_200ml / Отшелушивающий тоник с морской водой</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="n">
-        <v>966</v>
-      </c>
-      <c r="E25" s="7" t="n">
-        <v>485</v>
-      </c>
-      <c r="F25" s="7" t="n">
-        <v>7100</v>
-      </c>
-      <c r="G25" s="7" t="n">
-        <v>440</v>
-      </c>
-      <c r="H25" s="7" t="n">
-        <v>506</v>
-      </c>
-      <c r="I25" s="6" t="inlineStr">
-        <is>
-          <t>Papa Cosmetic</t>
-        </is>
-      </c>
-      <c r="J25" s="7" t="n">
-        <v>21</v>
-      </c>
-      <c r="K25" s="6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L25" s="7" t="n">
-        <v>20576</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="n"/>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>PETITFEE</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="n"/>
-      <c r="D26" s="3" t="n"/>
-      <c r="E26" s="3" t="n"/>
-      <c r="F26" s="3" t="n"/>
-      <c r="G26" s="3" t="n"/>
-      <c r="H26" s="3" t="n"/>
-      <c r="I26" s="2" t="n"/>
-      <c r="J26" s="3" t="n"/>
-      <c r="K26" s="2" t="n"/>
-      <c r="L26" s="3" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>PETITFEE</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>PETITFEE - Artichoke Soothing Hydrogel Face Mask [5pcs] / Смягчающая гидрогелевая маска для лица с экстрактом артишока</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="E27" s="7" t="n">
-        <v>499</v>
-      </c>
-      <c r="F27" s="7" t="n">
-        <v>7290</v>
-      </c>
-      <c r="G27" s="7" t="n">
-        <v>452</v>
-      </c>
-      <c r="H27" s="7" t="n">
-        <v>520</v>
-      </c>
-      <c r="I27" s="6" t="inlineStr">
-        <is>
-          <t>J2K (ответ)</t>
-        </is>
-      </c>
-      <c r="J27" s="7" t="n">
-        <v>21</v>
-      </c>
-      <c r="K27" s="6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L27" s="7" t="n">
-        <v>1274</v>
-      </c>
+      <c r="C27" s="2" t="n"/>
+      <c r="D27" s="3" t="n"/>
+      <c r="E27" s="3" t="n"/>
+      <c r="F27" s="3" t="n"/>
+      <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
+      <c r="I27" s="2" t="n"/>
+      <c r="J27" s="3" t="n"/>
+      <c r="K27" s="2" t="n"/>
+      <c r="L27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>CELIMAX</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>CELIMAX THE REAL NONI ENERGY AMPOULE_30ML (NEW) [30ml]/Восстанавливающая сыворотка с экстрактом нони для лица</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>57</v>
+      </c>
+      <c r="E28" s="7" t="n">
+        <v>764</v>
+      </c>
+      <c r="F28" s="7" t="n">
+        <v>11194</v>
+      </c>
+      <c r="G28" s="7" t="n">
+        <v>694</v>
+      </c>
+      <c r="H28" s="7" t="n">
+        <v>798</v>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>G&amp;E Global</t>
+        </is>
+      </c>
+      <c r="J28" s="7" t="n">
+        <v>34</v>
+      </c>
+      <c r="K28" s="6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L28" s="7" t="n">
+        <v>1955</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>ROUND LAB</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n"/>
+      <c r="D29" s="3" t="n"/>
+      <c r="E29" s="3" t="n"/>
+      <c r="F29" s="3" t="n"/>
+      <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
+      <c r="I29" s="2" t="n"/>
+      <c r="J29" s="3" t="n"/>
+      <c r="K29" s="2" t="n"/>
+      <c r="L29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>ROUND LAB</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>ROUND LAB 1025 DOKDO TONER_200ml / Отшелушивающий тоник с морской водой</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="n">
+        <v>966</v>
+      </c>
+      <c r="E30" s="7" t="n">
+        <v>485</v>
+      </c>
+      <c r="F30" s="7" t="n">
+        <v>7100</v>
+      </c>
+      <c r="G30" s="7" t="n">
+        <v>440</v>
+      </c>
+      <c r="H30" s="7" t="n">
+        <v>506</v>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>Papa Cosmetic</t>
+        </is>
+      </c>
+      <c r="J30" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="K30" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L30" s="7" t="n">
+        <v>20576</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n"/>
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>PETITFEE</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Mask Pack [5pcs] / Гидрогелевая маска для лица с черным жемчугом и золотом</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="n">
-        <v>90</v>
-      </c>
-      <c r="E28" s="7" t="n">
-        <v>478</v>
-      </c>
-      <c r="F28" s="7" t="n">
-        <v>6990</v>
-      </c>
-      <c r="G28" s="7" t="n">
-        <v>433</v>
-      </c>
-      <c r="H28" s="7" t="n">
-        <v>498</v>
-      </c>
-      <c r="I28" s="6" t="inlineStr">
+      <c r="C31" s="2" t="n"/>
+      <c r="D31" s="3" t="n"/>
+      <c r="E31" s="3" t="n"/>
+      <c r="F31" s="3" t="n"/>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
+      <c r="I31" s="2" t="n"/>
+      <c r="J31" s="3" t="n"/>
+      <c r="K31" s="2" t="n"/>
+      <c r="L31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>PETITFEE - Artichoke Soothing Hydrogel Face Mask [5pcs] / Смягчающая гидрогелевая маска для лица с экстрактом артишока</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="E32" s="7" t="n">
+        <v>499</v>
+      </c>
+      <c r="F32" s="7" t="n">
+        <v>7290</v>
+      </c>
+      <c r="G32" s="7" t="n">
+        <v>452</v>
+      </c>
+      <c r="H32" s="7" t="n">
+        <v>520</v>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
         <is>
           <t>J2K (ответ)</t>
         </is>
       </c>
-      <c r="J28" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="K28" s="6" t="n">
+      <c r="J32" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="K32" s="6" t="n">
         <v>4.3</v>
       </c>
-      <c r="L28" s="7" t="n">
-        <v>1830</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="n">
-        <v>19</v>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>PETITFEE</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>PETITFEE - Gold &amp; Snail Hydrogel Mask Pack [5pcs] / Гидрогелевая маска для лица с золотом и экстрактом улитки</t>
-        </is>
-      </c>
-      <c r="D29" s="7" t="n">
-        <v>150</v>
-      </c>
-      <c r="E29" s="7" t="n">
-        <v>478</v>
-      </c>
-      <c r="F29" s="7" t="n">
-        <v>6990</v>
-      </c>
-      <c r="G29" s="7" t="n">
-        <v>433</v>
-      </c>
-      <c r="H29" s="7" t="n">
-        <v>498</v>
-      </c>
-      <c r="I29" s="6" t="inlineStr">
-        <is>
-          <t>J2K (ответ)</t>
-        </is>
-      </c>
-      <c r="J29" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="K29" s="6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L29" s="7" t="n">
-        <v>3033</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="n"/>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>THE ORDINARY</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="n"/>
-      <c r="D30" s="3" t="n"/>
-      <c r="E30" s="3" t="n"/>
-      <c r="F30" s="3" t="n"/>
-      <c r="G30" s="3" t="n"/>
-      <c r="H30" s="3" t="n"/>
-      <c r="I30" s="2" t="n"/>
-      <c r="J30" s="3" t="n"/>
-      <c r="K30" s="2" t="n"/>
-      <c r="L30" s="3" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>THE ORDINARY</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>THE ORDINARY - Glycolic Acid 7% Toning Solution [KOR] [240ml] / Тоник с гликолевой кислотой 7%</t>
-        </is>
-      </c>
-      <c r="D31" s="7" t="n">
-        <v>31</v>
-      </c>
-      <c r="E31" s="7" t="n">
-        <v>845</v>
-      </c>
-      <c r="F31" s="7" t="n">
-        <v>12214</v>
-      </c>
-      <c r="G31" s="7" t="n">
-        <v>757</v>
-      </c>
-      <c r="H31" s="7" t="n">
-        <v>871</v>
-      </c>
-      <c r="I31" s="6" t="inlineStr">
-        <is>
-          <t>FINESKIN (ответ)</t>
-        </is>
-      </c>
-      <c r="J31" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="K31" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="L31" s="7" t="n">
-        <v>786</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="n"/>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>CELIMAX</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="n"/>
-      <c r="D32" s="3" t="n"/>
-      <c r="E32" s="3" t="n"/>
-      <c r="F32" s="3" t="n"/>
-      <c r="G32" s="3" t="n"/>
-      <c r="H32" s="3" t="n"/>
-      <c r="I32" s="2" t="n"/>
-      <c r="J32" s="3" t="n"/>
-      <c r="K32" s="2" t="n"/>
-      <c r="L32" s="3" t="n"/>
+      <c r="L32" s="7" t="n">
+        <v>1274</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>CELIMAX</t>
+          <t>PETITFEE</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>CELIMAX PORE+DARK SPOT BRIGHTENING SERUM_30ml [30ml]/Сыворотка для выравнивания тона и рельефа кожи лица</t>
+          <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Mask Pack [5pcs] / Гидрогелевая маска для лица с черным жемчугом и золотом</t>
         </is>
       </c>
       <c r="D33" s="7" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>688</v>
+        <v>478</v>
       </c>
       <c r="F33" s="7" t="n">
-        <v>9900</v>
+        <v>6990</v>
       </c>
       <c r="G33" s="7" t="n">
-        <v>614</v>
+        <v>433</v>
       </c>
       <c r="H33" s="7" t="n">
-        <v>706</v>
+        <v>498</v>
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>G&amp;E Global</t>
+          <t>J2K (ответ)</t>
         </is>
       </c>
       <c r="J33" s="7" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>2.7</v>
+        <v>4.3</v>
       </c>
       <c r="L33" s="7" t="n">
-        <v>1280</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>CELIMAX</t>
+          <t>PETITFEE</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>CELIMAX PORE+DARK SPOT BRIGHTENING PAD [100ml / 40pads]/Тонер-пэды для выравнивания тона и рельефа кожи</t>
+          <t>PETITFEE - Gold &amp; Snail Hydrogel Mask Pack [5pcs] / Гидрогелевая маска для лица с золотом и экстрактом улитки</t>
         </is>
       </c>
       <c r="D34" s="7" t="n">
-        <v>1375</v>
+        <v>150</v>
       </c>
       <c r="E34" s="7" t="n">
-        <v>556</v>
+        <v>478</v>
       </c>
       <c r="F34" s="7" t="n">
-        <v>7950</v>
+        <v>6990</v>
       </c>
       <c r="G34" s="7" t="n">
-        <v>493</v>
+        <v>433</v>
       </c>
       <c r="H34" s="7" t="n">
-        <v>567</v>
+        <v>498</v>
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
-          <t>G&amp;E Global</t>
+          <t>J2K (ответ)</t>
         </is>
       </c>
       <c r="J34" s="7" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>1.9</v>
+        <v>4.2</v>
       </c>
       <c r="L34" s="7" t="n">
-        <v>14651</v>
+        <v>3033</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>VT COSMETICS</t>
+          <t>THE ORDINARY</t>
         </is>
       </c>
       <c r="C35" s="2" t="n"/>
@@ -10195,32 +10489,32 @@
     </row>
     <row r="36">
       <c r="A36" s="6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>VT COSMETICS</t>
+          <t>THE ORDINARY</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>VT PDRN ESSENCE 100 / Укрепляющая бустер-эссенция с ПДРН</t>
+          <t>THE ORDINARY - Glycolic Acid 7% Toning Solution [KOR] [240ml] / Тоник с гликолевой кислотой 7%</t>
         </is>
       </c>
       <c r="D36" s="7" t="n">
-        <v>1009</v>
+        <v>31</v>
       </c>
       <c r="E36" s="7" t="n">
-        <v>1336</v>
+        <v>845</v>
       </c>
       <c r="F36" s="7" t="n">
-        <v>19080</v>
+        <v>12214</v>
       </c>
       <c r="G36" s="7" t="n">
-        <v>1183</v>
+        <v>757</v>
       </c>
       <c r="H36" s="7" t="n">
-        <v>1360</v>
+        <v>871</v>
       </c>
       <c r="I36" s="6" t="inlineStr">
         <is>
@@ -10228,20 +10522,20 @@
         </is>
       </c>
       <c r="J36" s="7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="L36" s="7" t="n">
-        <v>24674</v>
+        <v>786</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>CELIMAX</t>
         </is>
       </c>
       <c r="C37" s="2" t="n"/>
@@ -10257,72 +10551,240 @@
     </row>
     <row r="38">
       <c r="A38" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>CELIMAX</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>CELIMAX PORE+DARK SPOT BRIGHTENING SERUM_30ml [30ml]/Сыворотка для выравнивания тона и рельефа кожи лица</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="n">
+        <v>70</v>
+      </c>
+      <c r="E38" s="7" t="n">
+        <v>688</v>
+      </c>
+      <c r="F38" s="7" t="n">
+        <v>9900</v>
+      </c>
+      <c r="G38" s="7" t="n">
+        <v>614</v>
+      </c>
+      <c r="H38" s="7" t="n">
+        <v>706</v>
+      </c>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>G&amp;E Global</t>
+        </is>
+      </c>
+      <c r="J38" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="K38" s="6" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L38" s="7" t="n">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="n">
         <v>24</v>
       </c>
-      <c r="B38" s="6" t="inlineStr">
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>CELIMAX</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>CELIMAX PORE+DARK SPOT BRIGHTENING PAD [100ml / 40pads]/Тонер-пэды для выравнивания тона и рельефа кожи</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="n">
+        <v>1375</v>
+      </c>
+      <c r="E39" s="7" t="n">
+        <v>556</v>
+      </c>
+      <c r="F39" s="7" t="n">
+        <v>7950</v>
+      </c>
+      <c r="G39" s="7" t="n">
+        <v>493</v>
+      </c>
+      <c r="H39" s="7" t="n">
+        <v>567</v>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>G&amp;E Global</t>
+        </is>
+      </c>
+      <c r="J39" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="K39" s="6" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="L39" s="7" t="n">
+        <v>14651</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>VT COSMETICS</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="n"/>
+      <c r="D40" s="3" t="n"/>
+      <c r="E40" s="3" t="n"/>
+      <c r="F40" s="3" t="n"/>
+      <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
+      <c r="I40" s="2" t="n"/>
+      <c r="J40" s="3" t="n"/>
+      <c r="K40" s="2" t="n"/>
+      <c r="L40" s="3" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>VT COSMETICS</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>VT PDRN ESSENCE 100 / Укрепляющая бустер-эссенция с ПДРН</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="n">
+        <v>1009</v>
+      </c>
+      <c r="E41" s="7" t="n">
+        <v>1336</v>
+      </c>
+      <c r="F41" s="7" t="n">
+        <v>19080</v>
+      </c>
+      <c r="G41" s="7" t="n">
+        <v>1183</v>
+      </c>
+      <c r="H41" s="7" t="n">
+        <v>1360</v>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>FINESKIN (ответ)</t>
+        </is>
+      </c>
+      <c r="J41" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="K41" s="6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L41" s="7" t="n">
+        <v>24674</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n"/>
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>PETITFEE</t>
         </is>
       </c>
-      <c r="C38" s="6" t="inlineStr">
+      <c r="C42" s="2" t="n"/>
+      <c r="D42" s="3" t="n"/>
+      <c r="E42" s="3" t="n"/>
+      <c r="F42" s="3" t="n"/>
+      <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
+      <c r="I42" s="2" t="n"/>
+      <c r="J42" s="3" t="n"/>
+      <c r="K42" s="2" t="n"/>
+      <c r="L42" s="3" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
         <is>
           <t>PETITFEE - Cacao Energizing Hydrogel Mask Pack [5pcs] / Тонизирующая гидрогелевая маска для лица с экстрактом какао</t>
         </is>
       </c>
-      <c r="D38" s="7" t="n">
+      <c r="D43" s="7" t="n">
         <v>90</v>
       </c>
-      <c r="E38" s="7" t="n">
+      <c r="E43" s="7" t="n">
         <v>497</v>
       </c>
-      <c r="F38" s="7" t="n">
+      <c r="F43" s="7" t="n">
         <v>6990</v>
       </c>
-      <c r="G38" s="7" t="n">
+      <c r="G43" s="7" t="n">
         <v>433</v>
       </c>
-      <c r="H38" s="7" t="n">
+      <c r="H43" s="7" t="n">
         <v>498</v>
       </c>
-      <c r="I38" s="6" t="inlineStr">
+      <c r="I43" s="6" t="inlineStr">
         <is>
           <t>J2K (ответ)</t>
         </is>
       </c>
-      <c r="J38" s="7" t="n">
+      <c r="J43" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="K38" s="6" t="n">
+      <c r="K43" s="6" t="n">
         <v>0.3</v>
       </c>
-      <c r="L38" s="7" t="n">
+      <c r="L43" s="7" t="n">
         <v>137</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="9" t="inlineStr"/>
-      <c r="B39" s="9" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="9" t="inlineStr"/>
+      <c r="B44" s="9" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="C39" s="9" t="inlineStr">
-        <is>
-          <t>позиций: 24</t>
-        </is>
-      </c>
-      <c r="D39" s="10" t="n">
-        <v>27520</v>
-      </c>
-      <c r="E39" s="10" t="inlineStr"/>
-      <c r="F39" s="10" t="inlineStr"/>
-      <c r="G39" s="10" t="inlineStr"/>
-      <c r="H39" s="10" t="inlineStr"/>
-      <c r="I39" s="9" t="inlineStr"/>
-      <c r="J39" s="10" t="inlineStr"/>
-      <c r="K39" s="9" t="inlineStr"/>
-      <c r="L39" s="10" t="n">
-        <v>2466636</v>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>позиций: 26</t>
+        </is>
+      </c>
+      <c r="D44" s="10" t="n">
+        <v>28893</v>
+      </c>
+      <c r="E44" s="10" t="inlineStr"/>
+      <c r="F44" s="10" t="inlineStr"/>
+      <c r="G44" s="10" t="inlineStr"/>
+      <c r="H44" s="10" t="inlineStr"/>
+      <c r="I44" s="9" t="inlineStr"/>
+      <c r="J44" s="10" t="inlineStr"/>
+      <c r="K44" s="9" t="inlineStr"/>
+      <c r="L44" s="10" t="n">
+        <v>2526589</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Склад против Кореи.xlsx
+++ b/outputs/Склад против Кореи.xlsx
@@ -8,8 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ВСЕ ПОЗИЦИИ" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="В КОРЕЕ ДЕШЕВЛЕ" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="В КОРЕЕ ДОРОЖЕ" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ВЫГОДНО ВЕЗТИ" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="НЕВЫГОДНО ВЕЗТИ" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -506,12 +506,12 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Цена EXW, руб</t>
+          <t>Цена в Корее, руб</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>С доставкой, руб</t>
+          <t>Итого у нас на складе, руб</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -521,12 +521,12 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Разница, руб</t>
+          <t>Разница с доставкой, руб</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Разница, %</t>
+          <t>Разница с доставкой, %</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
@@ -5318,7 +5318,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L110"/>
+  <dimension ref="A1:L90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5368,12 +5368,12 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Цена EXW, руб</t>
+          <t>Цена в Корее, руб</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>С доставкой, руб</t>
+          <t>Итого у нас на складе, руб</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Разница, руб</t>
+          <t>Разница с доставкой, руб</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Разница, %</t>
+          <t>Разница с доставкой, %</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
@@ -5401,7 +5401,7 @@
       <c r="A2" s="2" t="n"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>CELIMAX</t>
         </is>
       </c>
       <c r="C2" s="2" t="n"/>
@@ -5421,42 +5421,42 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>CELIMAX</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT - Pearl Real Ampoule Mask [27ml] / ампульная маска для лица с жемчугом</t>
+          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD [170ml / 60pads]/Тонер-пэды от воспалений</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
-        <v>1190</v>
+        <v>1500</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>23</v>
+        <v>708</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>159</v>
+        <v>8509</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>10</v>
+        <v>528</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>11</v>
+        <v>607</v>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>FINESKIN (ответ)</t>
+          <t>Papa Cosmetic</t>
         </is>
       </c>
       <c r="J3" s="5" t="n">
-        <v>-11</v>
+        <v>-101</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>-50.1</v>
+        <v>-14.3</v>
       </c>
       <c r="L3" s="5" t="n">
-        <v>-13555</v>
+        <v>-151773</v>
       </c>
     </row>
     <row r="4">
@@ -5465,42 +5465,42 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>CELIMAX</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT - Vitamin Real Ampoule Mask [27ml] / Ампульная маска с витаминами</t>
+          <t>Celimax Dual Barrier Creamy Toner, тонер 150 мл</t>
         </is>
       </c>
       <c r="D4" s="5" t="n">
-        <v>1190</v>
+        <v>4520</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>23</v>
+        <v>664</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>159</v>
+        <v>9000</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>10</v>
+        <v>558</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>11</v>
+        <v>642</v>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>FINESKIN (ответ)</t>
+          <t>Papa Cosmetic</t>
         </is>
       </c>
       <c r="J4" s="5" t="n">
-        <v>-11</v>
+        <v>-22</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>-50.1</v>
+        <v>-3.3</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>-13555</v>
+        <v>-100163</v>
       </c>
     </row>
     <row r="5">
@@ -5509,42 +5509,42 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>CELIMAX</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT - Red Ginseng Real Ampoule Mask [27ml] / Ампульная маска с красным женьшенем</t>
+          <t>CELIMAX THE REAL NONI MOISTURE BALANCING TONER (NEW) [150ml]/Восстанавливающий тонер с экстрактом нони</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1190</v>
+        <v>23</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>23</v>
+        <v>720</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>159</v>
+        <v>9875</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>10</v>
+        <v>612</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>11</v>
+        <v>704</v>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>FINESKIN (ответ)</t>
+          <t>PAPA COSMETIC (ответ)</t>
         </is>
       </c>
       <c r="J5" s="5" t="n">
-        <v>-11</v>
+        <v>-15</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-50.1</v>
+        <v>-2.2</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>-13555</v>
+        <v>-356</v>
       </c>
     </row>
     <row r="6">
@@ -5553,116 +5553,90 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>CELIMAX</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT - Potato Real Ampoule Mask [27ml] / Ампульная маска с экстрактом картофеля</t>
+          <t>CELIMAX DUAL BARRIER SKIN WEARABLE CREAM [50ml]/Крем для восстановления защитного барьера кожи лица</t>
         </is>
       </c>
       <c r="D6" s="5" t="n">
-        <v>1190</v>
+        <v>90</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>23</v>
+        <v>864</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>159</v>
+        <v>11900</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>10</v>
+        <v>738</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>11</v>
+        <v>848</v>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>FINESKIN (ответ)</t>
+          <t>PAPA COSMETIC (ответ)</t>
         </is>
       </c>
       <c r="J6" s="5" t="n">
-        <v>-11</v>
+        <v>-16</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-50.1</v>
+        <v>-1.8</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>-13555</v>
+        <v>-1408</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>JIGOTT</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>JIGOTT - Pomegranate Real Ampoule Mask [27ml] / Ампульная маска с экстрактом граната</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>1190</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>159</v>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="H7" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>FINESKIN (ответ)</t>
-        </is>
-      </c>
-      <c r="J7" s="5" t="n">
-        <v>-11</v>
-      </c>
-      <c r="K7" s="4" t="n">
-        <v>-50.1</v>
-      </c>
-      <c r="L7" s="5" t="n">
-        <v>-13555</v>
-      </c>
+      <c r="A7" s="2" t="n"/>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>DEOPROCE</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="3" t="n"/>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+      <c r="I7" s="2" t="n"/>
+      <c r="J7" s="3" t="n"/>
+      <c r="K7" s="2" t="n"/>
+      <c r="L7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>DEOPROCE</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT - Placenta Real Ampoule Mask [27ml] / Ампульная маска с плацентой</t>
+          <t>DEOPROCE SHAMPOO - BLACK GARLIC INTENSME ENERGY [200ml]/ Шампунь с черным чесноком против выпадения волос</t>
         </is>
       </c>
       <c r="D8" s="5" t="n">
-        <v>1190</v>
+        <v>240</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>23</v>
+        <v>151</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>159</v>
+        <v>1781</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>10</v>
+        <v>110</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>11</v>
+        <v>127</v>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
@@ -5670,43 +5644,43 @@
         </is>
       </c>
       <c r="J8" s="5" t="n">
-        <v>-11</v>
+        <v>-24</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-50.1</v>
+        <v>-16</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>-13555</v>
+        <v>-5795</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>DEOPROCE</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT - Hyaluronic Acid Real Ampoule Mask [27ml] / Ампульная маска с гиалуроновой кислотой</t>
+          <t>DEOPROCE RINSE - BLACK GARLIC INTENSME ENERGY [1000ml] / Бальзам от выпадения волос Чёрный чеснок</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1190</v>
+        <v>400</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>23</v>
+        <v>359</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>159</v>
+        <v>4431</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>10</v>
+        <v>275</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>11</v>
+        <v>316</v>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
@@ -5714,43 +5688,43 @@
         </is>
       </c>
       <c r="J9" s="5" t="n">
-        <v>-11</v>
+        <v>-43</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-50.1</v>
+        <v>-12</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>-13555</v>
+        <v>-17200</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>DEOPROCE</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT - Honey Real Ampoule Mask [27ml] / Ампульная маска с экстрактом меда</t>
+          <t>DEOPROCE SHAMPOO - BLACK GARLIC INTENSME ENERGY [1000ml]/ Шампунь с черным чесноком против выпадения волос</t>
         </is>
       </c>
       <c r="D10" s="5" t="n">
-        <v>1190</v>
+        <v>400</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>23</v>
+        <v>368</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>159</v>
+        <v>4547</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>10</v>
+        <v>282</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>11</v>
+        <v>324</v>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
@@ -5758,87 +5732,61 @@
         </is>
       </c>
       <c r="J10" s="5" t="n">
-        <v>-11</v>
+        <v>-44</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-50.1</v>
+        <v>-11.9</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>-13555</v>
+        <v>-17488</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>JIGOTT</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>JIGOTT - Green Tea Real Ampoule Mask [27ml] / Ампульная маска с экстрактом зеленого чая</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="n">
-        <v>1190</v>
-      </c>
-      <c r="E11" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="F11" s="5" t="n">
-        <v>159</v>
-      </c>
-      <c r="G11" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="H11" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>FINESKIN (ответ)</t>
-        </is>
-      </c>
-      <c r="J11" s="5" t="n">
-        <v>-11</v>
-      </c>
-      <c r="K11" s="4" t="n">
-        <v>-50.1</v>
-      </c>
-      <c r="L11" s="5" t="n">
-        <v>-13555</v>
-      </c>
+      <c r="A11" s="2" t="n"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>ELIZAVECCA</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+      <c r="I11" s="2" t="n"/>
+      <c r="J11" s="3" t="n"/>
+      <c r="K11" s="2" t="n"/>
+      <c r="L11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>ELIZAVECCA</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT - Cucumber Real Ampoule Mask [27ml] / Тканевая маска с экстрактом огурца</t>
+          <t>ELIZAVECCA - CER-100 Collagen Ceramide Coating Protein Treatment [100ml] / Коллагеновая маска для волос</t>
         </is>
       </c>
       <c r="D12" s="5" t="n">
-        <v>1190</v>
+        <v>300</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>23</v>
+        <v>242</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>159</v>
+        <v>3276</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>10</v>
+        <v>203</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>11</v>
+        <v>234</v>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
@@ -5846,432 +5794,380 @@
         </is>
       </c>
       <c r="J12" s="5" t="n">
-        <v>-11</v>
+        <v>-9</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-50.1</v>
+        <v>-3.6</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>-13555</v>
+        <v>-2595</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>JIGOTT</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>JIGOTT - Collagen Real Ampoule Mask [27ml] / Ампульная маска с коллагеном</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>1190</v>
-      </c>
-      <c r="E13" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="F13" s="5" t="n">
-        <v>159</v>
-      </c>
-      <c r="G13" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="H13" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>FINESKIN (ответ)</t>
-        </is>
-      </c>
-      <c r="J13" s="5" t="n">
-        <v>-11</v>
-      </c>
-      <c r="K13" s="4" t="n">
-        <v>-50.1</v>
-      </c>
-      <c r="L13" s="5" t="n">
-        <v>-13555</v>
-      </c>
+      <c r="A13" s="2" t="n"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>ENOUGH</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="3" t="n"/>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+      <c r="I13" s="2" t="n"/>
+      <c r="J13" s="3" t="n"/>
+      <c r="K13" s="2" t="n"/>
+      <c r="L13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT - Caviar Real Ampoule Mask [27ml] / Ампульная маска с экстрактом икры</t>
+          <t xml:space="preserve">ENOUGH Collagen whitening cover tip concealer #01 [9g]/Консилер для лица (основная карточка) </t>
         </is>
       </c>
       <c r="D14" s="5" t="n">
-        <v>1190</v>
+        <v>200</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>23</v>
+        <v>183</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>159</v>
+        <v>2250</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>10</v>
+        <v>140</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>11</v>
+        <v>160</v>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>FINESKIN (ответ)</t>
+          <t>Классик</t>
         </is>
       </c>
       <c r="J14" s="5" t="n">
-        <v>-11</v>
+        <v>-23</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-50.1</v>
+        <v>-12.5</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>-13555</v>
+        <v>-4563</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT - Camellia Real Ampoule Mask [27ml] / Ампульная маска с экстрактом камелии</t>
+          <t>ENOUGH Collagen whitening cover tip concealer #02 [9g]/Консилер для лица (основная карточка)</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1190</v>
+        <v>300</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>23</v>
+        <v>183</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>159</v>
+        <v>2250</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>10</v>
+        <v>140</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>11</v>
+        <v>160</v>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>FINESKIN (ответ)</t>
+          <t>Классик</t>
         </is>
       </c>
       <c r="J15" s="5" t="n">
-        <v>-11</v>
+        <v>-23</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-50.1</v>
+        <v>-12.5</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>-13555</v>
+        <v>-6844</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT - Black Snail Real Ampoule Mask [27ml] / Ампульная маска с экстрактом слизи черной улитки</t>
+          <t>ENOUGH Collagen whitening cover tip concealer #03 [9g]/ Консилер для лица (основаная карточка)</t>
         </is>
       </c>
       <c r="D16" s="5" t="n">
-        <v>1190</v>
+        <v>260</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>23</v>
+        <v>183</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>159</v>
+        <v>2250</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>10</v>
+        <v>140</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>11</v>
+        <v>160</v>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>FINESKIN (ответ)</t>
+          <t>Классик</t>
         </is>
       </c>
       <c r="J16" s="5" t="n">
-        <v>-11</v>
+        <v>-23</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-50.1</v>
+        <v>-12.5</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>-13555</v>
+        <v>-5932</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT - Aloe Real Ampoule Mask [27ml] / Ампульная маска с экстрактом алое</t>
+          <t>ENOUGH - Collagen Whitening Moisture Cream 3in1 [50g] / Антивозрастной отбеливающий крем с коллагеном</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1190</v>
+        <v>344</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>23</v>
+        <v>184</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>159</v>
+        <v>2500</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>10</v>
+        <v>155</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>11</v>
+        <v>178</v>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>FINESKIN (ответ)</t>
+          <t>Классик</t>
         </is>
       </c>
       <c r="J17" s="5" t="n">
-        <v>-11</v>
+        <v>-6</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-50.1</v>
+        <v>-3.1</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>-13555</v>
+        <v>-1937</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>JIGOTT</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>JIGOTT - Lotus Real Ampoule Mask [27ml] / Ампульная маска с экстрактом лотоса</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="n">
-        <v>1190</v>
-      </c>
-      <c r="E18" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="F18" s="5" t="n">
-        <v>159</v>
-      </c>
-      <c r="G18" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="H18" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="I18" s="4" t="inlineStr">
-        <is>
-          <t>FINESKIN (ответ)</t>
-        </is>
-      </c>
-      <c r="J18" s="5" t="n">
-        <v>-11</v>
-      </c>
-      <c r="K18" s="4" t="n">
-        <v>-50.1</v>
-      </c>
-      <c r="L18" s="5" t="n">
-        <v>-13555</v>
-      </c>
+      <c r="A18" s="2" t="n"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>ETUDE</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="3" t="n"/>
+      <c r="E18" s="3" t="n"/>
+      <c r="F18" s="3" t="n"/>
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
+      <c r="I18" s="2" t="n"/>
+      <c r="J18" s="3" t="n"/>
+      <c r="K18" s="2" t="n"/>
+      <c r="L18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>ETUDE</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT - Ultimate Real Collagen Toner [300ml] / тонер с коллагеном антивозрастной</t>
+          <t>ETUDE - Baking Powder Crunch Pore Scrub [200ml] / Очищающий скраб для лица с содой</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>800</v>
+        <v>7279</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>265</v>
+        <v>361</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>2120</v>
+        <v>4400</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>131</v>
+        <v>273</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>151</v>
+        <v>314</v>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>FINESKIN (ответ)</t>
+          <t>PAPA COSMETIC (ответ)</t>
         </is>
       </c>
       <c r="J19" s="5" t="n">
-        <v>-114</v>
+        <v>-47</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-43</v>
+        <v>-13.1</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>-91363</v>
+        <v>-344369</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>JIGOTT</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>JIGOTT - Daily Real Cica Toner [300ml] / Тонер для лица с центеллой азиатской</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="n">
-        <v>800</v>
-      </c>
-      <c r="E20" s="5" t="n">
-        <v>265</v>
-      </c>
-      <c r="F20" s="5" t="n">
-        <v>2120</v>
-      </c>
-      <c r="G20" s="5" t="n">
-        <v>131</v>
-      </c>
-      <c r="H20" s="5" t="n">
-        <v>151</v>
-      </c>
-      <c r="I20" s="4" t="inlineStr">
-        <is>
-          <t>FINESKIN (ответ)</t>
-        </is>
-      </c>
-      <c r="J20" s="5" t="n">
-        <v>-114</v>
-      </c>
-      <c r="K20" s="4" t="n">
-        <v>-43</v>
-      </c>
-      <c r="L20" s="5" t="n">
-        <v>-91363</v>
-      </c>
+      <c r="A20" s="2" t="n"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>FARMSTAY</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="3" t="n"/>
+      <c r="E20" s="3" t="n"/>
+      <c r="F20" s="3" t="n"/>
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
+      <c r="I20" s="2" t="n"/>
+      <c r="J20" s="3" t="n"/>
+      <c r="K20" s="2" t="n"/>
+      <c r="L20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>FARMSTAY</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT - Moisture Real Aloe Vera Toner [300ml] / Тонер для лица увлажняющий с экстрактом алоэ</t>
+          <t>FARMSTAY - Collagen Water Full Moist Cream [100g] / Увлажняющий крем с коллагеном</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>265</v>
+        <v>484</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>2120</v>
+        <v>4390</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>131</v>
+        <v>272</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>151</v>
+        <v>313</v>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>FINESKIN (ответ)</t>
+          <t>Классик</t>
         </is>
       </c>
       <c r="J21" s="5" t="n">
-        <v>-114</v>
+        <v>-171</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-43</v>
+        <v>-35.4</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>-11420</v>
+        <v>-34283</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n"/>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="A22" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>FARMSTAY</t>
         </is>
       </c>
-      <c r="C22" s="2" t="n"/>
-      <c r="D22" s="3" t="n"/>
-      <c r="E22" s="3" t="n"/>
-      <c r="F22" s="3" t="n"/>
-      <c r="G22" s="3" t="n"/>
-      <c r="H22" s="3" t="n"/>
-      <c r="I22" s="2" t="n"/>
-      <c r="J22" s="3" t="n"/>
-      <c r="K22" s="2" t="n"/>
-      <c r="L22" s="3" t="n"/>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>FARMSTAY - Black Garlic Nourishing Shampoo [530ml] / Шампунь-кондиционер 2в1 с экстрактом черного чеснока</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>3239</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>397</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>3660</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>227</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>261</v>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>Классик</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="n">
+        <v>-136</v>
+      </c>
+      <c r="K22" s="4" t="n">
+        <v>-34.2</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>-439733</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
@@ -6280,23 +6176,23 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>FARMSTAY - Collagen Water Full Moist Cream [100g] / Увлажняющий крем с коллагеном</t>
+          <t>FARMSTAY - Collagen Water Full Shampoo &amp; Conditioner [530ml] / Шампунь-кондиционер 2в1 с коллагеном</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>200</v>
+        <v>3493</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>484</v>
+        <v>397</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>4390</v>
+        <v>3660</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>272</v>
+        <v>227</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>313</v>
+        <v>261</v>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
@@ -6304,18 +6200,18 @@
         </is>
       </c>
       <c r="J23" s="5" t="n">
-        <v>-171</v>
+        <v>-136</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-35.4</v>
+        <v>-34.2</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>-34283</v>
+        <v>-474217</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
@@ -6324,23 +6220,23 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>FARMSTAY - Collagen Water Full Shampoo &amp; Conditioner [530ml] / Шампунь-кондиционер 2в1 с коллагеном</t>
+          <t>FARMSTAY - Argan Oil Complete Volume Up Shampoo &amp; Conditioner [530ml] / Шампунь-кондиционер с аргановым маслом</t>
         </is>
       </c>
       <c r="D24" s="5" t="n">
-        <v>3493</v>
+        <v>2435</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>3660</v>
+        <v>3730</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
@@ -6348,18 +6244,18 @@
         </is>
       </c>
       <c r="J24" s="5" t="n">
-        <v>-136</v>
+        <v>-135</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-34.2</v>
+        <v>-33.6</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>-474217</v>
+        <v>-328265</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
@@ -6368,23 +6264,23 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>FARMSTAY - Black Garlic Nourishing Shampoo [530ml] / Шампунь-кондиционер 2в1 с экстрактом черного чеснока</t>
+          <t>FARMSTAY ESCARGOT NOBLESSE INTENSIVE AMPOULE/ сыворотка с улиткой</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>3239</v>
+        <v>901</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>3660</v>
+        <v>4660</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>227</v>
+        <v>289</v>
       </c>
       <c r="H25" s="5" t="n">
-        <v>261</v>
+        <v>332</v>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
@@ -6392,18 +6288,18 @@
         </is>
       </c>
       <c r="J25" s="5" t="n">
-        <v>-136</v>
+        <v>-58</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-34.2</v>
+        <v>-14.9</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>-439733</v>
+        <v>-52440</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
@@ -6412,23 +6308,23 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>FARMSTAY - Argan Oil Complete Volume Up Shampoo &amp; Conditioner [530ml] / Шампунь-кондиционер с аргановым маслом</t>
+          <t>FARMSTAY - Collagen Pure Cleansing Foam [180ml]/Пенка для умывания</t>
         </is>
       </c>
       <c r="D26" s="5" t="n">
-        <v>2435</v>
+        <v>300</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>401</v>
+        <v>161</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>3730</v>
+        <v>1930</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>231</v>
+        <v>120</v>
       </c>
       <c r="H26" s="5" t="n">
-        <v>266</v>
+        <v>138</v>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
@@ -6436,342 +6332,446 @@
         </is>
       </c>
       <c r="J26" s="5" t="n">
-        <v>-135</v>
+        <v>-24</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-33.6</v>
+        <v>-14.8</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>-328265</v>
+        <v>-7158</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n"/>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>MANYO</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="n"/>
-      <c r="D27" s="3" t="n"/>
-      <c r="E27" s="3" t="n"/>
-      <c r="F27" s="3" t="n"/>
-      <c r="G27" s="3" t="n"/>
-      <c r="H27" s="3" t="n"/>
-      <c r="I27" s="2" t="n"/>
-      <c r="J27" s="3" t="n"/>
-      <c r="K27" s="2" t="n"/>
-      <c r="L27" s="3" t="n"/>
+      <c r="A27" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>FARMSTAY</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>FARMSTAY - Collagen Water Full Moist Rolling Eye Serum [25ml] / Сыворотка роллер для глаз</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>156</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>232</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>2770</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>172</v>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>198</v>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>Классик</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="n">
+        <v>-34</v>
+      </c>
+      <c r="K27" s="4" t="n">
+        <v>-14.8</v>
+      </c>
+      <c r="L27" s="5" t="n">
+        <v>-5340</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>FARMSTAY</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>FARMSTAY - Escargot Noblesse Intensive Cream [50g] / Крем с муцином королевской улитки</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>860</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>314</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>4010</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>249</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>286</v>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>Классик</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="n">
+        <v>-28</v>
+      </c>
+      <c r="K28" s="4" t="n">
+        <v>-8.9</v>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>-24017</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>FARMSTAY</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>FARMSTAY - Collagen &amp; Hyaluronic Acid All-In One Ampoule [250ml] / Сыворотка с коллагеном и гиалуроновой кислотой</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>6179</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>348</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>4660</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>289</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>332</v>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>Классик</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="n">
+        <v>-16</v>
+      </c>
+      <c r="K29" s="4" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="L29" s="5" t="n">
+        <v>-95787</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>HEIMISH</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="3" t="n"/>
+      <c r="E30" s="3" t="n"/>
+      <c r="F30" s="3" t="n"/>
+      <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
+      <c r="I30" s="2" t="n"/>
+      <c r="J30" s="3" t="n"/>
+      <c r="K30" s="2" t="n"/>
+      <c r="L30" s="3" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>HEIMISH</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>HEIMISH - Artless Glow Base SPF50+ PA+++(Renew) [40ml] / База под макияж SPF50+ PA+++</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>941</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>770</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>8565</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>531</v>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>611</v>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>Классик</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="n">
+        <v>-160</v>
+      </c>
+      <c r="K31" s="4" t="n">
+        <v>-20.7</v>
+      </c>
+      <c r="L31" s="5" t="n">
+        <v>-150368</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>JIGOTT</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="n"/>
+      <c r="D32" s="3" t="n"/>
+      <c r="E32" s="3" t="n"/>
+      <c r="F32" s="3" t="n"/>
+      <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
+      <c r="I32" s="2" t="n"/>
+      <c r="J32" s="3" t="n"/>
+      <c r="K32" s="2" t="n"/>
+      <c r="L32" s="3" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>MANYO</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>MANYO - Bifida Biome Complex Ampoule [50ml] / Антивозрастная сыворотка для лица</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="n">
-        <v>1355</v>
-      </c>
-      <c r="E28" s="5" t="n">
-        <v>900</v>
-      </c>
-      <c r="F28" s="5" t="n">
-        <v>8740</v>
-      </c>
-      <c r="G28" s="5" t="n">
-        <v>542</v>
-      </c>
-      <c r="H28" s="5" t="n">
-        <v>623</v>
-      </c>
-      <c r="I28" s="4" t="inlineStr">
-        <is>
-          <t>PAPA COSMETIC (ответ)</t>
-        </is>
-      </c>
-      <c r="J28" s="5" t="n">
-        <v>-277</v>
-      </c>
-      <c r="K28" s="4" t="n">
-        <v>-30.7</v>
-      </c>
-      <c r="L28" s="5" t="n">
-        <v>-374817</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="n"/>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>SOME BY MI</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="n"/>
-      <c r="D29" s="3" t="n"/>
-      <c r="E29" s="3" t="n"/>
-      <c r="F29" s="3" t="n"/>
-      <c r="G29" s="3" t="n"/>
-      <c r="H29" s="3" t="n"/>
-      <c r="I29" s="2" t="n"/>
-      <c r="J29" s="3" t="n"/>
-      <c r="K29" s="2" t="n"/>
-      <c r="L29" s="3" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>SOME BY MI</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>SOME BY MI - AHA-BHA-PHA 30 Days Miracle Cream [60g] / Крем для лица</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="n">
-        <v>55</v>
-      </c>
-      <c r="E30" s="5" t="n">
-        <v>1057</v>
-      </c>
-      <c r="F30" s="5" t="n">
-        <v>10685</v>
-      </c>
-      <c r="G30" s="5" t="n">
-        <v>662</v>
-      </c>
-      <c r="H30" s="5" t="n">
-        <v>762</v>
-      </c>
-      <c r="I30" s="4" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>JIGOTT</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>JIGOTT - Aloe Real Ampoule Mask [27ml] / Ампульная маска с экстрактом алое</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>1190</v>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>159</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
         <is>
           <t>FINESKIN (ответ)</t>
         </is>
       </c>
-      <c r="J30" s="5" t="n">
-        <v>-295</v>
-      </c>
-      <c r="K30" s="4" t="n">
-        <v>-27.9</v>
-      </c>
-      <c r="L30" s="5" t="n">
-        <v>-16245</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="n"/>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>ROUND LAB</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="n"/>
-      <c r="D31" s="3" t="n"/>
-      <c r="E31" s="3" t="n"/>
-      <c r="F31" s="3" t="n"/>
-      <c r="G31" s="3" t="n"/>
-      <c r="H31" s="3" t="n"/>
-      <c r="I31" s="2" t="n"/>
-      <c r="J31" s="3" t="n"/>
-      <c r="K31" s="2" t="n"/>
-      <c r="L31" s="3" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>ROUND LAB</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>ROUND LAB PINE CALMING CICA AMPOULE_30ml - Сыворотка для жирной кожи лица увлажняющая с центеллой</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="n">
-        <v>32</v>
-      </c>
-      <c r="E32" s="5" t="n">
-        <v>820</v>
-      </c>
-      <c r="F32" s="5" t="n">
-        <v>8293</v>
-      </c>
-      <c r="G32" s="5" t="n">
-        <v>514</v>
-      </c>
-      <c r="H32" s="5" t="n">
-        <v>591</v>
-      </c>
-      <c r="I32" s="4" t="inlineStr">
-        <is>
-          <t>G&amp;E Global</t>
-        </is>
-      </c>
-      <c r="J32" s="5" t="n">
-        <v>-228</v>
-      </c>
-      <c r="K32" s="4" t="n">
-        <v>-27.9</v>
-      </c>
-      <c r="L32" s="5" t="n">
-        <v>-7310</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="n"/>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>PETITFEE</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="n"/>
-      <c r="D33" s="3" t="n"/>
-      <c r="E33" s="3" t="n"/>
-      <c r="F33" s="3" t="n"/>
-      <c r="G33" s="3" t="n"/>
-      <c r="H33" s="3" t="n"/>
-      <c r="I33" s="2" t="n"/>
-      <c r="J33" s="3" t="n"/>
-      <c r="K33" s="2" t="n"/>
-      <c r="L33" s="3" t="n"/>
+      <c r="J33" s="5" t="n">
+        <v>-11</v>
+      </c>
+      <c r="K33" s="4" t="n">
+        <v>-50.1</v>
+      </c>
+      <c r="L33" s="5" t="n">
+        <v>-13555</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>PETITFEE - Aura Quartz Hydrogel Eye Patch [60ea]</t>
+          <t>JIGOTT - Black Snail Real Ampoule Mask [27ml] / Ампульная маска с экстрактом слизи черной улитки</t>
         </is>
       </c>
       <c r="D34" s="5" t="n">
-        <v>89</v>
+        <v>1190</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>591</v>
+        <v>23</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>6190</v>
+        <v>159</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>384</v>
+        <v>10</v>
       </c>
       <c r="H34" s="5" t="n">
-        <v>441</v>
+        <v>11</v>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>J2K (ответ)</t>
+          <t>FINESKIN (ответ)</t>
         </is>
       </c>
       <c r="J34" s="5" t="n">
-        <v>-150</v>
+        <v>-11</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-25.4</v>
+        <v>-50.1</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>-13345</v>
+        <v>-13555</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n"/>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="A35" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>JIGOTT</t>
         </is>
       </c>
-      <c r="C35" s="2" t="n"/>
-      <c r="D35" s="3" t="n"/>
-      <c r="E35" s="3" t="n"/>
-      <c r="F35" s="3" t="n"/>
-      <c r="G35" s="3" t="n"/>
-      <c r="H35" s="3" t="n"/>
-      <c r="I35" s="2" t="n"/>
-      <c r="J35" s="3" t="n"/>
-      <c r="K35" s="2" t="n"/>
-      <c r="L35" s="3" t="n"/>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>JIGOTT - Camellia Real Ampoule Mask [27ml] / Ампульная маска с экстрактом камелии</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>1190</v>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>159</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>FINESKIN (ответ)</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="n">
+        <v>-11</v>
+      </c>
+      <c r="K35" s="4" t="n">
+        <v>-50.1</v>
+      </c>
+      <c r="L35" s="5" t="n">
+        <v>-13555</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>JIGOTT</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>JIGOTT - Caviar Real Ampoule Mask [27ml] / Ампульная маска с экстрактом икры</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>1190</v>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>159</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>FINESKIN (ответ)</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="n">
+        <v>-11</v>
+      </c>
+      <c r="K36" s="4" t="n">
+        <v>-50.1</v>
+      </c>
+      <c r="L36" s="5" t="n">
+        <v>-13555</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>JIGOTT</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>JIGOTT - Snail Lifting Cream [70ml] / Крем для лица увлажняющий антивозрастной</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="n">
-        <v>7463</v>
-      </c>
-      <c r="E36" s="5" t="n">
-        <v>202</v>
-      </c>
-      <c r="F36" s="5" t="n">
-        <v>2120</v>
-      </c>
-      <c r="G36" s="5" t="n">
-        <v>131</v>
-      </c>
-      <c r="H36" s="5" t="n">
-        <v>151</v>
-      </c>
-      <c r="I36" s="4" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>JIGOTT - Collagen Real Ampoule Mask [27ml] / Ампульная маска с коллагеном</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>1190</v>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>159</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="H37" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
         <is>
           <t>FINESKIN (ответ)</t>
         </is>
       </c>
-      <c r="J36" s="5" t="n">
-        <v>-51</v>
-      </c>
-      <c r="K36" s="4" t="n">
-        <v>-25.3</v>
-      </c>
-      <c r="L36" s="5" t="n">
-        <v>-381464</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="n"/>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>JMSOLUTION</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="n"/>
-      <c r="D37" s="3" t="n"/>
-      <c r="E37" s="3" t="n"/>
-      <c r="F37" s="3" t="n"/>
-      <c r="G37" s="3" t="n"/>
-      <c r="H37" s="3" t="n"/>
-      <c r="I37" s="2" t="n"/>
-      <c r="J37" s="3" t="n"/>
-      <c r="K37" s="2" t="n"/>
-      <c r="L37" s="3" t="n"/>
+      <c r="J37" s="5" t="n">
+        <v>-11</v>
+      </c>
+      <c r="K37" s="4" t="n">
+        <v>-50.1</v>
+      </c>
+      <c r="L37" s="5" t="n">
+        <v>-13555</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
@@ -6779,28 +6779,28 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>JMSOLUTION</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>JMSOLUTION GREEN DEAR TIGER CICA MASK PURE 30ml*10ea / Регенерирующая маска для лица с центеллой</t>
+          <t>JIGOTT - Cucumber Real Ampoule Mask [27ml] / Тканевая маска с экстрактом огурца</t>
         </is>
       </c>
       <c r="D38" s="5" t="n">
-        <v>110</v>
+        <v>1190</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>342</v>
+        <v>23</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>3604</v>
+        <v>159</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>223</v>
+        <v>10</v>
       </c>
       <c r="H38" s="5" t="n">
-        <v>257</v>
+        <v>11</v>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
@@ -6808,13 +6808,13 @@
         </is>
       </c>
       <c r="J38" s="5" t="n">
-        <v>-85</v>
+        <v>-11</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>-24.9</v>
+        <v>-50.1</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>-9384</v>
+        <v>-13555</v>
       </c>
     </row>
     <row r="39">
@@ -6823,28 +6823,28 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>JMSOLUTION</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>JMSOLUTION ACTIVE BLACK CAVIAR MASK [30ml*10ea] / Ультратонкая тканевая маска с черной икрой</t>
+          <t>JIGOTT - Green Tea Real Ampoule Mask [27ml] / Ампульная маска с экстрактом зеленого чая</t>
         </is>
       </c>
       <c r="D39" s="5" t="n">
-        <v>110</v>
+        <v>1190</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>342</v>
+        <v>23</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>3604</v>
+        <v>159</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>223</v>
+        <v>10</v>
       </c>
       <c r="H39" s="5" t="n">
-        <v>257</v>
+        <v>11</v>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
@@ -6852,13 +6852,13 @@
         </is>
       </c>
       <c r="J39" s="5" t="n">
-        <v>-85</v>
+        <v>-11</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>-24.9</v>
+        <v>-50.1</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>-9384</v>
+        <v>-13555</v>
       </c>
     </row>
     <row r="40">
@@ -6867,28 +6867,28 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>JMSOLUTION</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>JMSOLUTION - Active Jellyfish Vital Mask [30ml*10ea] / Ультратонкая тканевая маска с экстрактом медузы</t>
+          <t>JIGOTT - Honey Real Ampoule Mask [27ml] / Ампульная маска с экстрактом меда</t>
         </is>
       </c>
       <c r="D40" s="5" t="n">
-        <v>110</v>
+        <v>1190</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>342</v>
+        <v>23</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>3604</v>
+        <v>159</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>223</v>
+        <v>10</v>
       </c>
       <c r="H40" s="5" t="n">
-        <v>257</v>
+        <v>11</v>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
@@ -6896,13 +6896,13 @@
         </is>
       </c>
       <c r="J40" s="5" t="n">
-        <v>-85</v>
+        <v>-11</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>-24.9</v>
+        <v>-50.1</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>-9384</v>
+        <v>-13555</v>
       </c>
     </row>
     <row r="41">
@@ -6911,28 +6911,28 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>JMSOLUTION</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>JMSOLUTION - Active Golden Caviar Nourishing Mask [30ml*10ea] / Ультратонкая тканевая маска с золотом и икрой</t>
+          <t>JIGOTT - Hyaluronic Acid Real Ampoule Mask [27ml] / Ампульная маска с гиалуроновой кислотой</t>
         </is>
       </c>
       <c r="D41" s="5" t="n">
-        <v>110</v>
+        <v>1190</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>342</v>
+        <v>23</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>3604</v>
+        <v>159</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>223</v>
+        <v>10</v>
       </c>
       <c r="H41" s="5" t="n">
-        <v>257</v>
+        <v>11</v>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
@@ -6940,13 +6940,13 @@
         </is>
       </c>
       <c r="J41" s="5" t="n">
-        <v>-85</v>
+        <v>-11</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>-24.9</v>
+        <v>-50.1</v>
       </c>
       <c r="L41" s="5" t="n">
-        <v>-9384</v>
+        <v>-13555</v>
       </c>
     </row>
     <row r="42">
@@ -6955,28 +6955,28 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>JMSOLUTION</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>JMSOLUTION - Active Birds Nest Moisture Mask [30ml*10ea] / Ультратонкая тканевая маска с ласточкиным гнездом</t>
+          <t>JIGOTT - Lotus Real Ampoule Mask [27ml] / Ампульная маска с экстрактом лотоса</t>
         </is>
       </c>
       <c r="D42" s="5" t="n">
-        <v>110</v>
+        <v>1190</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>342</v>
+        <v>23</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>3604</v>
+        <v>159</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>223</v>
+        <v>10</v>
       </c>
       <c r="H42" s="5" t="n">
-        <v>257</v>
+        <v>11</v>
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
@@ -6984,222 +6984,326 @@
         </is>
       </c>
       <c r="J42" s="5" t="n">
-        <v>-85</v>
+        <v>-11</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>-24.9</v>
+        <v>-50.1</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>-9384</v>
+        <v>-13555</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n"/>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>ROUND LAB</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="n"/>
-      <c r="D43" s="3" t="n"/>
-      <c r="E43" s="3" t="n"/>
-      <c r="F43" s="3" t="n"/>
-      <c r="G43" s="3" t="n"/>
-      <c r="H43" s="3" t="n"/>
-      <c r="I43" s="2" t="n"/>
-      <c r="J43" s="3" t="n"/>
-      <c r="K43" s="2" t="n"/>
-      <c r="L43" s="3" t="n"/>
+      <c r="A43" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>JIGOTT</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>JIGOTT - Pearl Real Ampoule Mask [27ml] / ампульная маска для лица с жемчугом</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>1190</v>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>159</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="H43" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t>FINESKIN (ответ)</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="n">
+        <v>-11</v>
+      </c>
+      <c r="K43" s="4" t="n">
+        <v>-50.1</v>
+      </c>
+      <c r="L43" s="5" t="n">
+        <v>-13555</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>ROUND LAB</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>ROUND LAB BIRCH JUICE MOISTURIZING CREAM_80ml -Увлажняющий крем с березовым соком</t>
+          <t>JIGOTT - Placenta Real Ampoule Mask [27ml] / Ампульная маска с плацентой</t>
         </is>
       </c>
       <c r="D44" s="5" t="n">
-        <v>259</v>
+        <v>1190</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>1093</v>
+        <v>23</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>11702</v>
+        <v>159</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>726</v>
+        <v>10</v>
       </c>
       <c r="H44" s="5" t="n">
-        <v>834</v>
+        <v>11</v>
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>G&amp;E Global</t>
+          <t>FINESKIN (ответ)</t>
         </is>
       </c>
       <c r="J44" s="5" t="n">
-        <v>-259</v>
+        <v>-11</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>-23.7</v>
+        <v>-50.1</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>-66979</v>
+        <v>-13555</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n"/>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>HEIMISH</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="n"/>
-      <c r="D45" s="3" t="n"/>
-      <c r="E45" s="3" t="n"/>
-      <c r="F45" s="3" t="n"/>
-      <c r="G45" s="3" t="n"/>
-      <c r="H45" s="3" t="n"/>
-      <c r="I45" s="2" t="n"/>
-      <c r="J45" s="3" t="n"/>
-      <c r="K45" s="2" t="n"/>
-      <c r="L45" s="3" t="n"/>
+      <c r="A45" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>JIGOTT</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>JIGOTT - Pomegranate Real Ampoule Mask [27ml] / Ампульная маска с экстрактом граната</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="n">
+        <v>1190</v>
+      </c>
+      <c r="E45" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="F45" s="5" t="n">
+        <v>159</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="H45" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="I45" s="4" t="inlineStr">
+        <is>
+          <t>FINESKIN (ответ)</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="n">
+        <v>-11</v>
+      </c>
+      <c r="K45" s="4" t="n">
+        <v>-50.1</v>
+      </c>
+      <c r="L45" s="5" t="n">
+        <v>-13555</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>HEIMISH</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>HEIMISH - Artless Glow Base SPF50+ PA+++(Renew) [40ml] / База под макияж SPF50+ PA+++</t>
+          <t>JIGOTT - Potato Real Ampoule Mask [27ml] / Ампульная маска с экстрактом картофеля</t>
         </is>
       </c>
       <c r="D46" s="5" t="n">
-        <v>941</v>
+        <v>1190</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>770</v>
+        <v>23</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>8565</v>
+        <v>159</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>531</v>
+        <v>10</v>
       </c>
       <c r="H46" s="5" t="n">
-        <v>611</v>
+        <v>11</v>
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>Классик</t>
+          <t>FINESKIN (ответ)</t>
         </is>
       </c>
       <c r="J46" s="5" t="n">
-        <v>-160</v>
+        <v>-11</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>-20.7</v>
+        <v>-50.1</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>-150368</v>
+        <v>-13555</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n"/>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>MANYO</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="n"/>
-      <c r="D47" s="3" t="n"/>
-      <c r="E47" s="3" t="n"/>
-      <c r="F47" s="3" t="n"/>
-      <c r="G47" s="3" t="n"/>
-      <c r="H47" s="3" t="n"/>
-      <c r="I47" s="2" t="n"/>
-      <c r="J47" s="3" t="n"/>
-      <c r="K47" s="2" t="n"/>
-      <c r="L47" s="3" t="n"/>
+      <c r="A47" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>JIGOTT</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>JIGOTT - Red Ginseng Real Ampoule Mask [27ml] / Ампульная маска с красным женьшенем</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="n">
+        <v>1190</v>
+      </c>
+      <c r="E47" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="F47" s="5" t="n">
+        <v>159</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="H47" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="I47" s="4" t="inlineStr">
+        <is>
+          <t>FINESKIN (ответ)</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="n">
+        <v>-11</v>
+      </c>
+      <c r="K47" s="4" t="n">
+        <v>-50.1</v>
+      </c>
+      <c r="L47" s="5" t="n">
+        <v>-13555</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>MANYO</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>MANYO - Pure Cleansing Oil [200ml] / Гидрофильное масло для глубокого очищения</t>
+          <t>JIGOTT - Vitamin Real Ampoule Mask [27ml] / Ампульная маска с витаминами</t>
         </is>
       </c>
       <c r="D48" s="5" t="n">
-        <v>80</v>
+        <v>1190</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>853</v>
+        <v>23</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>9500</v>
+        <v>159</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>589</v>
+        <v>10</v>
       </c>
       <c r="H48" s="5" t="n">
-        <v>677</v>
+        <v>11</v>
       </c>
       <c r="I48" s="4" t="inlineStr">
         <is>
-          <t>PAPA COSMETIC (ответ)</t>
+          <t>FINESKIN (ответ)</t>
         </is>
       </c>
       <c r="J48" s="5" t="n">
-        <v>-176</v>
+        <v>-11</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>-20.6</v>
+        <v>-50.1</v>
       </c>
       <c r="L48" s="5" t="n">
-        <v>-14052</v>
+        <v>-13555</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n"/>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="A49" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>JIGOTT</t>
         </is>
       </c>
-      <c r="C49" s="2" t="n"/>
-      <c r="D49" s="3" t="n"/>
-      <c r="E49" s="3" t="n"/>
-      <c r="F49" s="3" t="n"/>
-      <c r="G49" s="3" t="n"/>
-      <c r="H49" s="3" t="n"/>
-      <c r="I49" s="2" t="n"/>
-      <c r="J49" s="3" t="n"/>
-      <c r="K49" s="2" t="n"/>
-      <c r="L49" s="3" t="n"/>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>JIGOTT - Daily Real Cica Toner [300ml] / Тонер для лица с центеллой азиатской</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="n">
+        <v>800</v>
+      </c>
+      <c r="E49" s="5" t="n">
+        <v>265</v>
+      </c>
+      <c r="F49" s="5" t="n">
+        <v>2120</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>131</v>
+      </c>
+      <c r="H49" s="5" t="n">
+        <v>151</v>
+      </c>
+      <c r="I49" s="4" t="inlineStr">
+        <is>
+          <t>FINESKIN (ответ)</t>
+        </is>
+      </c>
+      <c r="J49" s="5" t="n">
+        <v>-114</v>
+      </c>
+      <c r="K49" s="4" t="n">
+        <v>-43</v>
+      </c>
+      <c r="L49" s="5" t="n">
+        <v>-91363</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
@@ -7208,14 +7312,14 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT - Snail Reparing Cream [100ml] / Крем для лица увлажняющий антивозрастной с муцином улитки</t>
+          <t>JIGOTT - Moisture Real Aloe Vera Toner [300ml] / Тонер для лица увлажняющий с экстрактом алоэ</t>
         </is>
       </c>
       <c r="D50" s="5" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>186</v>
+        <v>265</v>
       </c>
       <c r="F50" s="5" t="n">
         <v>2120</v>
@@ -7232,61 +7336,87 @@
         </is>
       </c>
       <c r="J50" s="5" t="n">
-        <v>-35</v>
+        <v>-114</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>-18.7</v>
+        <v>-43</v>
       </c>
       <c r="L50" s="5" t="n">
-        <v>-17352</v>
+        <v>-11420</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n"/>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>PETITFEE</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="n"/>
-      <c r="D51" s="3" t="n"/>
-      <c r="E51" s="3" t="n"/>
-      <c r="F51" s="3" t="n"/>
-      <c r="G51" s="3" t="n"/>
-      <c r="H51" s="3" t="n"/>
-      <c r="I51" s="2" t="n"/>
-      <c r="J51" s="3" t="n"/>
-      <c r="K51" s="2" t="n"/>
-      <c r="L51" s="3" t="n"/>
+      <c r="A51" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>JIGOTT</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>JIGOTT - Ultimate Real Collagen Toner [300ml] / тонер с коллагеном антивозрастной</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="n">
+        <v>800</v>
+      </c>
+      <c r="E51" s="5" t="n">
+        <v>265</v>
+      </c>
+      <c r="F51" s="5" t="n">
+        <v>2120</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>131</v>
+      </c>
+      <c r="H51" s="5" t="n">
+        <v>151</v>
+      </c>
+      <c r="I51" s="4" t="inlineStr">
+        <is>
+          <t>FINESKIN (ответ)</t>
+        </is>
+      </c>
+      <c r="J51" s="5" t="n">
+        <v>-114</v>
+      </c>
+      <c r="K51" s="4" t="n">
+        <v>-43</v>
+      </c>
+      <c r="L51" s="5" t="n">
+        <v>-91363</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>PETITFEE - Gold Hydrogel Eye Patch [1 Pairs] / гидрогелевые патчи для глаз с золотом 1 пара</t>
+          <t>JIGOTT - Snail Lifting Cream [70ml] / Крем для лица увлажняющий антивозрастной</t>
         </is>
       </c>
       <c r="D52" s="5" t="n">
-        <v>428</v>
+        <v>7463</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>71</v>
+        <v>202</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>819</v>
+        <v>2120</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>51</v>
+        <v>131</v>
       </c>
       <c r="H52" s="5" t="n">
-        <v>58</v>
+        <v>151</v>
       </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
@@ -7294,43 +7424,43 @@
         </is>
       </c>
       <c r="J52" s="5" t="n">
-        <v>-13</v>
+        <v>-51</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>-18</v>
+        <v>-25.3</v>
       </c>
       <c r="L52" s="5" t="n">
-        <v>-5498</v>
+        <v>-381464</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Eye Patch [1 pairs]/ Гидрогелевые патчи для глаз с черным жемчугом и золотом 1 пара</t>
+          <t>JIGOTT - Snail Reparing Cream [100ml] / Крем для лица увлажняющий антивозрастной с муцином улитки</t>
         </is>
       </c>
       <c r="D53" s="5" t="n">
-        <v>320</v>
+        <v>500</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>71</v>
+        <v>186</v>
       </c>
       <c r="F53" s="5" t="n">
-        <v>819</v>
+        <v>2120</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>51</v>
+        <v>131</v>
       </c>
       <c r="H53" s="5" t="n">
-        <v>58</v>
+        <v>151</v>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
@@ -7338,20 +7468,20 @@
         </is>
       </c>
       <c r="J53" s="5" t="n">
-        <v>-13</v>
+        <v>-35</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>-18</v>
+        <v>-18.7</v>
       </c>
       <c r="L53" s="5" t="n">
-        <v>-4110</v>
+        <v>-17352</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n"/>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>ROUND LAB</t>
+          <t>JMSOLUTION</t>
         </is>
       </c>
       <c r="C54" s="2" t="n"/>
@@ -7367,131 +7497,183 @@
     </row>
     <row r="55">
       <c r="A55" s="4" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>ROUND LAB</t>
+          <t>JMSOLUTION</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>ROUND LAB MUGWORT CALMING CLEANSER_150ml - Очищающая пенка для умывания лица от прыщей и акне</t>
+          <t>JMSOLUTION - Active Birds Nest Moisture Mask [30ml*10ea] / Ультратонкая тканевая маска с ласточкиным гнездом</t>
         </is>
       </c>
       <c r="D55" s="5" t="n">
-        <v>1422</v>
+        <v>110</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>512</v>
+        <v>342</v>
       </c>
       <c r="F55" s="5" t="n">
-        <v>5963</v>
+        <v>3604</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>370</v>
+        <v>223</v>
       </c>
       <c r="H55" s="5" t="n">
-        <v>425</v>
+        <v>257</v>
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>G&amp;E Global</t>
+          <t>FINESKIN (ответ)</t>
         </is>
       </c>
       <c r="J55" s="5" t="n">
-        <v>-87</v>
+        <v>-85</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>-17</v>
+        <v>-24.9</v>
       </c>
       <c r="L55" s="5" t="n">
-        <v>-123939</v>
+        <v>-9384</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n"/>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>DEOPROCE</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="n"/>
-      <c r="D56" s="3" t="n"/>
-      <c r="E56" s="3" t="n"/>
-      <c r="F56" s="3" t="n"/>
-      <c r="G56" s="3" t="n"/>
-      <c r="H56" s="3" t="n"/>
-      <c r="I56" s="2" t="n"/>
-      <c r="J56" s="3" t="n"/>
-      <c r="K56" s="2" t="n"/>
-      <c r="L56" s="3" t="n"/>
+      <c r="A56" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>JMSOLUTION</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>JMSOLUTION - Active Golden Caviar Nourishing Mask [30ml*10ea] / Ультратонкая тканевая маска с золотом и икрой</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="n">
+        <v>110</v>
+      </c>
+      <c r="E56" s="5" t="n">
+        <v>342</v>
+      </c>
+      <c r="F56" s="5" t="n">
+        <v>3604</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>223</v>
+      </c>
+      <c r="H56" s="5" t="n">
+        <v>257</v>
+      </c>
+      <c r="I56" s="4" t="inlineStr">
+        <is>
+          <t>FINESKIN (ответ)</t>
+        </is>
+      </c>
+      <c r="J56" s="5" t="n">
+        <v>-85</v>
+      </c>
+      <c r="K56" s="4" t="n">
+        <v>-24.9</v>
+      </c>
+      <c r="L56" s="5" t="n">
+        <v>-9384</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>DEOPROCE</t>
+          <t>JMSOLUTION</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>DEOPROCE SHAMPOO - BLACK GARLIC INTENSME ENERGY [200ml]/ Шампунь с черным чесноком против выпадения волос</t>
+          <t>JMSOLUTION - Active Jellyfish Vital Mask [30ml*10ea] / Ультратонкая тканевая маска с экстрактом медузы</t>
         </is>
       </c>
       <c r="D57" s="5" t="n">
-        <v>240</v>
+        <v>110</v>
       </c>
       <c r="E57" s="5" t="n">
-        <v>151</v>
+        <v>342</v>
       </c>
       <c r="F57" s="5" t="n">
-        <v>1781</v>
+        <v>3604</v>
       </c>
       <c r="G57" s="5" t="n">
+        <v>223</v>
+      </c>
+      <c r="H57" s="5" t="n">
+        <v>257</v>
+      </c>
+      <c r="I57" s="4" t="inlineStr">
+        <is>
+          <t>FINESKIN (ответ)</t>
+        </is>
+      </c>
+      <c r="J57" s="5" t="n">
+        <v>-85</v>
+      </c>
+      <c r="K57" s="4" t="n">
+        <v>-24.9</v>
+      </c>
+      <c r="L57" s="5" t="n">
+        <v>-9384</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>JMSOLUTION</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>JMSOLUTION ACTIVE BLACK CAVIAR MASK [30ml*10ea] / Ультратонкая тканевая маска с черной икрой</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="n">
         <v>110</v>
       </c>
-      <c r="H57" s="5" t="n">
-        <v>127</v>
-      </c>
-      <c r="I57" s="4" t="inlineStr">
+      <c r="E58" s="5" t="n">
+        <v>342</v>
+      </c>
+      <c r="F58" s="5" t="n">
+        <v>3604</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>223</v>
+      </c>
+      <c r="H58" s="5" t="n">
+        <v>257</v>
+      </c>
+      <c r="I58" s="4" t="inlineStr">
         <is>
           <t>FINESKIN (ответ)</t>
         </is>
       </c>
-      <c r="J57" s="5" t="n">
-        <v>-24</v>
-      </c>
-      <c r="K57" s="4" t="n">
-        <v>-16</v>
-      </c>
-      <c r="L57" s="5" t="n">
-        <v>-5795</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="n"/>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>JMSOLUTION</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="n"/>
-      <c r="D58" s="3" t="n"/>
-      <c r="E58" s="3" t="n"/>
-      <c r="F58" s="3" t="n"/>
-      <c r="G58" s="3" t="n"/>
-      <c r="H58" s="3" t="n"/>
-      <c r="I58" s="2" t="n"/>
-      <c r="J58" s="3" t="n"/>
-      <c r="K58" s="2" t="n"/>
-      <c r="L58" s="3" t="n"/>
+      <c r="J58" s="5" t="n">
+        <v>-85</v>
+      </c>
+      <c r="K58" s="4" t="n">
+        <v>-24.9</v>
+      </c>
+      <c r="L58" s="5" t="n">
+        <v>-9384</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
@@ -7500,23 +7682,23 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>JMSOLUTION PANTHELENE INTENSIVE BARRIER MASK</t>
+          <t>JMSOLUTION GREEN DEAR TIGER CICA MASK PURE 30ml*10ea / Регенерирующая маска для лица с центеллой</t>
         </is>
       </c>
       <c r="D59" s="5" t="n">
         <v>110</v>
       </c>
       <c r="E59" s="5" t="n">
-        <v>450</v>
+        <v>342</v>
       </c>
       <c r="F59" s="5" t="n">
-        <v>5311</v>
+        <v>3604</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>329</v>
+        <v>223</v>
       </c>
       <c r="H59" s="5" t="n">
-        <v>379</v>
+        <v>257</v>
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
@@ -7524,18 +7706,18 @@
         </is>
       </c>
       <c r="J59" s="5" t="n">
-        <v>-72</v>
+        <v>-85</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>-15.9</v>
+        <v>-24.9</v>
       </c>
       <c r="L59" s="5" t="n">
-        <v>-7884</v>
+        <v>-9384</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
@@ -7579,7 +7761,7 @@
     </row>
     <row r="61">
       <c r="A61" s="4" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
@@ -7622,284 +7804,310 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n"/>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="A62" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>JMSOLUTION</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>JMSOLUTION PANTHELENE INTENSIVE BARRIER MASK</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="n">
+        <v>110</v>
+      </c>
+      <c r="E62" s="5" t="n">
+        <v>450</v>
+      </c>
+      <c r="F62" s="5" t="n">
+        <v>5311</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>329</v>
+      </c>
+      <c r="H62" s="5" t="n">
+        <v>379</v>
+      </c>
+      <c r="I62" s="4" t="inlineStr">
+        <is>
+          <t>FINESKIN (ответ)</t>
+        </is>
+      </c>
+      <c r="J62" s="5" t="n">
+        <v>-72</v>
+      </c>
+      <c r="K62" s="4" t="n">
+        <v>-15.9</v>
+      </c>
+      <c r="L62" s="5" t="n">
+        <v>-7884</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>LEBELAGE</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="n"/>
+      <c r="D63" s="3" t="n"/>
+      <c r="E63" s="3" t="n"/>
+      <c r="F63" s="3" t="n"/>
+      <c r="G63" s="3" t="n"/>
+      <c r="H63" s="3" t="n"/>
+      <c r="I63" s="2" t="n"/>
+      <c r="J63" s="3" t="n"/>
+      <c r="K63" s="2" t="n"/>
+      <c r="L63" s="3" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="n">
+        <v>53</v>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>LEBELAGE</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>LEBELAGE - Dr. Peptide Derma Eye Cream [40ml] / Крем для глаз антивозрастной с пептидами</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="n">
+        <v>400</v>
+      </c>
+      <c r="E64" s="5" t="n">
+        <v>108</v>
+      </c>
+      <c r="F64" s="5" t="n">
+        <v>1350</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>84</v>
+      </c>
+      <c r="H64" s="5" t="n">
+        <v>96</v>
+      </c>
+      <c r="I64" s="4" t="inlineStr">
+        <is>
+          <t>Классик</t>
+        </is>
+      </c>
+      <c r="J64" s="5" t="n">
+        <v>-12</v>
+      </c>
+      <c r="K64" s="4" t="n">
+        <v>-11</v>
+      </c>
+      <c r="L64" s="5" t="n">
+        <v>-4758</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n"/>
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>MANYO</t>
         </is>
       </c>
-      <c r="C62" s="2" t="n"/>
-      <c r="D62" s="3" t="n"/>
-      <c r="E62" s="3" t="n"/>
-      <c r="F62" s="3" t="n"/>
-      <c r="G62" s="3" t="n"/>
-      <c r="H62" s="3" t="n"/>
-      <c r="I62" s="2" t="n"/>
-      <c r="J62" s="3" t="n"/>
-      <c r="K62" s="2" t="n"/>
-      <c r="L62" s="3" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="B63" s="4" t="inlineStr">
-        <is>
-          <t>MANYO</t>
-        </is>
-      </c>
-      <c r="C63" s="4" t="inlineStr">
-        <is>
-          <t>MANYO BIFIDA COMPLEX AMPOULE GEL CLEANSER [400ml] / Гель для умывания с бифидобактериями</t>
-        </is>
-      </c>
-      <c r="D63" s="5" t="n">
-        <v>650</v>
-      </c>
-      <c r="E63" s="5" t="n">
-        <v>740</v>
-      </c>
-      <c r="F63" s="5" t="n">
-        <v>8740</v>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v>542</v>
-      </c>
-      <c r="H63" s="5" t="n">
-        <v>623</v>
-      </c>
-      <c r="I63" s="4" t="inlineStr">
-        <is>
-          <t>PAPA COSMETIC (ответ)</t>
-        </is>
-      </c>
-      <c r="J63" s="5" t="n">
-        <v>-117</v>
-      </c>
-      <c r="K63" s="4" t="n">
-        <v>-15.8</v>
-      </c>
-      <c r="L63" s="5" t="n">
-        <v>-75886</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="n"/>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>FARMSTAY</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="n"/>
-      <c r="D64" s="3" t="n"/>
-      <c r="E64" s="3" t="n"/>
-      <c r="F64" s="3" t="n"/>
-      <c r="G64" s="3" t="n"/>
-      <c r="H64" s="3" t="n"/>
-      <c r="I64" s="2" t="n"/>
-      <c r="J64" s="3" t="n"/>
-      <c r="K64" s="2" t="n"/>
-      <c r="L64" s="3" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="4" t="n">
-        <v>46</v>
-      </c>
-      <c r="B65" s="4" t="inlineStr">
-        <is>
-          <t>FARMSTAY</t>
-        </is>
-      </c>
-      <c r="C65" s="4" t="inlineStr">
-        <is>
-          <t>FARMSTAY ESCARGOT NOBLESSE INTENSIVE AMPOULE/ сыворотка с улиткой</t>
-        </is>
-      </c>
-      <c r="D65" s="5" t="n">
-        <v>901</v>
-      </c>
-      <c r="E65" s="5" t="n">
-        <v>390</v>
-      </c>
-      <c r="F65" s="5" t="n">
-        <v>4660</v>
-      </c>
-      <c r="G65" s="5" t="n">
-        <v>289</v>
-      </c>
-      <c r="H65" s="5" t="n">
-        <v>332</v>
-      </c>
-      <c r="I65" s="4" t="inlineStr">
-        <is>
-          <t>Классик</t>
-        </is>
-      </c>
-      <c r="J65" s="5" t="n">
-        <v>-58</v>
-      </c>
-      <c r="K65" s="4" t="n">
-        <v>-14.9</v>
-      </c>
-      <c r="L65" s="5" t="n">
-        <v>-52440</v>
-      </c>
+      <c r="C65" s="2" t="n"/>
+      <c r="D65" s="3" t="n"/>
+      <c r="E65" s="3" t="n"/>
+      <c r="F65" s="3" t="n"/>
+      <c r="G65" s="3" t="n"/>
+      <c r="H65" s="3" t="n"/>
+      <c r="I65" s="2" t="n"/>
+      <c r="J65" s="3" t="n"/>
+      <c r="K65" s="2" t="n"/>
+      <c r="L65" s="3" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="4" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>FARMSTAY</t>
+          <t>MANYO</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>FARMSTAY - Collagen Water Full Moist Rolling Eye Serum [25ml] / Сыворотка роллер для глаз</t>
+          <t>MANYO - Bifida Biome Complex Ampoule [50ml] / Антивозрастная сыворотка для лица</t>
         </is>
       </c>
       <c r="D66" s="5" t="n">
-        <v>156</v>
+        <v>1355</v>
       </c>
       <c r="E66" s="5" t="n">
-        <v>232</v>
+        <v>900</v>
       </c>
       <c r="F66" s="5" t="n">
-        <v>2770</v>
+        <v>8740</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>172</v>
+        <v>542</v>
       </c>
       <c r="H66" s="5" t="n">
-        <v>198</v>
+        <v>623</v>
       </c>
       <c r="I66" s="4" t="inlineStr">
         <is>
-          <t>Классик</t>
+          <t>PAPA COSMETIC (ответ)</t>
         </is>
       </c>
       <c r="J66" s="5" t="n">
-        <v>-34</v>
+        <v>-277</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>-14.8</v>
+        <v>-30.7</v>
       </c>
       <c r="L66" s="5" t="n">
-        <v>-5340</v>
+        <v>-374817</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>FARMSTAY</t>
+          <t>MANYO</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>FARMSTAY - Collagen Pure Cleansing Foam [180ml]/Пенка для умывания</t>
+          <t>MANYO - Pure Cleansing Oil [200ml] / Гидрофильное масло для глубокого очищения</t>
         </is>
       </c>
       <c r="D67" s="5" t="n">
-        <v>300</v>
+        <v>80</v>
       </c>
       <c r="E67" s="5" t="n">
-        <v>161</v>
+        <v>853</v>
       </c>
       <c r="F67" s="5" t="n">
-        <v>1930</v>
+        <v>9500</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>120</v>
+        <v>589</v>
       </c>
       <c r="H67" s="5" t="n">
-        <v>138</v>
+        <v>677</v>
       </c>
       <c r="I67" s="4" t="inlineStr">
         <is>
-          <t>Классик</t>
+          <t>PAPA COSMETIC (ответ)</t>
         </is>
       </c>
       <c r="J67" s="5" t="n">
-        <v>-24</v>
+        <v>-176</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>-14.8</v>
+        <v>-20.6</v>
       </c>
       <c r="L67" s="5" t="n">
-        <v>-7158</v>
+        <v>-14052</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n"/>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>CELIMAX</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="n"/>
-      <c r="D68" s="3" t="n"/>
-      <c r="E68" s="3" t="n"/>
-      <c r="F68" s="3" t="n"/>
-      <c r="G68" s="3" t="n"/>
-      <c r="H68" s="3" t="n"/>
-      <c r="I68" s="2" t="n"/>
-      <c r="J68" s="3" t="n"/>
-      <c r="K68" s="2" t="n"/>
-      <c r="L68" s="3" t="n"/>
+      <c r="A68" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>MANYO</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>MANYO BIFIDA COMPLEX AMPOULE GEL CLEANSER [400ml] / Гель для умывания с бифидобактериями</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="n">
+        <v>650</v>
+      </c>
+      <c r="E68" s="5" t="n">
+        <v>740</v>
+      </c>
+      <c r="F68" s="5" t="n">
+        <v>8740</v>
+      </c>
+      <c r="G68" s="5" t="n">
+        <v>542</v>
+      </c>
+      <c r="H68" s="5" t="n">
+        <v>623</v>
+      </c>
+      <c r="I68" s="4" t="inlineStr">
+        <is>
+          <t>PAPA COSMETIC (ответ)</t>
+        </is>
+      </c>
+      <c r="J68" s="5" t="n">
+        <v>-117</v>
+      </c>
+      <c r="K68" s="4" t="n">
+        <v>-15.8</v>
+      </c>
+      <c r="L68" s="5" t="n">
+        <v>-75886</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>CELIMAX</t>
+          <t>MANYO</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD [170ml / 60pads]/Тонер-пэды от воспалений</t>
+          <t>MANYO - Bifida Biome Ampoule Lotion [300ml] / Укрепляющий лосьон с бифидобактериями</t>
         </is>
       </c>
       <c r="D69" s="5" t="n">
-        <v>1500</v>
+        <v>624</v>
       </c>
       <c r="E69" s="5" t="n">
-        <v>708</v>
+        <v>735</v>
       </c>
       <c r="F69" s="5" t="n">
-        <v>8509</v>
+        <v>9500</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>528</v>
+        <v>589</v>
       </c>
       <c r="H69" s="5" t="n">
-        <v>607</v>
+        <v>677</v>
       </c>
       <c r="I69" s="4" t="inlineStr">
         <is>
-          <t>Papa Cosmetic</t>
+          <t>PAPA COSMETIC (ответ)</t>
         </is>
       </c>
       <c r="J69" s="5" t="n">
-        <v>-101</v>
+        <v>-58</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>-14.3</v>
+        <v>-7.9</v>
       </c>
       <c r="L69" s="5" t="n">
-        <v>-151773</v>
+        <v>-36186</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n"/>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>ETUDE</t>
+          <t>PETITFEE</t>
         </is>
       </c>
       <c r="C70" s="2" t="n"/>
@@ -7915,309 +8123,361 @@
     </row>
     <row r="71">
       <c r="A71" s="4" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>ETUDE</t>
+          <t>PETITFEE</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>ETUDE - Baking Powder Crunch Pore Scrub [200ml] / Очищающий скраб для лица с содой</t>
+          <t>PETITFEE - Aura Quartz Hydrogel Eye Patch [60ea]</t>
         </is>
       </c>
       <c r="D71" s="5" t="n">
-        <v>7279</v>
+        <v>89</v>
       </c>
       <c r="E71" s="5" t="n">
-        <v>361</v>
+        <v>591</v>
       </c>
       <c r="F71" s="5" t="n">
-        <v>4400</v>
+        <v>6190</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>273</v>
+        <v>384</v>
       </c>
       <c r="H71" s="5" t="n">
-        <v>314</v>
+        <v>441</v>
       </c>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t>PAPA COSMETIC (ответ)</t>
+          <t>J2K (ответ)</t>
         </is>
       </c>
       <c r="J71" s="5" t="n">
-        <v>-47</v>
+        <v>-150</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>-13.1</v>
+        <v>-25.4</v>
       </c>
       <c r="L71" s="5" t="n">
-        <v>-344369</v>
+        <v>-13345</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n"/>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>ENOUGH</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="n"/>
-      <c r="D72" s="3" t="n"/>
-      <c r="E72" s="3" t="n"/>
-      <c r="F72" s="3" t="n"/>
-      <c r="G72" s="3" t="n"/>
-      <c r="H72" s="3" t="n"/>
-      <c r="I72" s="2" t="n"/>
-      <c r="J72" s="3" t="n"/>
-      <c r="K72" s="2" t="n"/>
-      <c r="L72" s="3" t="n"/>
+      <c r="A72" s="4" t="n">
+        <v>59</v>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Eye Patch [1 pairs]/ Гидрогелевые патчи для глаз с черным жемчугом и золотом 1 пара</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="n">
+        <v>320</v>
+      </c>
+      <c r="E72" s="5" t="n">
+        <v>71</v>
+      </c>
+      <c r="F72" s="5" t="n">
+        <v>819</v>
+      </c>
+      <c r="G72" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="H72" s="5" t="n">
+        <v>58</v>
+      </c>
+      <c r="I72" s="4" t="inlineStr">
+        <is>
+          <t>FINESKIN (ответ)</t>
+        </is>
+      </c>
+      <c r="J72" s="5" t="n">
+        <v>-13</v>
+      </c>
+      <c r="K72" s="4" t="n">
+        <v>-18</v>
+      </c>
+      <c r="L72" s="5" t="n">
+        <v>-4110</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>PETITFEE - Gold Hydrogel Eye Patch [1 Pairs] / гидрогелевые патчи для глаз с золотом 1 пара</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="n">
+        <v>428</v>
+      </c>
+      <c r="E73" s="5" t="n">
+        <v>71</v>
+      </c>
+      <c r="F73" s="5" t="n">
+        <v>819</v>
+      </c>
+      <c r="G73" s="5" t="n">
         <v>51</v>
       </c>
-      <c r="B73" s="4" t="inlineStr">
-        <is>
-          <t>ENOUGH</t>
-        </is>
-      </c>
-      <c r="C73" s="4" t="inlineStr">
-        <is>
-          <t>ENOUGH Collagen whitening cover tip concealer #02 [9g]/Консилер для лица (основная карточка)</t>
-        </is>
-      </c>
-      <c r="D73" s="5" t="n">
-        <v>300</v>
-      </c>
-      <c r="E73" s="5" t="n">
-        <v>183</v>
-      </c>
-      <c r="F73" s="5" t="n">
-        <v>2250</v>
-      </c>
-      <c r="G73" s="5" t="n">
-        <v>140</v>
-      </c>
       <c r="H73" s="5" t="n">
-        <v>160</v>
+        <v>58</v>
       </c>
       <c r="I73" s="4" t="inlineStr">
         <is>
-          <t>Классик</t>
+          <t>FINESKIN (ответ)</t>
         </is>
       </c>
       <c r="J73" s="5" t="n">
-        <v>-23</v>
+        <v>-13</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>-12.5</v>
+        <v>-18</v>
       </c>
       <c r="L73" s="5" t="n">
-        <v>-6844</v>
+        <v>-5498</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>ENOUGH</t>
+          <t>PETITFEE</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENOUGH Collagen whitening cover tip concealer #01 [9g]/Консилер для лица (основная карточка) </t>
+          <t>PETITFEE - Gold &amp; Snail Hydrogel Eye Patch [60ea] / Гидрогелевые патчи для глаз с золотом и улиткой</t>
         </is>
       </c>
       <c r="D74" s="5" t="n">
-        <v>200</v>
+        <v>144</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>183</v>
+        <v>415</v>
       </c>
       <c r="F74" s="5" t="n">
-        <v>2250</v>
+        <v>5690</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>140</v>
+        <v>353</v>
       </c>
       <c r="H74" s="5" t="n">
-        <v>160</v>
+        <v>406</v>
       </c>
       <c r="I74" s="4" t="inlineStr">
         <is>
-          <t>Классик</t>
+          <t>J2K (ответ)</t>
         </is>
       </c>
       <c r="J74" s="5" t="n">
-        <v>-23</v>
+        <v>-10</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>-12.5</v>
+        <v>-2.3</v>
       </c>
       <c r="L74" s="5" t="n">
-        <v>-4563</v>
+        <v>-1406</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="n">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>ENOUGH</t>
+          <t>PETITFEE</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>ENOUGH Collagen whitening cover tip concealer #03 [9g]/ Консилер для лица (основаная карточка)</t>
+          <t>PETITFEE - Gold Hydrogel Eye Patch [60ea] / гидрогелевые патчи для глаз с золотом</t>
         </is>
       </c>
       <c r="D75" s="5" t="n">
-        <v>260</v>
+        <v>405</v>
       </c>
       <c r="E75" s="5" t="n">
-        <v>183</v>
+        <v>415</v>
       </c>
       <c r="F75" s="5" t="n">
-        <v>2250</v>
+        <v>5690</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>140</v>
+        <v>353</v>
       </c>
       <c r="H75" s="5" t="n">
-        <v>160</v>
+        <v>406</v>
       </c>
       <c r="I75" s="4" t="inlineStr">
         <is>
-          <t>Классик</t>
+          <t>J2K (ответ)</t>
         </is>
       </c>
       <c r="J75" s="5" t="n">
-        <v>-23</v>
+        <v>-10</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>-12.5</v>
+        <v>-2.3</v>
       </c>
       <c r="L75" s="5" t="n">
-        <v>-5932</v>
+        <v>-3954</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n"/>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>DEOPROCE</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="n"/>
-      <c r="D76" s="3" t="n"/>
-      <c r="E76" s="3" t="n"/>
-      <c r="F76" s="3" t="n"/>
-      <c r="G76" s="3" t="n"/>
-      <c r="H76" s="3" t="n"/>
-      <c r="I76" s="2" t="n"/>
-      <c r="J76" s="3" t="n"/>
-      <c r="K76" s="2" t="n"/>
-      <c r="L76" s="3" t="n"/>
+      <c r="A76" s="4" t="n">
+        <v>63</v>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>PETITFEE - Gold Hydrogel Mask Pack [5pcs] / Гидрогелевая маска для лица с золотом</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="n">
+        <v>390</v>
+      </c>
+      <c r="E76" s="5" t="n">
+        <v>507</v>
+      </c>
+      <c r="F76" s="5" t="n">
+        <v>6990</v>
+      </c>
+      <c r="G76" s="5" t="n">
+        <v>433</v>
+      </c>
+      <c r="H76" s="5" t="n">
+        <v>498</v>
+      </c>
+      <c r="I76" s="4" t="inlineStr">
+        <is>
+          <t>J2K (ответ)</t>
+        </is>
+      </c>
+      <c r="J76" s="5" t="n">
+        <v>-9</v>
+      </c>
+      <c r="K76" s="4" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="L76" s="5" t="n">
+        <v>-3421</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>DEOPROCE</t>
+          <t>PETITFEE</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>DEOPROCE RINSE - BLACK GARLIC INTENSME ENERGY [1000ml] / Бальзам от выпадения волос Чёрный чеснок</t>
+          <t>PETITFEE - Bera Glucan Deep Firming Eye Patch [60ea] / Тканевые патчи для век увлажняющие</t>
         </is>
       </c>
       <c r="D77" s="5" t="n">
-        <v>400</v>
+        <v>180</v>
       </c>
       <c r="E77" s="5" t="n">
-        <v>359</v>
+        <v>487</v>
       </c>
       <c r="F77" s="5" t="n">
-        <v>4431</v>
+        <v>6790</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>275</v>
+        <v>421</v>
       </c>
       <c r="H77" s="5" t="n">
-        <v>316</v>
+        <v>484</v>
       </c>
       <c r="I77" s="4" t="inlineStr">
         <is>
-          <t>FINESKIN (ответ)</t>
+          <t>J2K (ответ)</t>
         </is>
       </c>
       <c r="J77" s="5" t="n">
-        <v>-43</v>
+        <v>-3</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>-12</v>
+        <v>-0.5</v>
       </c>
       <c r="L77" s="5" t="n">
-        <v>-17200</v>
+        <v>-461</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>DEOPROCE</t>
+          <t>PETITFEE</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>DEOPROCE SHAMPOO - BLACK GARLIC INTENSME ENERGY [1000ml]/ Шампунь с черным чесноком против выпадения волос</t>
+          <t>PETITFEE - Pink Vita Brightening Eye Patch [60ea] / Тканевые патчи для век увлажняющие</t>
         </is>
       </c>
       <c r="D78" s="5" t="n">
-        <v>400</v>
+        <v>117</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>368</v>
+        <v>487</v>
       </c>
       <c r="F78" s="5" t="n">
-        <v>4547</v>
+        <v>6790</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>282</v>
+        <v>421</v>
       </c>
       <c r="H78" s="5" t="n">
-        <v>324</v>
+        <v>484</v>
       </c>
       <c r="I78" s="4" t="inlineStr">
         <is>
-          <t>FINESKIN (ответ)</t>
+          <t>J2K (ответ)</t>
         </is>
       </c>
       <c r="J78" s="5" t="n">
-        <v>-44</v>
+        <v>-3</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>-11.9</v>
+        <v>-0.5</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>-17488</v>
+        <v>-300</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n"/>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>LEBELAGE</t>
+          <t>ROUND LAB</t>
         </is>
       </c>
       <c r="C79" s="2" t="n"/>
@@ -8233,69 +8493,95 @@
     </row>
     <row r="80">
       <c r="A80" s="4" t="n">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>LEBELAGE</t>
+          <t>ROUND LAB</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>LEBELAGE - Dr. Peptide Derma Eye Cream [40ml] / Крем для глаз антивозрастной с пептидами</t>
+          <t>ROUND LAB PINE CALMING CICA AMPOULE_30ml - Сыворотка для жирной кожи лица увлажняющая с центеллой</t>
         </is>
       </c>
       <c r="D80" s="5" t="n">
-        <v>400</v>
+        <v>32</v>
       </c>
       <c r="E80" s="5" t="n">
-        <v>108</v>
+        <v>820</v>
       </c>
       <c r="F80" s="5" t="n">
-        <v>1350</v>
+        <v>8293</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>84</v>
+        <v>514</v>
       </c>
       <c r="H80" s="5" t="n">
-        <v>96</v>
+        <v>591</v>
       </c>
       <c r="I80" s="4" t="inlineStr">
         <is>
-          <t>Классик</t>
+          <t>G&amp;E Global</t>
         </is>
       </c>
       <c r="J80" s="5" t="n">
-        <v>-12</v>
+        <v>-228</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>-11</v>
+        <v>-27.9</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>-4758</v>
+        <v>-7310</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n"/>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="A81" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
         <is>
           <t>ROUND LAB</t>
         </is>
       </c>
-      <c r="C81" s="2" t="n"/>
-      <c r="D81" s="3" t="n"/>
-      <c r="E81" s="3" t="n"/>
-      <c r="F81" s="3" t="n"/>
-      <c r="G81" s="3" t="n"/>
-      <c r="H81" s="3" t="n"/>
-      <c r="I81" s="2" t="n"/>
-      <c r="J81" s="3" t="n"/>
-      <c r="K81" s="2" t="n"/>
-      <c r="L81" s="3" t="n"/>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>ROUND LAB BIRCH JUICE MOISTURIZING CREAM_80ml -Увлажняющий крем с березовым соком</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="n">
+        <v>259</v>
+      </c>
+      <c r="E81" s="5" t="n">
+        <v>1093</v>
+      </c>
+      <c r="F81" s="5" t="n">
+        <v>11702</v>
+      </c>
+      <c r="G81" s="5" t="n">
+        <v>726</v>
+      </c>
+      <c r="H81" s="5" t="n">
+        <v>834</v>
+      </c>
+      <c r="I81" s="4" t="inlineStr">
+        <is>
+          <t>G&amp;E Global</t>
+        </is>
+      </c>
+      <c r="J81" s="5" t="n">
+        <v>-259</v>
+      </c>
+      <c r="K81" s="4" t="n">
+        <v>-23.7</v>
+      </c>
+      <c r="L81" s="5" t="n">
+        <v>-66979</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="n">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
@@ -8304,938 +8590,292 @@
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
+          <t>ROUND LAB MUGWORT CALMING CLEANSER_150ml - Очищающая пенка для умывания лица от прыщей и акне</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="n">
+        <v>1422</v>
+      </c>
+      <c r="E82" s="5" t="n">
+        <v>512</v>
+      </c>
+      <c r="F82" s="5" t="n">
+        <v>5963</v>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>370</v>
+      </c>
+      <c r="H82" s="5" t="n">
+        <v>425</v>
+      </c>
+      <c r="I82" s="4" t="inlineStr">
+        <is>
+          <t>G&amp;E Global</t>
+        </is>
+      </c>
+      <c r="J82" s="5" t="n">
+        <v>-87</v>
+      </c>
+      <c r="K82" s="4" t="n">
+        <v>-17</v>
+      </c>
+      <c r="L82" s="5" t="n">
+        <v>-123939</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="n">
+        <v>69</v>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>ROUND LAB</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
           <t>ROUND LAB 1025 DOKDO CLEANSER_150ml - Увлажняющая пенка для умывания лица</t>
         </is>
       </c>
-      <c r="D82" s="5" t="n">
+      <c r="D83" s="5" t="n">
         <v>7126</v>
       </c>
-      <c r="E82" s="5" t="n">
+      <c r="E83" s="5" t="n">
         <v>463</v>
       </c>
-      <c r="F82" s="5" t="n">
+      <c r="F83" s="5" t="n">
         <v>5857</v>
       </c>
-      <c r="G82" s="5" t="n">
+      <c r="G83" s="5" t="n">
         <v>363</v>
       </c>
-      <c r="H82" s="5" t="n">
+      <c r="H83" s="5" t="n">
         <v>418</v>
       </c>
-      <c r="I82" s="4" t="inlineStr">
+      <c r="I83" s="4" t="inlineStr">
         <is>
           <t>G&amp;E Global</t>
         </is>
       </c>
-      <c r="J82" s="5" t="n">
+      <c r="J83" s="5" t="n">
         <v>-46</v>
       </c>
-      <c r="K82" s="4" t="n">
+      <c r="K83" s="4" t="n">
         <v>-9.800000000000001</v>
       </c>
-      <c r="L82" s="5" t="n">
+      <c r="L83" s="5" t="n">
         <v>-324845</v>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="n"/>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>FARMSTAY</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="n"/>
-      <c r="D83" s="3" t="n"/>
-      <c r="E83" s="3" t="n"/>
-      <c r="F83" s="3" t="n"/>
-      <c r="G83" s="3" t="n"/>
-      <c r="H83" s="3" t="n"/>
-      <c r="I83" s="2" t="n"/>
-      <c r="J83" s="3" t="n"/>
-      <c r="K83" s="2" t="n"/>
-      <c r="L83" s="3" t="n"/>
-    </row>
     <row r="84">
-      <c r="A84" s="4" t="n">
-        <v>58</v>
-      </c>
-      <c r="B84" s="4" t="inlineStr">
-        <is>
-          <t>FARMSTAY</t>
-        </is>
-      </c>
-      <c r="C84" s="4" t="inlineStr">
-        <is>
-          <t>FARMSTAY - Escargot Noblesse Intensive Cream [50g] / Крем с муцином королевской улитки</t>
-        </is>
-      </c>
-      <c r="D84" s="5" t="n">
-        <v>860</v>
-      </c>
-      <c r="E84" s="5" t="n">
-        <v>314</v>
-      </c>
-      <c r="F84" s="5" t="n">
-        <v>4010</v>
-      </c>
-      <c r="G84" s="5" t="n">
-        <v>249</v>
-      </c>
-      <c r="H84" s="5" t="n">
-        <v>286</v>
-      </c>
-      <c r="I84" s="4" t="inlineStr">
-        <is>
-          <t>Классик</t>
-        </is>
-      </c>
-      <c r="J84" s="5" t="n">
-        <v>-28</v>
-      </c>
-      <c r="K84" s="4" t="n">
-        <v>-8.9</v>
-      </c>
-      <c r="L84" s="5" t="n">
-        <v>-24017</v>
-      </c>
+      <c r="A84" s="2" t="n"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>SKIN1004</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="n"/>
+      <c r="D84" s="3" t="n"/>
+      <c r="E84" s="3" t="n"/>
+      <c r="F84" s="3" t="n"/>
+      <c r="G84" s="3" t="n"/>
+      <c r="H84" s="3" t="n"/>
+      <c r="I84" s="2" t="n"/>
+      <c r="J84" s="3" t="n"/>
+      <c r="K84" s="2" t="n"/>
+      <c r="L84" s="3" t="n"/>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n"/>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>MANYO</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="n"/>
-      <c r="D85" s="3" t="n"/>
-      <c r="E85" s="3" t="n"/>
-      <c r="F85" s="3" t="n"/>
-      <c r="G85" s="3" t="n"/>
-      <c r="H85" s="3" t="n"/>
-      <c r="I85" s="2" t="n"/>
-      <c r="J85" s="3" t="n"/>
-      <c r="K85" s="2" t="n"/>
-      <c r="L85" s="3" t="n"/>
+      <c r="A85" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>SKIN1004</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>SKIN1004 - Madagascar Centella Ampoule [30ml] / Сыворотка для лица успокаивающая из экстракта центеллы.</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="E85" s="5" t="n">
+        <v>368</v>
+      </c>
+      <c r="F85" s="5" t="n">
+        <v>5038</v>
+      </c>
+      <c r="G85" s="5" t="n">
+        <v>312</v>
+      </c>
+      <c r="H85" s="5" t="n">
+        <v>359</v>
+      </c>
+      <c r="I85" s="4" t="inlineStr">
+        <is>
+          <t>FINESKIN (ответ)</t>
+        </is>
+      </c>
+      <c r="J85" s="5" t="n">
+        <v>-9</v>
+      </c>
+      <c r="K85" s="4" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="L85" s="5" t="n">
+        <v>-260</v>
+      </c>
     </row>
     <row r="86">
-      <c r="A86" s="4" t="n">
-        <v>59</v>
-      </c>
-      <c r="B86" s="4" t="inlineStr">
-        <is>
-          <t>MANYO</t>
-        </is>
-      </c>
-      <c r="C86" s="4" t="inlineStr">
-        <is>
-          <t>MANYO - Bifida Biome Ampoule Lotion [300ml] / Укрепляющий лосьон с бифидобактериями</t>
-        </is>
-      </c>
-      <c r="D86" s="5" t="n">
-        <v>624</v>
-      </c>
-      <c r="E86" s="5" t="n">
-        <v>735</v>
-      </c>
-      <c r="F86" s="5" t="n">
-        <v>9500</v>
-      </c>
-      <c r="G86" s="5" t="n">
-        <v>589</v>
-      </c>
-      <c r="H86" s="5" t="n">
-        <v>677</v>
-      </c>
-      <c r="I86" s="4" t="inlineStr">
-        <is>
-          <t>PAPA COSMETIC (ответ)</t>
-        </is>
-      </c>
-      <c r="J86" s="5" t="n">
-        <v>-58</v>
-      </c>
-      <c r="K86" s="4" t="n">
-        <v>-7.9</v>
-      </c>
-      <c r="L86" s="5" t="n">
-        <v>-36186</v>
-      </c>
+      <c r="A86" s="2" t="n"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>SOME BY MI</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="n"/>
+      <c r="D86" s="3" t="n"/>
+      <c r="E86" s="3" t="n"/>
+      <c r="F86" s="3" t="n"/>
+      <c r="G86" s="3" t="n"/>
+      <c r="H86" s="3" t="n"/>
+      <c r="I86" s="2" t="n"/>
+      <c r="J86" s="3" t="n"/>
+      <c r="K86" s="2" t="n"/>
+      <c r="L86" s="3" t="n"/>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n"/>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>FARMSTAY</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="n"/>
-      <c r="D87" s="3" t="n"/>
-      <c r="E87" s="3" t="n"/>
-      <c r="F87" s="3" t="n"/>
-      <c r="G87" s="3" t="n"/>
-      <c r="H87" s="3" t="n"/>
-      <c r="I87" s="2" t="n"/>
-      <c r="J87" s="3" t="n"/>
-      <c r="K87" s="2" t="n"/>
-      <c r="L87" s="3" t="n"/>
+      <c r="A87" s="4" t="n">
+        <v>71</v>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>SOME BY MI</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>SOME BY MI - AHA-BHA-PHA 30 Days Miracle Cream [60g] / Крем для лица</t>
+        </is>
+      </c>
+      <c r="D87" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="E87" s="5" t="n">
+        <v>1057</v>
+      </c>
+      <c r="F87" s="5" t="n">
+        <v>10685</v>
+      </c>
+      <c r="G87" s="5" t="n">
+        <v>662</v>
+      </c>
+      <c r="H87" s="5" t="n">
+        <v>762</v>
+      </c>
+      <c r="I87" s="4" t="inlineStr">
+        <is>
+          <t>FINESKIN (ответ)</t>
+        </is>
+      </c>
+      <c r="J87" s="5" t="n">
+        <v>-295</v>
+      </c>
+      <c r="K87" s="4" t="n">
+        <v>-27.9</v>
+      </c>
+      <c r="L87" s="5" t="n">
+        <v>-16245</v>
+      </c>
     </row>
     <row r="88">
-      <c r="A88" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="B88" s="4" t="inlineStr">
-        <is>
-          <t>FARMSTAY</t>
-        </is>
-      </c>
-      <c r="C88" s="4" t="inlineStr">
-        <is>
-          <t>FARMSTAY - Collagen &amp; Hyaluronic Acid All-In One Ampoule [250ml] / Сыворотка с коллагеном и гиалуроновой кислотой</t>
-        </is>
-      </c>
-      <c r="D88" s="5" t="n">
-        <v>6179</v>
-      </c>
-      <c r="E88" s="5" t="n">
-        <v>348</v>
-      </c>
-      <c r="F88" s="5" t="n">
-        <v>4660</v>
-      </c>
-      <c r="G88" s="5" t="n">
-        <v>289</v>
-      </c>
-      <c r="H88" s="5" t="n">
-        <v>332</v>
-      </c>
-      <c r="I88" s="4" t="inlineStr">
-        <is>
-          <t>Классик</t>
-        </is>
-      </c>
-      <c r="J88" s="5" t="n">
-        <v>-16</v>
-      </c>
-      <c r="K88" s="4" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="L88" s="5" t="n">
-        <v>-95787</v>
-      </c>
+      <c r="A88" s="2" t="n"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>VT COSMETICS</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="n"/>
+      <c r="D88" s="3" t="n"/>
+      <c r="E88" s="3" t="n"/>
+      <c r="F88" s="3" t="n"/>
+      <c r="G88" s="3" t="n"/>
+      <c r="H88" s="3" t="n"/>
+      <c r="I88" s="2" t="n"/>
+      <c r="J88" s="3" t="n"/>
+      <c r="K88" s="2" t="n"/>
+      <c r="L88" s="3" t="n"/>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n"/>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>ELIZAVECCA</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="n"/>
-      <c r="D89" s="3" t="n"/>
-      <c r="E89" s="3" t="n"/>
-      <c r="F89" s="3" t="n"/>
-      <c r="G89" s="3" t="n"/>
-      <c r="H89" s="3" t="n"/>
-      <c r="I89" s="2" t="n"/>
-      <c r="J89" s="3" t="n"/>
-      <c r="K89" s="2" t="n"/>
-      <c r="L89" s="3" t="n"/>
+      <c r="A89" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>VT COSMETICS</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>VT REEDLE SHOT 100 / Бустер-сыворотка с микроиглами</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="n">
+        <v>397</v>
+      </c>
+      <c r="E89" s="5" t="n">
+        <v>974</v>
+      </c>
+      <c r="F89" s="5" t="n">
+        <v>13568</v>
+      </c>
+      <c r="G89" s="5" t="n">
+        <v>841</v>
+      </c>
+      <c r="H89" s="5" t="n">
+        <v>967</v>
+      </c>
+      <c r="I89" s="4" t="inlineStr">
+        <is>
+          <t>FINESKIN (ответ)</t>
+        </is>
+      </c>
+      <c r="J89" s="5" t="n">
+        <v>-7</v>
+      </c>
+      <c r="K89" s="4" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="L89" s="5" t="n">
+        <v>-2637</v>
+      </c>
     </row>
     <row r="90">
-      <c r="A90" s="4" t="n">
-        <v>61</v>
-      </c>
-      <c r="B90" s="4" t="inlineStr">
-        <is>
-          <t>ELIZAVECCA</t>
-        </is>
-      </c>
-      <c r="C90" s="4" t="inlineStr">
-        <is>
-          <t>ELIZAVECCA - CER-100 Collagen Ceramide Coating Protein Treatment [100ml] / Коллагеновая маска для волос</t>
-        </is>
-      </c>
-      <c r="D90" s="5" t="n">
-        <v>300</v>
-      </c>
-      <c r="E90" s="5" t="n">
-        <v>242</v>
-      </c>
-      <c r="F90" s="5" t="n">
-        <v>3276</v>
-      </c>
-      <c r="G90" s="5" t="n">
-        <v>203</v>
-      </c>
-      <c r="H90" s="5" t="n">
-        <v>234</v>
-      </c>
-      <c r="I90" s="4" t="inlineStr">
-        <is>
-          <t>FINESKIN (ответ)</t>
-        </is>
-      </c>
-      <c r="J90" s="5" t="n">
-        <v>-9</v>
-      </c>
-      <c r="K90" s="4" t="n">
-        <v>-3.6</v>
-      </c>
-      <c r="L90" s="5" t="n">
-        <v>-2595</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="n"/>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>CELIMAX</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="n"/>
-      <c r="D91" s="3" t="n"/>
-      <c r="E91" s="3" t="n"/>
-      <c r="F91" s="3" t="n"/>
-      <c r="G91" s="3" t="n"/>
-      <c r="H91" s="3" t="n"/>
-      <c r="I91" s="2" t="n"/>
-      <c r="J91" s="3" t="n"/>
-      <c r="K91" s="2" t="n"/>
-      <c r="L91" s="3" t="n"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="4" t="n">
-        <v>62</v>
-      </c>
-      <c r="B92" s="4" t="inlineStr">
-        <is>
-          <t>CELIMAX</t>
-        </is>
-      </c>
-      <c r="C92" s="4" t="inlineStr">
-        <is>
-          <t>Celimax Dual Barrier Creamy Toner, тонер 150 мл</t>
-        </is>
-      </c>
-      <c r="D92" s="5" t="n">
-        <v>4520</v>
-      </c>
-      <c r="E92" s="5" t="n">
-        <v>664</v>
-      </c>
-      <c r="F92" s="5" t="n">
-        <v>9000</v>
-      </c>
-      <c r="G92" s="5" t="n">
-        <v>558</v>
-      </c>
-      <c r="H92" s="5" t="n">
-        <v>642</v>
-      </c>
-      <c r="I92" s="4" t="inlineStr">
-        <is>
-          <t>Papa Cosmetic</t>
-        </is>
-      </c>
-      <c r="J92" s="5" t="n">
-        <v>-22</v>
-      </c>
-      <c r="K92" s="4" t="n">
-        <v>-3.3</v>
-      </c>
-      <c r="L92" s="5" t="n">
-        <v>-100163</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="n"/>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>ENOUGH</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="n"/>
-      <c r="D93" s="3" t="n"/>
-      <c r="E93" s="3" t="n"/>
-      <c r="F93" s="3" t="n"/>
-      <c r="G93" s="3" t="n"/>
-      <c r="H93" s="3" t="n"/>
-      <c r="I93" s="2" t="n"/>
-      <c r="J93" s="3" t="n"/>
-      <c r="K93" s="2" t="n"/>
-      <c r="L93" s="3" t="n"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="4" t="n">
-        <v>63</v>
-      </c>
-      <c r="B94" s="4" t="inlineStr">
-        <is>
-          <t>ENOUGH</t>
-        </is>
-      </c>
-      <c r="C94" s="4" t="inlineStr">
-        <is>
-          <t>ENOUGH - Collagen Whitening Moisture Cream 3in1 [50g] / Антивозрастной отбеливающий крем с коллагеном</t>
-        </is>
-      </c>
-      <c r="D94" s="5" t="n">
-        <v>344</v>
-      </c>
-      <c r="E94" s="5" t="n">
-        <v>184</v>
-      </c>
-      <c r="F94" s="5" t="n">
-        <v>2500</v>
-      </c>
-      <c r="G94" s="5" t="n">
-        <v>155</v>
-      </c>
-      <c r="H94" s="5" t="n">
-        <v>178</v>
-      </c>
-      <c r="I94" s="4" t="inlineStr">
-        <is>
-          <t>Классик</t>
-        </is>
-      </c>
-      <c r="J94" s="5" t="n">
-        <v>-6</v>
-      </c>
-      <c r="K94" s="4" t="n">
-        <v>-3.1</v>
-      </c>
-      <c r="L94" s="5" t="n">
-        <v>-1937</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="n"/>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>SKIN1004</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="n"/>
-      <c r="D95" s="3" t="n"/>
-      <c r="E95" s="3" t="n"/>
-      <c r="F95" s="3" t="n"/>
-      <c r="G95" s="3" t="n"/>
-      <c r="H95" s="3" t="n"/>
-      <c r="I95" s="2" t="n"/>
-      <c r="J95" s="3" t="n"/>
-      <c r="K95" s="2" t="n"/>
-      <c r="L95" s="3" t="n"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="4" t="n">
-        <v>64</v>
-      </c>
-      <c r="B96" s="4" t="inlineStr">
-        <is>
-          <t>SKIN1004</t>
-        </is>
-      </c>
-      <c r="C96" s="4" t="inlineStr">
-        <is>
-          <t>SKIN1004 - Madagascar Centella Ampoule [30ml] / Сыворотка для лица успокаивающая из экстракта центеллы.</t>
-        </is>
-      </c>
-      <c r="D96" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="E96" s="5" t="n">
-        <v>368</v>
-      </c>
-      <c r="F96" s="5" t="n">
-        <v>5038</v>
-      </c>
-      <c r="G96" s="5" t="n">
-        <v>312</v>
-      </c>
-      <c r="H96" s="5" t="n">
-        <v>359</v>
-      </c>
-      <c r="I96" s="4" t="inlineStr">
-        <is>
-          <t>FINESKIN (ответ)</t>
-        </is>
-      </c>
-      <c r="J96" s="5" t="n">
-        <v>-9</v>
-      </c>
-      <c r="K96" s="4" t="n">
-        <v>-2.4</v>
-      </c>
-      <c r="L96" s="5" t="n">
-        <v>-260</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="n"/>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>PETITFEE</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="n"/>
-      <c r="D97" s="3" t="n"/>
-      <c r="E97" s="3" t="n"/>
-      <c r="F97" s="3" t="n"/>
-      <c r="G97" s="3" t="n"/>
-      <c r="H97" s="3" t="n"/>
-      <c r="I97" s="2" t="n"/>
-      <c r="J97" s="3" t="n"/>
-      <c r="K97" s="2" t="n"/>
-      <c r="L97" s="3" t="n"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="4" t="n">
-        <v>65</v>
-      </c>
-      <c r="B98" s="4" t="inlineStr">
-        <is>
-          <t>PETITFEE</t>
-        </is>
-      </c>
-      <c r="C98" s="4" t="inlineStr">
-        <is>
-          <t>PETITFEE - Gold &amp; Snail Hydrogel Eye Patch [60ea] / Гидрогелевые патчи для глаз с золотом и улиткой</t>
-        </is>
-      </c>
-      <c r="D98" s="5" t="n">
-        <v>144</v>
-      </c>
-      <c r="E98" s="5" t="n">
-        <v>415</v>
-      </c>
-      <c r="F98" s="5" t="n">
-        <v>5690</v>
-      </c>
-      <c r="G98" s="5" t="n">
-        <v>353</v>
-      </c>
-      <c r="H98" s="5" t="n">
-        <v>406</v>
-      </c>
-      <c r="I98" s="4" t="inlineStr">
-        <is>
-          <t>J2K (ответ)</t>
-        </is>
-      </c>
-      <c r="J98" s="5" t="n">
-        <v>-10</v>
-      </c>
-      <c r="K98" s="4" t="n">
-        <v>-2.3</v>
-      </c>
-      <c r="L98" s="5" t="n">
-        <v>-1406</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="4" t="n">
-        <v>66</v>
-      </c>
-      <c r="B99" s="4" t="inlineStr">
-        <is>
-          <t>PETITFEE</t>
-        </is>
-      </c>
-      <c r="C99" s="4" t="inlineStr">
-        <is>
-          <t>PETITFEE - Gold Hydrogel Eye Patch [60ea] / гидрогелевые патчи для глаз с золотом</t>
-        </is>
-      </c>
-      <c r="D99" s="5" t="n">
-        <v>405</v>
-      </c>
-      <c r="E99" s="5" t="n">
-        <v>415</v>
-      </c>
-      <c r="F99" s="5" t="n">
-        <v>5690</v>
-      </c>
-      <c r="G99" s="5" t="n">
-        <v>353</v>
-      </c>
-      <c r="H99" s="5" t="n">
-        <v>406</v>
-      </c>
-      <c r="I99" s="4" t="inlineStr">
-        <is>
-          <t>J2K (ответ)</t>
-        </is>
-      </c>
-      <c r="J99" s="5" t="n">
-        <v>-10</v>
-      </c>
-      <c r="K99" s="4" t="n">
-        <v>-2.3</v>
-      </c>
-      <c r="L99" s="5" t="n">
-        <v>-3954</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="n"/>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>CELIMAX</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="n"/>
-      <c r="D100" s="3" t="n"/>
-      <c r="E100" s="3" t="n"/>
-      <c r="F100" s="3" t="n"/>
-      <c r="G100" s="3" t="n"/>
-      <c r="H100" s="3" t="n"/>
-      <c r="I100" s="2" t="n"/>
-      <c r="J100" s="3" t="n"/>
-      <c r="K100" s="2" t="n"/>
-      <c r="L100" s="3" t="n"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="4" t="n">
-        <v>67</v>
-      </c>
-      <c r="B101" s="4" t="inlineStr">
-        <is>
-          <t>CELIMAX</t>
-        </is>
-      </c>
-      <c r="C101" s="4" t="inlineStr">
-        <is>
-          <t>CELIMAX THE REAL NONI MOISTURE BALANCING TONER (NEW) [150ml]/Восстанавливающий тонер с экстрактом нони</t>
-        </is>
-      </c>
-      <c r="D101" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="E101" s="5" t="n">
-        <v>720</v>
-      </c>
-      <c r="F101" s="5" t="n">
-        <v>9875</v>
-      </c>
-      <c r="G101" s="5" t="n">
-        <v>612</v>
-      </c>
-      <c r="H101" s="5" t="n">
-        <v>704</v>
-      </c>
-      <c r="I101" s="4" t="inlineStr">
-        <is>
-          <t>PAPA COSMETIC (ответ)</t>
-        </is>
-      </c>
-      <c r="J101" s="5" t="n">
-        <v>-15</v>
-      </c>
-      <c r="K101" s="4" t="n">
-        <v>-2.2</v>
-      </c>
-      <c r="L101" s="5" t="n">
-        <v>-356</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="4" t="n">
-        <v>68</v>
-      </c>
-      <c r="B102" s="4" t="inlineStr">
-        <is>
-          <t>CELIMAX</t>
-        </is>
-      </c>
-      <c r="C102" s="4" t="inlineStr">
-        <is>
-          <t>CELIMAX DUAL BARRIER SKIN WEARABLE CREAM [50ml]/Крем для восстановления защитного барьера кожи лица</t>
-        </is>
-      </c>
-      <c r="D102" s="5" t="n">
-        <v>90</v>
-      </c>
-      <c r="E102" s="5" t="n">
-        <v>864</v>
-      </c>
-      <c r="F102" s="5" t="n">
-        <v>11900</v>
-      </c>
-      <c r="G102" s="5" t="n">
-        <v>738</v>
-      </c>
-      <c r="H102" s="5" t="n">
-        <v>848</v>
-      </c>
-      <c r="I102" s="4" t="inlineStr">
-        <is>
-          <t>PAPA COSMETIC (ответ)</t>
-        </is>
-      </c>
-      <c r="J102" s="5" t="n">
-        <v>-16</v>
-      </c>
-      <c r="K102" s="4" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="L102" s="5" t="n">
-        <v>-1408</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="n"/>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>PETITFEE</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="n"/>
-      <c r="D103" s="3" t="n"/>
-      <c r="E103" s="3" t="n"/>
-      <c r="F103" s="3" t="n"/>
-      <c r="G103" s="3" t="n"/>
-      <c r="H103" s="3" t="n"/>
-      <c r="I103" s="2" t="n"/>
-      <c r="J103" s="3" t="n"/>
-      <c r="K103" s="2" t="n"/>
-      <c r="L103" s="3" t="n"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="4" t="n">
-        <v>69</v>
-      </c>
-      <c r="B104" s="4" t="inlineStr">
-        <is>
-          <t>PETITFEE</t>
-        </is>
-      </c>
-      <c r="C104" s="4" t="inlineStr">
-        <is>
-          <t>PETITFEE - Gold Hydrogel Mask Pack [5pcs] / Гидрогелевая маска для лица с золотом</t>
-        </is>
-      </c>
-      <c r="D104" s="5" t="n">
-        <v>390</v>
-      </c>
-      <c r="E104" s="5" t="n">
-        <v>507</v>
-      </c>
-      <c r="F104" s="5" t="n">
-        <v>6990</v>
-      </c>
-      <c r="G104" s="5" t="n">
-        <v>433</v>
-      </c>
-      <c r="H104" s="5" t="n">
-        <v>498</v>
-      </c>
-      <c r="I104" s="4" t="inlineStr">
-        <is>
-          <t>J2K (ответ)</t>
-        </is>
-      </c>
-      <c r="J104" s="5" t="n">
-        <v>-9</v>
-      </c>
-      <c r="K104" s="4" t="n">
-        <v>-1.7</v>
-      </c>
-      <c r="L104" s="5" t="n">
-        <v>-3421</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="n"/>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>VT COSMETICS</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="n"/>
-      <c r="D105" s="3" t="n"/>
-      <c r="E105" s="3" t="n"/>
-      <c r="F105" s="3" t="n"/>
-      <c r="G105" s="3" t="n"/>
-      <c r="H105" s="3" t="n"/>
-      <c r="I105" s="2" t="n"/>
-      <c r="J105" s="3" t="n"/>
-      <c r="K105" s="2" t="n"/>
-      <c r="L105" s="3" t="n"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="4" t="n">
-        <v>70</v>
-      </c>
-      <c r="B106" s="4" t="inlineStr">
-        <is>
-          <t>VT COSMETICS</t>
-        </is>
-      </c>
-      <c r="C106" s="4" t="inlineStr">
-        <is>
-          <t>VT REEDLE SHOT 100 / Бустер-сыворотка с микроиглами</t>
-        </is>
-      </c>
-      <c r="D106" s="5" t="n">
-        <v>397</v>
-      </c>
-      <c r="E106" s="5" t="n">
-        <v>974</v>
-      </c>
-      <c r="F106" s="5" t="n">
-        <v>13568</v>
-      </c>
-      <c r="G106" s="5" t="n">
-        <v>841</v>
-      </c>
-      <c r="H106" s="5" t="n">
-        <v>967</v>
-      </c>
-      <c r="I106" s="4" t="inlineStr">
-        <is>
-          <t>FINESKIN (ответ)</t>
-        </is>
-      </c>
-      <c r="J106" s="5" t="n">
-        <v>-7</v>
-      </c>
-      <c r="K106" s="4" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="L106" s="5" t="n">
-        <v>-2637</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="n"/>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>PETITFEE</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="n"/>
-      <c r="D107" s="3" t="n"/>
-      <c r="E107" s="3" t="n"/>
-      <c r="F107" s="3" t="n"/>
-      <c r="G107" s="3" t="n"/>
-      <c r="H107" s="3" t="n"/>
-      <c r="I107" s="2" t="n"/>
-      <c r="J107" s="3" t="n"/>
-      <c r="K107" s="2" t="n"/>
-      <c r="L107" s="3" t="n"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="4" t="n">
-        <v>71</v>
-      </c>
-      <c r="B108" s="4" t="inlineStr">
-        <is>
-          <t>PETITFEE</t>
-        </is>
-      </c>
-      <c r="C108" s="4" t="inlineStr">
-        <is>
-          <t>PETITFEE - Bera Glucan Deep Firming Eye Patch [60ea] / Тканевые патчи для век увлажняющие</t>
-        </is>
-      </c>
-      <c r="D108" s="5" t="n">
-        <v>180</v>
-      </c>
-      <c r="E108" s="5" t="n">
-        <v>487</v>
-      </c>
-      <c r="F108" s="5" t="n">
-        <v>6790</v>
-      </c>
-      <c r="G108" s="5" t="n">
-        <v>421</v>
-      </c>
-      <c r="H108" s="5" t="n">
-        <v>484</v>
-      </c>
-      <c r="I108" s="4" t="inlineStr">
-        <is>
-          <t>J2K (ответ)</t>
-        </is>
-      </c>
-      <c r="J108" s="5" t="n">
-        <v>-3</v>
-      </c>
-      <c r="K108" s="4" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="L108" s="5" t="n">
-        <v>-461</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="4" t="n">
-        <v>72</v>
-      </c>
-      <c r="B109" s="4" t="inlineStr">
-        <is>
-          <t>PETITFEE</t>
-        </is>
-      </c>
-      <c r="C109" s="4" t="inlineStr">
-        <is>
-          <t>PETITFEE - Pink Vita Brightening Eye Patch [60ea] / Тканевые патчи для век увлажняющие</t>
-        </is>
-      </c>
-      <c r="D109" s="5" t="n">
-        <v>117</v>
-      </c>
-      <c r="E109" s="5" t="n">
-        <v>487</v>
-      </c>
-      <c r="F109" s="5" t="n">
-        <v>6790</v>
-      </c>
-      <c r="G109" s="5" t="n">
-        <v>421</v>
-      </c>
-      <c r="H109" s="5" t="n">
-        <v>484</v>
-      </c>
-      <c r="I109" s="4" t="inlineStr">
-        <is>
-          <t>J2K (ответ)</t>
-        </is>
-      </c>
-      <c r="J109" s="5" t="n">
-        <v>-3</v>
-      </c>
-      <c r="K109" s="4" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="L109" s="5" t="n">
-        <v>-300</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="9" t="inlineStr"/>
-      <c r="B110" s="9" t="inlineStr">
+      <c r="A90" s="9" t="inlineStr"/>
+      <c r="B90" s="9" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="C110" s="9" t="inlineStr">
+      <c r="C90" s="9" t="inlineStr">
         <is>
           <t>позиций: 72</t>
         </is>
       </c>
-      <c r="D110" s="10" t="n">
+      <c r="D90" s="10" t="n">
         <v>78646</v>
       </c>
-      <c r="E110" s="10" t="inlineStr"/>
-      <c r="F110" s="10" t="inlineStr"/>
-      <c r="G110" s="10" t="inlineStr"/>
-      <c r="H110" s="10" t="inlineStr"/>
-      <c r="I110" s="9" t="inlineStr"/>
-      <c r="J110" s="10" t="inlineStr"/>
-      <c r="K110" s="9" t="inlineStr"/>
-      <c r="L110" s="10" t="n">
+      <c r="E90" s="10" t="inlineStr"/>
+      <c r="F90" s="10" t="inlineStr"/>
+      <c r="G90" s="10" t="inlineStr"/>
+      <c r="H90" s="10" t="inlineStr"/>
+      <c r="I90" s="9" t="inlineStr"/>
+      <c r="J90" s="10" t="inlineStr"/>
+      <c r="K90" s="9" t="inlineStr"/>
+      <c r="L90" s="10" t="n">
         <v>-4232854</v>
       </c>
     </row>
@@ -9250,7 +8890,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L44"/>
+  <dimension ref="A1:L36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -9300,12 +8940,12 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Цена EXW, руб</t>
+          <t>Цена в Корее, руб</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>С доставкой, руб</t>
+          <t>Итого у нас на складе, руб</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -9315,12 +8955,12 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Разница, руб</t>
+          <t>Разница с доставкой, руб</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Разница, %</t>
+          <t>Разница с доставкой, %</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
@@ -9436,88 +9076,140 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n"/>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>ENOUGH</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="n"/>
-      <c r="G5" s="3" t="n"/>
-      <c r="H5" s="3" t="n"/>
-      <c r="I5" s="2" t="n"/>
-      <c r="J5" s="3" t="n"/>
-      <c r="K5" s="2" t="n"/>
-      <c r="L5" s="3" t="n"/>
+      <c r="A5" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>CELIMAX</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD_10EA [30ml]/успокаивающие тонер-пэды</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>97</v>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>1526</v>
+      </c>
+      <c r="G5" s="7" t="n">
+        <v>95</v>
+      </c>
+      <c r="H5" s="7" t="n">
+        <v>109</v>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>G&amp;E Global</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="K5" s="6" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="L5" s="7" t="n">
+        <v>11864</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>ENOUGH</t>
+          <t>CELIMAX</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>ENOUGH - Collagen Moisture Essential Cream [50ml] / Увлажняющий крем для лица с коллагеном</t>
+          <t>CELIMAX PORE+DARK SPOT BRIGHTENING CREAM [35ml]/Крем для выравнивания тона и рельефа кожи лица</t>
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>7340</v>
+        <v>13</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>161</v>
+        <v>623</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>2650</v>
+        <v>9508</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>164</v>
+        <v>589</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>189</v>
+        <v>678</v>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>FINESKIN (ответ)</t>
+          <t>G&amp;E Global</t>
         </is>
       </c>
       <c r="J6" s="7" t="n">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>17.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>202914</v>
+        <v>708</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n"/>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="A7" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>CELIMAX</t>
         </is>
       </c>
-      <c r="C7" s="2" t="n"/>
-      <c r="D7" s="3" t="n"/>
-      <c r="E7" s="3" t="n"/>
-      <c r="F7" s="3" t="n"/>
-      <c r="G7" s="3" t="n"/>
-      <c r="H7" s="3" t="n"/>
-      <c r="I7" s="2" t="n"/>
-      <c r="J7" s="3" t="n"/>
-      <c r="K7" s="2" t="n"/>
-      <c r="L7" s="3" t="n"/>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>CELIMAX THE REAL NONI ENERGY AMPOULE_30ML (NEW) [30ml]/Восстанавливающая сыворотка с экстрактом нони для лица</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>57</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>764</v>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>11194</v>
+      </c>
+      <c r="G7" s="7" t="n">
+        <v>694</v>
+      </c>
+      <c r="H7" s="7" t="n">
+        <v>798</v>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>G&amp;E Global</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="n">
+        <v>34</v>
+      </c>
+      <c r="K7" s="6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L7" s="7" t="n">
+        <v>1955</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
@@ -9526,23 +9218,23 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD_10EA [30ml]/успокаивающие тонер-пэды</t>
+          <t>CELIMAX PORE+DARK SPOT BRIGHTENING SERUM_30ml [30ml]/Сыворотка для выравнивания тона и рельефа кожи лица</t>
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>97</v>
+        <v>688</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>1526</v>
+        <v>9900</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>95</v>
+        <v>614</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>109</v>
+        <v>706</v>
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
@@ -9550,18 +9242,18 @@
         </is>
       </c>
       <c r="J8" s="7" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>12.2</v>
+        <v>2.7</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>11864</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
@@ -9570,23 +9262,23 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>CELIMAX PORE+DARK SPOT BRIGHTENING CREAM [35ml]/Крем для выравнивания тона и рельефа кожи лица</t>
+          <t>CELIMAX PORE+DARK SPOT BRIGHTENING PAD [100ml / 40pads]/Тонер-пэды для выравнивания тона и рельефа кожи</t>
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>13</v>
+        <v>1375</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>623</v>
+        <v>556</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>9508</v>
+        <v>7950</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>589</v>
+        <v>493</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>678</v>
+        <v>567</v>
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
@@ -9594,20 +9286,20 @@
         </is>
       </c>
       <c r="J9" s="7" t="n">
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>8.699999999999999</v>
+        <v>1.9</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>708</v>
+        <v>14651</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C10" s="2" t="n"/>
@@ -9623,179 +9315,127 @@
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>PETITFEE - Agave Cooling Hydrogel Face Mask [5pcs] / Охлаждающая гидрогелевая маска для лица с экстрактом агавы</t>
+          <t>ENOUGH - Collagen Moisture Essential Cream [50ml] / Увлажняющий крем для лица с коллагеном</t>
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>600</v>
+        <v>7340</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>486</v>
+        <v>161</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>7290</v>
+        <v>2650</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>452</v>
+        <v>164</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>520</v>
+        <v>189</v>
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>J2K (ответ)</t>
+          <t>FINESKIN (ответ)</t>
         </is>
       </c>
       <c r="J11" s="7" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>6.9</v>
+        <v>17.1</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>20020</v>
+        <v>202914</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>PETITFEE</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>PETITFEE - Agave Cooling Hydrogel Eye Patch [60ea] / Охлаждающие гидрогелевые патчи для глаз с экстрактом агавы</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="n">
-        <v>360</v>
-      </c>
-      <c r="E12" s="7" t="n">
-        <v>415</v>
-      </c>
-      <c r="F12" s="7" t="n">
-        <v>6190</v>
-      </c>
-      <c r="G12" s="7" t="n">
-        <v>384</v>
-      </c>
-      <c r="H12" s="7" t="n">
-        <v>441</v>
-      </c>
-      <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>J2K (ответ)</t>
-        </is>
-      </c>
-      <c r="J12" s="7" t="n">
-        <v>26</v>
-      </c>
-      <c r="K12" s="6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="L12" s="7" t="n">
-        <v>9319</v>
-      </c>
+      <c r="A12" s="2" t="n"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>FARMSTAY</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="3" t="n"/>
+      <c r="F12" s="3" t="n"/>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
+      <c r="I12" s="2" t="n"/>
+      <c r="J12" s="3" t="n"/>
+      <c r="K12" s="2" t="n"/>
+      <c r="L12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>FARMSTAY</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>PETITFEE - Chamomile Lightening Hydrogel Eye Patch [60ea] / Успокаивающие гидрогелевые патчи для глаз с экстрактом ромашки</t>
+          <t>FARMSTAY - Gold Snail Premium Cream [50ml] / Омолаживающий крем с муцином улитки и коллоидным золотом</t>
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>415</v>
+        <v>431</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>6190</v>
+        <v>6390</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>384</v>
+        <v>396</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>441</v>
+        <v>456</v>
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>J2K (ответ)</t>
+          <t>Классик</t>
         </is>
       </c>
       <c r="J13" s="7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>0</v>
+        <v>22101</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>PETITFEE</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>PETITFEE - Cacao Energizing Hydrogel Eye Patch [60ea] / Тонизирующие гидрогелевые патчи для глаз с экстрактом какао</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="n">
-        <v>72</v>
-      </c>
-      <c r="E14" s="7" t="n">
-        <v>415</v>
-      </c>
-      <c r="F14" s="7" t="n">
-        <v>6190</v>
-      </c>
-      <c r="G14" s="7" t="n">
-        <v>384</v>
-      </c>
-      <c r="H14" s="7" t="n">
-        <v>441</v>
-      </c>
-      <c r="I14" s="6" t="inlineStr">
-        <is>
-          <t>J2K (ответ)</t>
-        </is>
-      </c>
-      <c r="J14" s="7" t="n">
-        <v>26</v>
-      </c>
-      <c r="K14" s="6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="L14" s="7" t="n">
-        <v>1864</v>
-      </c>
+      <c r="A14" s="2" t="n"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>MANYO</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="3" t="n"/>
+      <c r="E14" s="3" t="n"/>
+      <c r="F14" s="3" t="n"/>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
+      <c r="I14" s="2" t="n"/>
+      <c r="J14" s="3" t="n"/>
+      <c r="K14" s="2" t="n"/>
+      <c r="L14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="n">
@@ -9803,189 +9443,241 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
+          <t>MANYO</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>MANYO BIFIDA INFUSION SHOT AMPOULE 1DX [50ml] / Сыворотка с микроиглами и пробиотиками</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>614</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>997</v>
+      </c>
+      <c r="F15" s="7" t="n">
+        <v>14820</v>
+      </c>
+      <c r="G15" s="7" t="n">
+        <v>919</v>
+      </c>
+      <c r="H15" s="7" t="n">
+        <v>1057</v>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>PAPA COSMETIC (ответ)</t>
+        </is>
+      </c>
+      <c r="J15" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="K15" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="L15" s="7" t="n">
+        <v>36788</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>MANYO</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>MANYO - Galac Whitening Vita Serum [50ml] / Осветляющая сыворотка с Витамином C</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>759</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>647</v>
+      </c>
+      <c r="F16" s="7" t="n">
+        <v>9500</v>
+      </c>
+      <c r="G16" s="7" t="n">
+        <v>589</v>
+      </c>
+      <c r="H16" s="7" t="n">
+        <v>677</v>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>PAPA COSMETIC (ответ)</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="n">
+        <v>31</v>
+      </c>
+      <c r="K16" s="6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L16" s="7" t="n">
+        <v>23165</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>PETITFEE</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>PETITFEE - Artichoke Soothing Hydrogel Eye Patch [60ea] / Смягчающие гидрогелевые патчи для глаз с экстрактом артишока</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="n">
-        <v>156</v>
-      </c>
-      <c r="E15" s="7" t="n">
-        <v>415</v>
-      </c>
-      <c r="F15" s="7" t="n">
-        <v>6190</v>
-      </c>
-      <c r="G15" s="7" t="n">
-        <v>384</v>
-      </c>
-      <c r="H15" s="7" t="n">
-        <v>441</v>
-      </c>
-      <c r="I15" s="6" t="inlineStr">
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="3" t="n"/>
+      <c r="F17" s="3" t="n"/>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+      <c r="I17" s="2" t="n"/>
+      <c r="J17" s="3" t="n"/>
+      <c r="K17" s="2" t="n"/>
+      <c r="L17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>PETITFEE - Agave Cooling Hydrogel Face Mask [5pcs] / Охлаждающая гидрогелевая маска для лица с экстрактом агавы</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>600</v>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>486</v>
+      </c>
+      <c r="F18" s="7" t="n">
+        <v>7290</v>
+      </c>
+      <c r="G18" s="7" t="n">
+        <v>452</v>
+      </c>
+      <c r="H18" s="7" t="n">
+        <v>520</v>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
         <is>
           <t>J2K (ответ)</t>
         </is>
       </c>
-      <c r="J15" s="7" t="n">
-        <v>26</v>
-      </c>
-      <c r="K15" s="6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="L15" s="7" t="n">
-        <v>4038</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n"/>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>MANYO</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="3" t="n"/>
-      <c r="E16" s="3" t="n"/>
-      <c r="F16" s="3" t="n"/>
-      <c r="G16" s="3" t="n"/>
-      <c r="H16" s="3" t="n"/>
-      <c r="I16" s="2" t="n"/>
-      <c r="J16" s="3" t="n"/>
-      <c r="K16" s="2" t="n"/>
-      <c r="L16" s="3" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>MANYO</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>MANYO BIFIDA INFUSION SHOT AMPOULE 1DX [50ml] / Сыворотка с микроиглами и пробиотиками</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="n">
-        <v>614</v>
-      </c>
-      <c r="E17" s="7" t="n">
-        <v>997</v>
-      </c>
-      <c r="F17" s="7" t="n">
-        <v>14820</v>
-      </c>
-      <c r="G17" s="7" t="n">
-        <v>919</v>
-      </c>
-      <c r="H17" s="7" t="n">
-        <v>1057</v>
-      </c>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>PAPA COSMETIC (ответ)</t>
-        </is>
-      </c>
-      <c r="J17" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="K17" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="L17" s="7" t="n">
-        <v>36788</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n"/>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>FARMSTAY</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="n"/>
-      <c r="D18" s="3" t="n"/>
-      <c r="E18" s="3" t="n"/>
-      <c r="F18" s="3" t="n"/>
-      <c r="G18" s="3" t="n"/>
-      <c r="H18" s="3" t="n"/>
-      <c r="I18" s="2" t="n"/>
-      <c r="J18" s="3" t="n"/>
-      <c r="K18" s="2" t="n"/>
-      <c r="L18" s="3" t="n"/>
+      <c r="J18" s="7" t="n">
+        <v>33</v>
+      </c>
+      <c r="K18" s="6" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="L18" s="7" t="n">
+        <v>20020</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>FARMSTAY</t>
+          <t>PETITFEE</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>FARMSTAY - Gold Snail Premium Cream [50ml] / Омолаживающий крем с муцином улитки и коллоидным золотом</t>
+          <t>PETITFEE - Agave Cooling Hydrogel Eye Patch [60ea] / Охлаждающие гидрогелевые патчи для глаз с экстрактом агавы</t>
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>900</v>
+        <v>360</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>431</v>
+        <v>415</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>6390</v>
+        <v>6190</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>396</v>
+        <v>384</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>456</v>
+        <v>441</v>
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
-          <t>Классик</t>
+          <t>J2K (ответ)</t>
         </is>
       </c>
       <c r="J19" s="7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="L19" s="7" t="n">
-        <v>22101</v>
+        <v>9319</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n"/>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="A20" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>PETITFEE</t>
         </is>
       </c>
-      <c r="C20" s="2" t="n"/>
-      <c r="D20" s="3" t="n"/>
-      <c r="E20" s="3" t="n"/>
-      <c r="F20" s="3" t="n"/>
-      <c r="G20" s="3" t="n"/>
-      <c r="H20" s="3" t="n"/>
-      <c r="I20" s="2" t="n"/>
-      <c r="J20" s="3" t="n"/>
-      <c r="K20" s="2" t="n"/>
-      <c r="L20" s="3" t="n"/>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>PETITFEE - Artichoke Soothing Hydrogel Eye Patch [60ea] / Смягчающие гидрогелевые патчи для глаз с экстрактом артишока</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>156</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>415</v>
+      </c>
+      <c r="F20" s="7" t="n">
+        <v>6190</v>
+      </c>
+      <c r="G20" s="7" t="n">
+        <v>384</v>
+      </c>
+      <c r="H20" s="7" t="n">
+        <v>441</v>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>J2K (ответ)</t>
+        </is>
+      </c>
+      <c r="J20" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="K20" s="6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L20" s="7" t="n">
+        <v>4038</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
@@ -9994,23 +9686,23 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>PETITFEE - Collagen &amp; CoQ10 Hydrogel Eye Patch [60ea] / Гидрогелевые патчи для глаз с коллагеном и коэнзимом Q10</t>
+          <t>PETITFEE - Cacao Energizing Hydrogel Eye Patch [60ea] / Тонизирующие гидрогелевые патчи для глаз с экстрактом какао</t>
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>360</v>
+        <v>72</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>385</v>
+        <v>415</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>5690</v>
+        <v>6190</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>353</v>
+        <v>384</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>406</v>
+        <v>441</v>
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
@@ -10018,18 +9710,18 @@
         </is>
       </c>
       <c r="J21" s="7" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="L21" s="7" t="n">
-        <v>7433</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
@@ -10038,23 +9730,23 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>PETITFEE - Gold &amp; EGF Hydrogel Eye &amp; Spot Patch [60ea]/ гидрогелевые патчи с золотом и EGF</t>
+          <t>PETITFEE - Chamomile Lightening Hydrogel Eye Patch [60ea] / Успокаивающие гидрогелевые патчи для глаз с экстрактом ромашки</t>
         </is>
       </c>
       <c r="D22" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>385</v>
+        <v>415</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>5690</v>
+        <v>6190</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>353</v>
+        <v>384</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>406</v>
+        <v>441</v>
       </c>
       <c r="I22" s="6" t="inlineStr">
         <is>
@@ -10062,98 +9754,150 @@
         </is>
       </c>
       <c r="J22" s="7" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="L22" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n"/>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>MANYO</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="n"/>
-      <c r="D23" s="3" t="n"/>
-      <c r="E23" s="3" t="n"/>
-      <c r="F23" s="3" t="n"/>
-      <c r="G23" s="3" t="n"/>
-      <c r="H23" s="3" t="n"/>
-      <c r="I23" s="2" t="n"/>
-      <c r="J23" s="3" t="n"/>
-      <c r="K23" s="2" t="n"/>
-      <c r="L23" s="3" t="n"/>
+      <c r="A23" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>PETITFEE - Collagen &amp; CoQ10 Hydrogel Eye Patch [60ea] / Гидрогелевые патчи для глаз с коллагеном и коэнзимом Q10</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="n">
+        <v>360</v>
+      </c>
+      <c r="E23" s="7" t="n">
+        <v>385</v>
+      </c>
+      <c r="F23" s="7" t="n">
+        <v>5690</v>
+      </c>
+      <c r="G23" s="7" t="n">
+        <v>353</v>
+      </c>
+      <c r="H23" s="7" t="n">
+        <v>406</v>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>J2K (ответ)</t>
+        </is>
+      </c>
+      <c r="J23" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="K23" s="6" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="L23" s="7" t="n">
+        <v>7433</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>MANYO</t>
+          <t>PETITFEE</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>MANYO - Galac Whitening Vita Serum [50ml] / Осветляющая сыворотка с Витамином C</t>
+          <t>PETITFEE - Gold &amp; EGF Hydrogel Eye &amp; Spot Patch [60ea]/ гидрогелевые патчи с золотом и EGF</t>
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>759</v>
+        <v>0</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>647</v>
+        <v>385</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>9500</v>
+        <v>5690</v>
       </c>
       <c r="G24" s="7" t="n">
-        <v>589</v>
+        <v>353</v>
       </c>
       <c r="H24" s="7" t="n">
-        <v>677</v>
+        <v>406</v>
       </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
-          <t>PAPA COSMETIC (ответ)</t>
+          <t>J2K (ответ)</t>
         </is>
       </c>
       <c r="J24" s="7" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="K24" s="6" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="L24" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Eye Patch [60ea] / Гидрогелевые патчи для глаз с черным жемчугом и золотом</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="n">
+        <v>216</v>
+      </c>
+      <c r="E25" s="7" t="n">
+        <v>388</v>
+      </c>
+      <c r="F25" s="7" t="n">
+        <v>5690</v>
+      </c>
+      <c r="G25" s="7" t="n">
+        <v>353</v>
+      </c>
+      <c r="H25" s="7" t="n">
+        <v>406</v>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>J2K (ответ)</t>
+        </is>
+      </c>
+      <c r="J25" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="K25" s="6" t="n">
         <v>4.7</v>
       </c>
-      <c r="L24" s="7" t="n">
-        <v>23165</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="n"/>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>PETITFEE</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="n"/>
-      <c r="D25" s="3" t="n"/>
-      <c r="E25" s="3" t="n"/>
-      <c r="F25" s="3" t="n"/>
-      <c r="G25" s="3" t="n"/>
-      <c r="H25" s="3" t="n"/>
-      <c r="I25" s="2" t="n"/>
-      <c r="J25" s="3" t="n"/>
-      <c r="K25" s="2" t="n"/>
-      <c r="L25" s="3" t="n"/>
+      <c r="L25" s="7" t="n">
+        <v>3894</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
@@ -10162,23 +9906,23 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Eye Patch [60ea] / Гидрогелевые патчи для глаз с черным жемчугом и золотом</t>
+          <t>PETITFEE - Artichoke Soothing Hydrogel Face Mask [5pcs] / Смягчающая гидрогелевая маска для лица с экстрактом артишока</t>
         </is>
       </c>
       <c r="D26" s="7" t="n">
-        <v>216</v>
+        <v>60</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>388</v>
+        <v>499</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>5690</v>
+        <v>7290</v>
       </c>
       <c r="G26" s="7" t="n">
-        <v>353</v>
+        <v>452</v>
       </c>
       <c r="H26" s="7" t="n">
-        <v>406</v>
+        <v>520</v>
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
@@ -10186,604 +9930,356 @@
         </is>
       </c>
       <c r="J26" s="7" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="L26" s="7" t="n">
-        <v>3894</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n"/>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>CELIMAX</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="n"/>
-      <c r="D27" s="3" t="n"/>
-      <c r="E27" s="3" t="n"/>
-      <c r="F27" s="3" t="n"/>
-      <c r="G27" s="3" t="n"/>
-      <c r="H27" s="3" t="n"/>
-      <c r="I27" s="2" t="n"/>
-      <c r="J27" s="3" t="n"/>
-      <c r="K27" s="2" t="n"/>
-      <c r="L27" s="3" t="n"/>
+      <c r="A27" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Mask Pack [5pcs] / Гидрогелевая маска для лица с черным жемчугом и золотом</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="E27" s="7" t="n">
+        <v>478</v>
+      </c>
+      <c r="F27" s="7" t="n">
+        <v>6990</v>
+      </c>
+      <c r="G27" s="7" t="n">
+        <v>433</v>
+      </c>
+      <c r="H27" s="7" t="n">
+        <v>498</v>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>J2K (ответ)</t>
+        </is>
+      </c>
+      <c r="J27" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="K27" s="6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L27" s="7" t="n">
+        <v>1830</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>CELIMAX</t>
+          <t>PETITFEE</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>CELIMAX THE REAL NONI ENERGY AMPOULE_30ML (NEW) [30ml]/Восстанавливающая сыворотка с экстрактом нони для лица</t>
+          <t>PETITFEE - Gold &amp; Snail Hydrogel Mask Pack [5pcs] / Гидрогелевая маска для лица с золотом и экстрактом улитки</t>
         </is>
       </c>
       <c r="D28" s="7" t="n">
-        <v>57</v>
+        <v>150</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>764</v>
+        <v>478</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>11194</v>
+        <v>6990</v>
       </c>
       <c r="G28" s="7" t="n">
-        <v>694</v>
+        <v>433</v>
       </c>
       <c r="H28" s="7" t="n">
-        <v>798</v>
+        <v>498</v>
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
-          <t>G&amp;E Global</t>
+          <t>J2K (ответ)</t>
         </is>
       </c>
       <c r="J28" s="7" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="L28" s="7" t="n">
-        <v>1955</v>
+        <v>3033</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n"/>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="A29" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>PETITFEE - Cacao Energizing Hydrogel Mask Pack [5pcs] / Тонизирующая гидрогелевая маска для лица с экстрактом какао</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="E29" s="7" t="n">
+        <v>497</v>
+      </c>
+      <c r="F29" s="7" t="n">
+        <v>6990</v>
+      </c>
+      <c r="G29" s="7" t="n">
+        <v>433</v>
+      </c>
+      <c r="H29" s="7" t="n">
+        <v>498</v>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>J2K (ответ)</t>
+        </is>
+      </c>
+      <c r="J29" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K29" s="6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L29" s="7" t="n">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n"/>
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>ROUND LAB</t>
         </is>
       </c>
-      <c r="C29" s="2" t="n"/>
-      <c r="D29" s="3" t="n"/>
-      <c r="E29" s="3" t="n"/>
-      <c r="F29" s="3" t="n"/>
-      <c r="G29" s="3" t="n"/>
-      <c r="H29" s="3" t="n"/>
-      <c r="I29" s="2" t="n"/>
-      <c r="J29" s="3" t="n"/>
-      <c r="K29" s="2" t="n"/>
-      <c r="L29" s="3" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="3" t="n"/>
+      <c r="E30" s="3" t="n"/>
+      <c r="F30" s="3" t="n"/>
+      <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
+      <c r="I30" s="2" t="n"/>
+      <c r="J30" s="3" t="n"/>
+      <c r="K30" s="2" t="n"/>
+      <c r="L30" s="3" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>ROUND LAB</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>ROUND LAB 1025 DOKDO TONER_200ml / Отшелушивающий тоник с морской водой</t>
         </is>
       </c>
-      <c r="D30" s="7" t="n">
+      <c r="D31" s="7" t="n">
         <v>966</v>
       </c>
-      <c r="E30" s="7" t="n">
+      <c r="E31" s="7" t="n">
         <v>485</v>
       </c>
-      <c r="F30" s="7" t="n">
+      <c r="F31" s="7" t="n">
         <v>7100</v>
       </c>
-      <c r="G30" s="7" t="n">
+      <c r="G31" s="7" t="n">
         <v>440</v>
       </c>
-      <c r="H30" s="7" t="n">
+      <c r="H31" s="7" t="n">
         <v>506</v>
       </c>
-      <c r="I30" s="6" t="inlineStr">
+      <c r="I31" s="6" t="inlineStr">
         <is>
           <t>Papa Cosmetic</t>
         </is>
       </c>
-      <c r="J30" s="7" t="n">
+      <c r="J31" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="K30" s="6" t="n">
+      <c r="K31" s="6" t="n">
         <v>4.4</v>
       </c>
-      <c r="L30" s="7" t="n">
+      <c r="L31" s="7" t="n">
         <v>20576</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="n"/>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>PETITFEE</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="n"/>
-      <c r="D31" s="3" t="n"/>
-      <c r="E31" s="3" t="n"/>
-      <c r="F31" s="3" t="n"/>
-      <c r="G31" s="3" t="n"/>
-      <c r="H31" s="3" t="n"/>
-      <c r="I31" s="2" t="n"/>
-      <c r="J31" s="3" t="n"/>
-      <c r="K31" s="2" t="n"/>
-      <c r="L31" s="3" t="n"/>
-    </row>
     <row r="32">
-      <c r="A32" s="6" t="n">
-        <v>19</v>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>PETITFEE</t>
-        </is>
-      </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>PETITFEE - Artichoke Soothing Hydrogel Face Mask [5pcs] / Смягчающая гидрогелевая маска для лица с экстрактом артишока</t>
-        </is>
-      </c>
-      <c r="D32" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="E32" s="7" t="n">
-        <v>499</v>
-      </c>
-      <c r="F32" s="7" t="n">
-        <v>7290</v>
-      </c>
-      <c r="G32" s="7" t="n">
-        <v>452</v>
-      </c>
-      <c r="H32" s="7" t="n">
-        <v>520</v>
-      </c>
-      <c r="I32" s="6" t="inlineStr">
-        <is>
-          <t>J2K (ответ)</t>
-        </is>
-      </c>
-      <c r="J32" s="7" t="n">
-        <v>21</v>
-      </c>
-      <c r="K32" s="6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L32" s="7" t="n">
-        <v>1274</v>
-      </c>
+      <c r="A32" s="2" t="n"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>THE ORDINARY</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="n"/>
+      <c r="D32" s="3" t="n"/>
+      <c r="E32" s="3" t="n"/>
+      <c r="F32" s="3" t="n"/>
+      <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
+      <c r="I32" s="2" t="n"/>
+      <c r="J32" s="3" t="n"/>
+      <c r="K32" s="2" t="n"/>
+      <c r="L32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>THE ORDINARY</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Mask Pack [5pcs] / Гидрогелевая маска для лица с черным жемчугом и золотом</t>
+          <t>THE ORDINARY - Glycolic Acid 7% Toning Solution [KOR] [240ml] / Тоник с гликолевой кислотой 7%</t>
         </is>
       </c>
       <c r="D33" s="7" t="n">
-        <v>90</v>
+        <v>31</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>478</v>
+        <v>845</v>
       </c>
       <c r="F33" s="7" t="n">
-        <v>6990</v>
+        <v>12214</v>
       </c>
       <c r="G33" s="7" t="n">
-        <v>433</v>
+        <v>757</v>
       </c>
       <c r="H33" s="7" t="n">
-        <v>498</v>
+        <v>871</v>
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>J2K (ответ)</t>
+          <t>FINESKIN (ответ)</t>
         </is>
       </c>
       <c r="J33" s="7" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="L33" s="7" t="n">
-        <v>1830</v>
+        <v>786</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="n">
-        <v>21</v>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>PETITFEE</t>
-        </is>
-      </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>PETITFEE - Gold &amp; Snail Hydrogel Mask Pack [5pcs] / Гидрогелевая маска для лица с золотом и экстрактом улитки</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="n">
-        <v>150</v>
-      </c>
-      <c r="E34" s="7" t="n">
-        <v>478</v>
-      </c>
-      <c r="F34" s="7" t="n">
-        <v>6990</v>
-      </c>
-      <c r="G34" s="7" t="n">
-        <v>433</v>
-      </c>
-      <c r="H34" s="7" t="n">
-        <v>498</v>
-      </c>
-      <c r="I34" s="6" t="inlineStr">
-        <is>
-          <t>J2K (ответ)</t>
-        </is>
-      </c>
-      <c r="J34" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="K34" s="6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L34" s="7" t="n">
-        <v>3033</v>
-      </c>
+      <c r="A34" s="2" t="n"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>VT COSMETICS</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n"/>
+      <c r="D34" s="3" t="n"/>
+      <c r="E34" s="3" t="n"/>
+      <c r="F34" s="3" t="n"/>
+      <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
+      <c r="I34" s="2" t="n"/>
+      <c r="J34" s="3" t="n"/>
+      <c r="K34" s="2" t="n"/>
+      <c r="L34" s="3" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n"/>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>THE ORDINARY</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="n"/>
-      <c r="D35" s="3" t="n"/>
-      <c r="E35" s="3" t="n"/>
-      <c r="F35" s="3" t="n"/>
-      <c r="G35" s="3" t="n"/>
-      <c r="H35" s="3" t="n"/>
-      <c r="I35" s="2" t="n"/>
-      <c r="J35" s="3" t="n"/>
-      <c r="K35" s="2" t="n"/>
-      <c r="L35" s="3" t="n"/>
+      <c r="A35" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>VT COSMETICS</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>VT PDRN ESSENCE 100 / Укрепляющая бустер-эссенция с ПДРН</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="n">
+        <v>1009</v>
+      </c>
+      <c r="E35" s="7" t="n">
+        <v>1336</v>
+      </c>
+      <c r="F35" s="7" t="n">
+        <v>19080</v>
+      </c>
+      <c r="G35" s="7" t="n">
+        <v>1183</v>
+      </c>
+      <c r="H35" s="7" t="n">
+        <v>1360</v>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>FINESKIN (ответ)</t>
+        </is>
+      </c>
+      <c r="J35" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="K35" s="6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L35" s="7" t="n">
+        <v>24674</v>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="6" t="n">
-        <v>22</v>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
-        <is>
-          <t>THE ORDINARY</t>
-        </is>
-      </c>
-      <c r="C36" s="6" t="inlineStr">
-        <is>
-          <t>THE ORDINARY - Glycolic Acid 7% Toning Solution [KOR] [240ml] / Тоник с гликолевой кислотой 7%</t>
-        </is>
-      </c>
-      <c r="D36" s="7" t="n">
-        <v>31</v>
-      </c>
-      <c r="E36" s="7" t="n">
-        <v>845</v>
-      </c>
-      <c r="F36" s="7" t="n">
-        <v>12214</v>
-      </c>
-      <c r="G36" s="7" t="n">
-        <v>757</v>
-      </c>
-      <c r="H36" s="7" t="n">
-        <v>871</v>
-      </c>
-      <c r="I36" s="6" t="inlineStr">
-        <is>
-          <t>FINESKIN (ответ)</t>
-        </is>
-      </c>
-      <c r="J36" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="K36" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="L36" s="7" t="n">
-        <v>786</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="n"/>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>CELIMAX</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="n"/>
-      <c r="D37" s="3" t="n"/>
-      <c r="E37" s="3" t="n"/>
-      <c r="F37" s="3" t="n"/>
-      <c r="G37" s="3" t="n"/>
-      <c r="H37" s="3" t="n"/>
-      <c r="I37" s="2" t="n"/>
-      <c r="J37" s="3" t="n"/>
-      <c r="K37" s="2" t="n"/>
-      <c r="L37" s="3" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="n">
-        <v>23</v>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>CELIMAX</t>
-        </is>
-      </c>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>CELIMAX PORE+DARK SPOT BRIGHTENING SERUM_30ml [30ml]/Сыворотка для выравнивания тона и рельефа кожи лица</t>
-        </is>
-      </c>
-      <c r="D38" s="7" t="n">
-        <v>70</v>
-      </c>
-      <c r="E38" s="7" t="n">
-        <v>688</v>
-      </c>
-      <c r="F38" s="7" t="n">
-        <v>9900</v>
-      </c>
-      <c r="G38" s="7" t="n">
-        <v>614</v>
-      </c>
-      <c r="H38" s="7" t="n">
-        <v>706</v>
-      </c>
-      <c r="I38" s="6" t="inlineStr">
-        <is>
-          <t>G&amp;E Global</t>
-        </is>
-      </c>
-      <c r="J38" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="K38" s="6" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="L38" s="7" t="n">
-        <v>1280</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="6" t="n">
-        <v>24</v>
-      </c>
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>CELIMAX</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>CELIMAX PORE+DARK SPOT BRIGHTENING PAD [100ml / 40pads]/Тонер-пэды для выравнивания тона и рельефа кожи</t>
-        </is>
-      </c>
-      <c r="D39" s="7" t="n">
-        <v>1375</v>
-      </c>
-      <c r="E39" s="7" t="n">
-        <v>556</v>
-      </c>
-      <c r="F39" s="7" t="n">
-        <v>7950</v>
-      </c>
-      <c r="G39" s="7" t="n">
-        <v>493</v>
-      </c>
-      <c r="H39" s="7" t="n">
-        <v>567</v>
-      </c>
-      <c r="I39" s="6" t="inlineStr">
-        <is>
-          <t>G&amp;E Global</t>
-        </is>
-      </c>
-      <c r="J39" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="K39" s="6" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="L39" s="7" t="n">
-        <v>14651</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="n"/>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>VT COSMETICS</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="n"/>
-      <c r="D40" s="3" t="n"/>
-      <c r="E40" s="3" t="n"/>
-      <c r="F40" s="3" t="n"/>
-      <c r="G40" s="3" t="n"/>
-      <c r="H40" s="3" t="n"/>
-      <c r="I40" s="2" t="n"/>
-      <c r="J40" s="3" t="n"/>
-      <c r="K40" s="2" t="n"/>
-      <c r="L40" s="3" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="B41" s="6" t="inlineStr">
-        <is>
-          <t>VT COSMETICS</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>VT PDRN ESSENCE 100 / Укрепляющая бустер-эссенция с ПДРН</t>
-        </is>
-      </c>
-      <c r="D41" s="7" t="n">
-        <v>1009</v>
-      </c>
-      <c r="E41" s="7" t="n">
-        <v>1336</v>
-      </c>
-      <c r="F41" s="7" t="n">
-        <v>19080</v>
-      </c>
-      <c r="G41" s="7" t="n">
-        <v>1183</v>
-      </c>
-      <c r="H41" s="7" t="n">
-        <v>1360</v>
-      </c>
-      <c r="I41" s="6" t="inlineStr">
-        <is>
-          <t>FINESKIN (ответ)</t>
-        </is>
-      </c>
-      <c r="J41" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="K41" s="6" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="L41" s="7" t="n">
-        <v>24674</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="n"/>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>PETITFEE</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="n"/>
-      <c r="D42" s="3" t="n"/>
-      <c r="E42" s="3" t="n"/>
-      <c r="F42" s="3" t="n"/>
-      <c r="G42" s="3" t="n"/>
-      <c r="H42" s="3" t="n"/>
-      <c r="I42" s="2" t="n"/>
-      <c r="J42" s="3" t="n"/>
-      <c r="K42" s="2" t="n"/>
-      <c r="L42" s="3" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="6" t="n">
-        <v>26</v>
-      </c>
-      <c r="B43" s="6" t="inlineStr">
-        <is>
-          <t>PETITFEE</t>
-        </is>
-      </c>
-      <c r="C43" s="6" t="inlineStr">
-        <is>
-          <t>PETITFEE - Cacao Energizing Hydrogel Mask Pack [5pcs] / Тонизирующая гидрогелевая маска для лица с экстрактом какао</t>
-        </is>
-      </c>
-      <c r="D43" s="7" t="n">
-        <v>90</v>
-      </c>
-      <c r="E43" s="7" t="n">
-        <v>497</v>
-      </c>
-      <c r="F43" s="7" t="n">
-        <v>6990</v>
-      </c>
-      <c r="G43" s="7" t="n">
-        <v>433</v>
-      </c>
-      <c r="H43" s="7" t="n">
-        <v>498</v>
-      </c>
-      <c r="I43" s="6" t="inlineStr">
-        <is>
-          <t>J2K (ответ)</t>
-        </is>
-      </c>
-      <c r="J43" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="K43" s="6" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="L43" s="7" t="n">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="9" t="inlineStr"/>
-      <c r="B44" s="9" t="inlineStr">
+      <c r="A36" s="9" t="inlineStr"/>
+      <c r="B36" s="9" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="C44" s="9" t="inlineStr">
+      <c r="C36" s="9" t="inlineStr">
         <is>
           <t>позиций: 26</t>
         </is>
       </c>
-      <c r="D44" s="10" t="n">
+      <c r="D36" s="10" t="n">
         <v>28893</v>
       </c>
-      <c r="E44" s="10" t="inlineStr"/>
-      <c r="F44" s="10" t="inlineStr"/>
-      <c r="G44" s="10" t="inlineStr"/>
-      <c r="H44" s="10" t="inlineStr"/>
-      <c r="I44" s="9" t="inlineStr"/>
-      <c r="J44" s="10" t="inlineStr"/>
-      <c r="K44" s="9" t="inlineStr"/>
-      <c r="L44" s="10" t="n">
+      <c r="E36" s="10" t="inlineStr"/>
+      <c r="F36" s="10" t="inlineStr"/>
+      <c r="G36" s="10" t="inlineStr"/>
+      <c r="H36" s="10" t="inlineStr"/>
+      <c r="I36" s="9" t="inlineStr"/>
+      <c r="J36" s="10" t="inlineStr"/>
+      <c r="K36" s="9" t="inlineStr"/>
+      <c r="L36" s="10" t="n">
         <v>2526589</v>
       </c>
     </row>
